--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://docs.philips.com/personal/pratibha_mehta_philips_com/Documents/Desktop/DMB-Kavya/DMB-Dashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{CF61E371-FDC2-4313-8354-7F57E073A406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{940CBCCD-E27B-418F-9113-5180B4E2B1BD}"/>
+  <xr:revisionPtr revIDLastSave="3207" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E097B0B-CC12-443A-81FF-F45BC921F7B0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" state="hidden" r:id="rId1"/>
@@ -586,7 +586,7 @@
     <t>Increase contract penetration %</t>
   </si>
   <si>
-    <t>1.2% Gap VS AOP. YoY improvement by 0.4%. Expected turnaround is Sep 2026. GRC CP% dropped significantly. NAR to catch up in Q3</t>
+    <t>0.9% Gap VS AOP. YoY improvement by 0.4%. Expected turnaround is Sep 2026. GRC CP% dropped significantly. NAR to catch up in Q3</t>
   </si>
   <si>
     <t>Funnel focus actions driven across regions for same</t>
@@ -828,13 +828,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="mmm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="mmm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1320,7 +1320,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1331,14 +1331,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1368,87 +1368,87 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1470,13 +1470,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1513,21 +1513,21 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1536,31 +1536,31 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1862,7 +1862,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1883,7 +1911,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1946,83 +2002,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2045,111 +2024,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2198,6 +2072,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2206,6 +2094,118 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2234,6 +2234,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2283,13 +2290,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5188,29 +5188,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AD843-49A7-417E-9F24-86908363EFA2}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.54296875" customWidth="1"/>
-    <col min="5" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" customWidth="1"/>
+    <col min="5" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15.95">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22">
       <c r="A5" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5364,7 +5364,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22">
       <c r="A6" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5433,9 +5433,9 @@
         <f>IF('AOP Critical'!S7="","",'AOP Critical'!S7)</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="S6" s="69" t="str">
+      <c r="S6" s="69">
         <f>IF('AOP Critical'!T7="","",'AOP Critical'!T7)</f>
-        <v/>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="T6" s="69" t="str">
         <f>IF('AOP Critical'!U7="","",'AOP Critical'!U7)</f>
@@ -5445,12 +5445,12 @@
         <f>IF('AOP Critical'!V7="","",'AOP Critical'!V7)</f>
         <v/>
       </c>
-      <c r="V6" s="69" t="str">
+      <c r="V6" s="69">
         <f>IF('AOP Critical'!W7="","",'AOP Critical'!W7)</f>
-        <v/>
+        <v>0.06</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22">
       <c r="A7" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5536,7 +5536,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22">
       <c r="A8" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5605,9 +5605,9 @@
         <f>IF('AOP Critical'!S9="","",'AOP Critical'!S9)</f>
         <v>1</v>
       </c>
-      <c r="S8" s="72" t="str">
+      <c r="S8" s="72">
         <f>IF('AOP Critical'!T9="","",'AOP Critical'!T9)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T8" s="72" t="str">
         <f>IF('AOP Critical'!U9="","",'AOP Critical'!U9)</f>
@@ -5622,7 +5622,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5708,7 +5708,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5777,9 +5777,9 @@
         <f>IF('AOP Critical'!S11="","",'AOP Critical'!S11)</f>
         <v>0</v>
       </c>
-      <c r="S10" t="str">
+      <c r="S10">
         <f>IF('AOP Critical'!T11="","",'AOP Critical'!T11)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T10" t="str">
         <f>IF('AOP Critical'!U11="","",'AOP Critical'!U11)</f>
@@ -5794,7 +5794,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22">
       <c r="A11" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5880,7 +5880,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22">
       <c r="A12" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5966,12 +5966,12 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22">
       <c r="A15" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6129,7 +6129,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22">
       <c r="A16" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6219,7 +6219,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22">
       <c r="A17" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6309,7 +6309,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22">
       <c r="A18" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6399,7 +6399,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22">
       <c r="A19" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6489,7 +6489,7 @@
         <v>0.73999999999999966</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22">
       <c r="A20" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6579,12 +6579,12 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22">
       <c r="A23" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6742,7 +6742,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22">
       <c r="A24" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6832,7 +6832,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22">
       <c r="A25" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6922,7 +6922,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22">
       <c r="A26" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -7012,7 +7012,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22">
       <c r="A27" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7102,7 +7102,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22">
       <c r="A28" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7192,7 +7192,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22">
       <c r="A29" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7282,7 +7282,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22">
       <c r="A30" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7372,12 +7372,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22">
       <c r="A33" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7535,7 +7535,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22">
       <c r="A34" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7625,7 +7625,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22">
       <c r="A35" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7715,7 +7715,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22">
       <c r="A36" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7805,7 +7805,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22">
       <c r="A37" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7895,7 +7895,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22">
       <c r="A38" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7985,7 +7985,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22">
       <c r="A39" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8075,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22">
       <c r="A40" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8165,7 +8165,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22">
       <c r="A41" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8255,7 +8255,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22">
       <c r="A42" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8345,12 +8345,12 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22">
       <c r="A43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22">
       <c r="A45" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8508,7 +8508,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22">
       <c r="A46" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8598,7 +8598,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22">
       <c r="A47" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8685,7 +8685,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22">
       <c r="A48" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8771,7 +8771,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22">
       <c r="A49" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8861,7 +8861,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22">
       <c r="A50" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8951,7 +8951,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22">
       <c r="A51" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9041,7 +9041,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22">
       <c r="A52" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9131,12 +9131,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22">
       <c r="A54" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -9525,34 +9525,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AC66"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.54296875" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="26.81640625" customWidth="1"/>
-    <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.81640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7265625" customWidth="1"/>
-    <col min="12" max="12" width="5.54296875" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="6.81640625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="6.26953125" customWidth="1"/>
-    <col min="15" max="15" width="7.26953125" customWidth="1"/>
-    <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="6.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" hidden="1" customWidth="1"/>
+    <col min="17" max="22" width="6.140625" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
-    <col min="25" max="25" width="68.1796875" customWidth="1"/>
-    <col min="26" max="26" width="17.7265625" customWidth="1"/>
+    <col min="24" max="24" width="58.85546875" style="20" customWidth="1"/>
+    <col min="25" max="25" width="68.140625" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" customWidth="1"/>
     <col min="27" max="27" width="57" style="13" customWidth="1"/>
-    <col min="28" max="46" width="8.54296875" customWidth="1"/>
+    <col min="28" max="46" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9563,7 +9563,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9572,7 +9572,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
       <c r="A3" s="110" t="s">
         <v>40</v>
       </c>
@@ -9596,10 +9596,10 @@
       <c r="X3" s="21"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" s="5" customFormat="1">
       <c r="A4" s="112" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
-        <v>Current Month-Year :2026-09</v>
+        <v>Current Month-Year :2026-10</v>
       </c>
       <c r="B4" s="112"/>
       <c r="C4" s="112"/>
@@ -9628,7 +9628,7 @@
       <c r="Z4" s="112"/>
       <c r="AA4" s="112"/>
     </row>
-    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="27" customHeight="1">
       <c r="A5" s="88" t="s">
         <v>0</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27">
       <c r="A6" s="109" t="s">
         <v>47</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27">
       <c r="A7" s="109"/>
       <c r="B7" s="91"/>
       <c r="C7" s="92"/>
@@ -9818,16 +9818,20 @@
       <c r="S7" s="52">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T7" s="52"/>
+      <c r="T7" s="52">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U7" s="52"/>
       <c r="V7" s="52"/>
-      <c r="W7" s="52"/>
+      <c r="W7" s="52">
+        <v>0.06</v>
+      </c>
       <c r="X7" s="94"/>
       <c r="Y7" s="96"/>
       <c r="Z7" s="96"/>
       <c r="AA7" s="124"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27">
       <c r="A8" s="109"/>
       <c r="B8" s="91" t="s">
         <v>56</v>
@@ -9892,7 +9896,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27">
       <c r="A9" s="109"/>
       <c r="B9" s="91"/>
       <c r="C9" s="92"/>
@@ -9930,7 +9934,9 @@
       <c r="S9" s="54">
         <v>1</v>
       </c>
-      <c r="T9" s="54"/>
+      <c r="T9" s="54">
+        <v>1</v>
+      </c>
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
@@ -9939,7 +9945,7 @@
       <c r="Z9" s="115"/>
       <c r="AA9" s="124"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27">
       <c r="A10" s="109"/>
       <c r="B10" s="91" t="s">
         <v>60</v>
@@ -10002,7 +10008,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="15" thickBot="1">
       <c r="A11" s="109"/>
       <c r="B11" s="91"/>
       <c r="C11" s="92"/>
@@ -10040,7 +10046,9 @@
       <c r="S11" s="32">
         <v>0</v>
       </c>
-      <c r="T11" s="32"/>
+      <c r="T11" s="32">
+        <v>0</v>
+      </c>
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
@@ -10049,7 +10057,7 @@
       <c r="Z11" s="118"/>
       <c r="AA11" s="124"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27">
       <c r="A12" s="109" t="s">
         <v>24</v>
       </c>
@@ -10122,7 +10130,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27">
       <c r="A13" s="109"/>
       <c r="B13" s="93"/>
       <c r="C13" s="93"/>
@@ -10169,7 +10177,7 @@
       <c r="Z13" s="96"/>
       <c r="AA13" s="124"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27">
       <c r="A14" s="109"/>
       <c r="B14" s="93" t="s">
         <v>68</v>
@@ -10234,7 +10242,7 @@
       <c r="Z14" s="152"/>
       <c r="AA14" s="151"/>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" ht="15" thickBot="1">
       <c r="A15" s="109"/>
       <c r="B15" s="93"/>
       <c r="C15" s="122"/>
@@ -10281,7 +10289,7 @@
       <c r="Z15" s="113"/>
       <c r="AA15" s="131"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27">
       <c r="A16" s="109" t="s">
         <v>25</v>
       </c>
@@ -10350,7 +10358,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27">
       <c r="A17" s="109"/>
       <c r="B17" s="93"/>
       <c r="C17" s="93"/>
@@ -10397,7 +10405,7 @@
       <c r="Z17" s="115"/>
       <c r="AA17" s="124"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27">
       <c r="A18" s="109"/>
       <c r="B18" s="93" t="s">
         <v>80</v>
@@ -10463,7 +10471,7 @@
       </c>
       <c r="AA18" s="157"/>
     </row>
-    <row r="19" spans="1:27" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
       <c r="A19" s="109"/>
       <c r="B19" s="93"/>
       <c r="C19" s="93"/>
@@ -10510,7 +10518,7 @@
       <c r="Z19" s="156"/>
       <c r="AA19" s="157"/>
     </row>
-    <row r="20" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" ht="21" customHeight="1">
       <c r="A20" s="109"/>
       <c r="B20" s="93" t="s">
         <v>84</v>
@@ -10577,7 +10585,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
       <c r="A21" s="109"/>
       <c r="B21" s="93"/>
       <c r="C21" s="93"/>
@@ -10624,7 +10632,7 @@
       <c r="Z21" s="119"/>
       <c r="AA21" s="125"/>
     </row>
-    <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" ht="15.95" customHeight="1">
       <c r="A22" s="109" t="s">
         <v>26</v>
       </c>
@@ -10697,7 +10705,7 @@
       </c>
       <c r="AA22" s="162"/>
     </row>
-    <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="A23" s="169"/>
       <c r="B23" s="93"/>
       <c r="C23" s="122"/>
@@ -10744,7 +10752,7 @@
       <c r="Z23" s="115"/>
       <c r="AA23" s="163"/>
     </row>
-    <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" ht="17.45" customHeight="1">
       <c r="A24" s="143" t="s">
         <v>27</v>
       </c>
@@ -10813,7 +10821,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:27" ht="15" thickBot="1">
       <c r="A25" s="168"/>
       <c r="B25" s="93"/>
       <c r="C25" s="122"/>
@@ -10864,7 +10872,7 @@
       <c r="Z25" s="153"/>
       <c r="AA25" s="124"/>
     </row>
-    <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" ht="14.45" customHeight="1">
       <c r="A26" s="168"/>
       <c r="B26" s="91" t="s">
         <v>98</v>
@@ -10927,7 +10935,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
       <c r="A27" s="168"/>
       <c r="B27" s="91"/>
       <c r="C27" s="161"/>
@@ -10974,7 +10982,7 @@
       <c r="Z27" s="115"/>
       <c r="AA27" s="124"/>
     </row>
-    <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" ht="14.45" customHeight="1">
       <c r="A28" s="168"/>
       <c r="B28" s="90" t="s">
         <v>101</v>
@@ -11039,7 +11047,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:27" ht="15" thickBot="1">
       <c r="A29" s="168"/>
       <c r="B29" s="90"/>
       <c r="C29" s="93"/>
@@ -11086,7 +11094,7 @@
       <c r="Z29" s="153"/>
       <c r="AA29" s="129"/>
     </row>
-    <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" ht="14.45" customHeight="1">
       <c r="A30" s="168"/>
       <c r="B30" s="90"/>
       <c r="C30" s="93" t="s">
@@ -11145,7 +11153,7 @@
       <c r="Z30" s="119"/>
       <c r="AA30" s="166"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:27">
       <c r="A31" s="168"/>
       <c r="B31" s="90"/>
       <c r="C31" s="93"/>
@@ -11192,7 +11200,7 @@
       <c r="Z31" s="153"/>
       <c r="AA31" s="167"/>
     </row>
-    <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" ht="14.45" customHeight="1">
       <c r="A32" s="168"/>
       <c r="B32" s="93" t="s">
         <v>106</v>
@@ -11259,7 +11267,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
       <c r="A33" s="168"/>
       <c r="B33" s="93"/>
       <c r="C33" s="122"/>
@@ -11306,7 +11314,7 @@
       <c r="Z33" s="153"/>
       <c r="AA33" s="124"/>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:29">
       <c r="A34" s="109" t="s">
         <v>28</v>
       </c>
@@ -11363,7 +11371,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:29">
       <c r="A35" s="109"/>
       <c r="B35" s="148"/>
       <c r="C35" s="93"/>
@@ -11410,7 +11418,7 @@
       <c r="Z35" s="115"/>
       <c r="AA35" s="124"/>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:29">
       <c r="A36" s="109"/>
       <c r="B36" s="148" t="s">
         <v>35</v>
@@ -11465,7 +11473,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:29">
       <c r="A37" s="109"/>
       <c r="B37" s="148"/>
       <c r="C37" s="93"/>
@@ -11510,7 +11518,7 @@
       <c r="Z37" s="119"/>
       <c r="AA37" s="125"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:29" s="5" customFormat="1">
       <c r="A38" s="138"/>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -11539,7 +11547,7 @@
       <c r="Z38" s="139"/>
       <c r="AA38" s="139"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
       <c r="A39" s="141" t="s">
         <v>117</v>
       </c>
@@ -11570,7 +11578,7 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:29" ht="27.6" customHeight="1">
       <c r="A40" s="44" t="s">
         <v>0</v>
       </c>
@@ -11653,7 +11661,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:29">
       <c r="A41" s="142" t="s">
         <v>47</v>
       </c>
@@ -11731,7 +11739,7 @@
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:29" ht="23.1" customHeight="1">
       <c r="A42" s="143"/>
       <c r="B42" s="91"/>
       <c r="C42" s="92"/>
@@ -11778,7 +11786,7 @@
       <c r="Z42" s="131"/>
       <c r="AA42" s="126"/>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:29">
       <c r="A43" s="144" t="s">
         <v>26</v>
       </c>
@@ -11839,7 +11847,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:29">
       <c r="A44" s="144"/>
       <c r="B44" s="91"/>
       <c r="C44" s="92"/>
@@ -11890,7 +11898,7 @@
       <c r="Z44" s="133"/>
       <c r="AA44" s="134"/>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:29">
       <c r="A45" s="144"/>
       <c r="B45" s="91" t="s">
         <v>131</v>
@@ -11959,7 +11967,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:29" ht="16.5" customHeight="1">
       <c r="A46" s="144"/>
       <c r="B46" s="91"/>
       <c r="C46" s="92"/>
@@ -12004,7 +12012,7 @@
       <c r="Z46" s="133"/>
       <c r="AA46" s="126"/>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:29">
       <c r="A47" s="144"/>
       <c r="B47" s="91" t="s">
         <v>134</v>
@@ -12079,7 +12087,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:29" ht="20.45" customHeight="1">
       <c r="A48" s="144"/>
       <c r="B48" s="91"/>
       <c r="C48" s="92"/>
@@ -12127,7 +12135,7 @@
       <c r="Z48" s="133"/>
       <c r="AA48" s="90"/>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:27">
       <c r="A49" s="143" t="s">
         <v>137</v>
       </c>
@@ -12204,7 +12212,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:27">
       <c r="A50" s="143"/>
       <c r="B50" s="150"/>
       <c r="C50" s="92"/>
@@ -12251,7 +12259,7 @@
       <c r="Z50" s="133"/>
       <c r="AA50" s="126"/>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:27">
       <c r="A51" s="144" t="s">
         <v>25</v>
       </c>
@@ -12320,7 +12328,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:27" ht="15" thickBot="1">
       <c r="A52" s="144"/>
       <c r="B52" s="91"/>
       <c r="C52" s="92"/>
@@ -12367,13 +12375,13 @@
       <c r="Z52" s="133"/>
       <c r="AA52" s="93"/>
     </row>
-    <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="58" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="60" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="62" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="64" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="66" ht="14.45" customHeight="1"/>
   </sheetData>
   <mergeCells count="270">
     <mergeCell ref="A24:A33"/>
@@ -12694,31 +12702,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="76" stopIfTrue="1">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    <cfRule type="expression" dxfId="66" priority="73">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="75">
+    <cfRule type="expression" dxfId="65" priority="74">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="75">
       <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="74">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="73">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    <cfRule type="expression" dxfId="63" priority="76" stopIfTrue="1">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="expression" dxfId="62" priority="244">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="69">
+    <cfRule type="expression" dxfId="62" priority="69">
       <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="242">
+    <cfRule type="expression" dxfId="61" priority="242">
       <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="243">
+    <cfRule type="expression" dxfId="60" priority="243">
       <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="244">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
@@ -12735,185 +12743,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="168">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="172">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="170">
+    <cfRule type="expression" dxfId="55" priority="170">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="171">
+    <cfRule type="expression" dxfId="54" priority="171">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="172">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="173" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="expression" dxfId="51" priority="102">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    <cfRule type="containsBlanks" dxfId="51" priority="99">
+      <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="101">
+    <cfRule type="expression" dxfId="50" priority="100">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="101">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="49" priority="99">
-      <formula>LEN(TRIM(L52))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="100">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    <cfRule type="expression" dxfId="48" priority="102">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="103" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="expression" dxfId="46" priority="66" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+    <cfRule type="containsBlanks" dxfId="46" priority="62">
+      <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="65">
+    <cfRule type="expression" dxfId="45" priority="63">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="64">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="65">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="63">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="43" priority="62">
-      <formula>LEN(TRIM(L25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="64">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    <cfRule type="expression" dxfId="42" priority="66" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="41" priority="13">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    <cfRule type="containsBlanks" dxfId="41" priority="11">
+      <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="12">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="39" priority="11">
+    <cfRule type="expression" dxfId="39" priority="13">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="14">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="36" priority="16">
       <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="20" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="17">
+    <cfRule type="expression" dxfId="35" priority="17">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="19">
+    <cfRule type="expression" dxfId="34" priority="18">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="19">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="35" priority="16">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="18">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="14">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="expression" dxfId="31" priority="60">
+    <cfRule type="containsBlanks" dxfId="31" priority="57">
+      <formula>LEN(TRIM(N44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="58">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="59">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="60">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="61" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="29" priority="57">
-      <formula>LEN(TRIM(N44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="58">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="59">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="expression" dxfId="26" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="26" priority="21">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="24">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="22">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="22">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="22" priority="21">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="22" priority="25" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="5">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="4">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="20" priority="2">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="3">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="1">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="4">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="17" priority="2">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="17" priority="5">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="expression" dxfId="16" priority="10" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="16" priority="6">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="9">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="7">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="8">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="9">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="12" priority="6">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="12" priority="10" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="expression" dxfId="11" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="11" priority="47">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="50">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="48">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="49">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="48">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="50">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="7" priority="47">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="7" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="expression" dxfId="6" priority="43">
+    <cfRule type="containsBlanks" dxfId="6" priority="42">
+      <formula>LEN(TRIM(W44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="43">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="5" priority="42">
-      <formula>LEN(TRIM(W44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="46" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="44">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="45">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="44">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -12964,10 +12972,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E190B01FBBC71F4E813E2B7C33AC5708" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e03fafc537a6dde41221df5bcac5e224">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="68108f69-118e-4385-83b3-00743b1bf54c" xmlns:ns3="f5a961e1-edc1-4f62-8655-e8a46ef79e5c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="890c93a9779df6c6d0b1580c0c9dfda5" ns2:_="" ns3:_="">
-    <xsd:import namespace="68108f69-118e-4385-83b3-00743b1bf54c"/>
-    <xsd:import namespace="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
+    <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -12976,17 +12983,7 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -12994,7 +12991,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="68108f69-118e-4385-83b3-00743b1bf54c" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -13007,90 +13004,10 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="19" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="20" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f5a961e1-edc1-4f62-8655-e8a46ef79e5c" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="12" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{1eecd06c-06a1-41c6-8d98-e61957be1bb4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f5a961e1-edc1-4f62-8655-e8a46ef79e5c">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -13208,59 +13125,24 @@
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f5a961e1-edc1-4f62-8655-e8a46ef79e5c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="68108f69-118e-4385-83b3-00743b1bf54c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6ADF58E-7D5A-460E-8A70-F141F18752FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
-    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F488CD-71A3-46BB-878D-37FDAEEAEE94}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
-    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1569,32 +1569,236 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1608,212 +1812,8 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9573,10 +9573,10 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="110"/>
+      <c r="B3" s="162"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9597,36 +9597,36 @@
       <c r="AA3" s="14"/>
     </row>
     <row r="4" spans="1:27" s="5" customFormat="1">
-      <c r="A4" s="112" t="str">
+      <c r="A4" s="163" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="163"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="163"/>
+      <c r="K4" s="163"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="163"/>
+      <c r="U4" s="163"/>
+      <c r="V4" s="163"/>
+      <c r="W4" s="163"/>
+      <c r="X4" s="163"/>
+      <c r="Y4" s="163"/>
+      <c r="Z4" s="163"/>
+      <c r="AA4" s="163"/>
     </row>
     <row r="5" spans="1:27" ht="27" customHeight="1">
       <c r="A5" s="88" t="s">
@@ -9641,11 +9641,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="116" t="s">
+      <c r="E5" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="164"/>
       <c r="H5" s="89" t="s">
         <v>8</v>
       </c>
@@ -9708,30 +9708,30 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="108">
+      <c r="E6" s="104">
         <v>10</v>
       </c>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="111" t="s">
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="107" t="s">
+      <c r="J6" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9773,24 +9773,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="106"/>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="123" t="s">
+      <c r="X6" s="110"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="117" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="109"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="107"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="106"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9826,34 +9826,34 @@
       <c r="W7" s="52">
         <v>0.06</v>
       </c>
-      <c r="X7" s="94"/>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
-      <c r="AA7" s="124"/>
+      <c r="X7" s="111"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="118"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="109"/>
-      <c r="B8" s="91" t="s">
+      <c r="A8" s="92"/>
+      <c r="B8" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="108">
+      <c r="E8" s="104">
         <v>90</v>
       </c>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="111" t="s">
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="108" t="s">
+      <c r="I8" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="107" t="s">
+      <c r="J8" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9885,28 +9885,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="95" t="s">
+      <c r="X8" s="111"/>
+      <c r="Y8" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="114">
+      <c r="Z8" s="115">
         <v>46231</v>
       </c>
-      <c r="AA8" s="123" t="s">
+      <c r="AA8" s="117" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="109"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="107"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="106"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9940,34 +9940,34 @@
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="124"/>
+      <c r="X9" s="111"/>
+      <c r="Y9" s="131"/>
+      <c r="Z9" s="116"/>
+      <c r="AA9" s="118"/>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="109"/>
-      <c r="B10" s="91" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="108">
+      <c r="E10" s="104">
         <v>1</v>
       </c>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="111" t="s">
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="107" t="s">
+      <c r="J10" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -10001,24 +10001,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="94"/>
-      <c r="Y10" s="164"/>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="123" t="s">
+      <c r="X10" s="111"/>
+      <c r="Y10" s="119"/>
+      <c r="Z10" s="165"/>
+      <c r="AA10" s="117" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" thickBot="1">
-      <c r="A11" s="109"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="107"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="106"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10052,36 +10052,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="94"/>
-      <c r="Y11" s="165"/>
-      <c r="Z11" s="118"/>
-      <c r="AA11" s="124"/>
+      <c r="X11" s="111"/>
+      <c r="Y11" s="120"/>
+      <c r="Z11" s="166"/>
+      <c r="AA11" s="118"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="109" t="s">
+      <c r="A12" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="108">
+      <c r="E12" s="104">
         <v>84</v>
       </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="111" t="s">
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="108" t="s">
+      <c r="I12" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="107" t="s">
+      <c r="J12" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10123,24 +10123,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="154"/>
-      <c r="Y12" s="95"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="123" t="s">
+      <c r="X12" s="129"/>
+      <c r="Y12" s="130"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="117" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="109"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="107"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="106"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10172,34 +10172,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="154"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="124"/>
+      <c r="X13" s="129"/>
+      <c r="Y13" s="131"/>
+      <c r="Z13" s="131"/>
+      <c r="AA13" s="118"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="109"/>
-      <c r="B14" s="93" t="s">
+      <c r="A14" s="92"/>
+      <c r="B14" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C14" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="108">
+      <c r="E14" s="104">
         <v>54.6</v>
       </c>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="111" t="s">
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="108" t="s">
+      <c r="I14" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="107" t="s">
+      <c r="J14" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10233,26 +10233,26 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="137" t="s">
+      <c r="X14" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="152" t="s">
+      <c r="Y14" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="Z14" s="152"/>
-      <c r="AA14" s="151"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="127"/>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1">
-      <c r="A15" s="109"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="107"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="106"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10284,36 +10284,36 @@
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="106"/>
-      <c r="Y15" s="113"/>
-      <c r="Z15" s="113"/>
-      <c r="AA15" s="131"/>
+      <c r="X15" s="110"/>
+      <c r="Y15" s="101"/>
+      <c r="Z15" s="101"/>
+      <c r="AA15" s="128"/>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="109" t="s">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="C16" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="90" t="s">
+      <c r="D16" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="108" t="s">
+      <c r="E16" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="111" t="s">
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="107" t="s">
+      <c r="J16" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10347,28 +10347,28 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="94" t="s">
+      <c r="X16" s="111" t="s">
         <v>77</v>
       </c>
-      <c r="Y16" s="95" t="s">
+      <c r="Y16" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="123" t="s">
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="117" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="109"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="107"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="106"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10400,34 +10400,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="94"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="124"/>
+      <c r="X17" s="111"/>
+      <c r="Y17" s="131"/>
+      <c r="Z17" s="116"/>
+      <c r="AA17" s="118"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="109"/>
-      <c r="B18" s="93" t="s">
+      <c r="A18" s="92"/>
+      <c r="B18" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="93" t="s">
+      <c r="D18" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="108" t="s">
+      <c r="E18" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="111" t="s">
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="108" t="s">
+      <c r="I18" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="107" t="s">
+      <c r="J18" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10462,26 +10462,26 @@
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="158" t="s">
+      <c r="X18" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="Y18" s="158"/>
-      <c r="Z18" s="155">
+      <c r="Y18" s="135"/>
+      <c r="Z18" s="132">
         <v>46108</v>
       </c>
-      <c r="AA18" s="157"/>
+      <c r="AA18" s="134"/>
     </row>
     <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
-      <c r="A19" s="109"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="107"/>
+      <c r="A19" s="92"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="106"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
@@ -10513,34 +10513,34 @@
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="50"/>
-      <c r="X19" s="158"/>
-      <c r="Y19" s="158"/>
-      <c r="Z19" s="156"/>
-      <c r="AA19" s="157"/>
+      <c r="X19" s="135"/>
+      <c r="Y19" s="135"/>
+      <c r="Z19" s="133"/>
+      <c r="AA19" s="134"/>
     </row>
     <row r="20" spans="1:27" ht="21" customHeight="1">
-      <c r="A20" s="109"/>
-      <c r="B20" s="93" t="s">
+      <c r="A20" s="92"/>
+      <c r="B20" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="90" t="s">
+      <c r="D20" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="108" t="s">
+      <c r="E20" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="108"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="111" t="s">
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="108" t="s">
+      <c r="I20" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="107" t="s">
+      <c r="J20" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10574,28 +10574,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="99" t="s">
+      <c r="X20" s="167" t="s">
         <v>86</v>
       </c>
-      <c r="Y20" s="101" t="s">
+      <c r="Y20" s="169" t="s">
         <v>87</v>
       </c>
-      <c r="Z20" s="153"/>
-      <c r="AA20" s="125" t="s">
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="153" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="107"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="106"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10627,36 +10627,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="100"/>
-      <c r="Y21" s="102"/>
-      <c r="Z21" s="119"/>
-      <c r="AA21" s="125"/>
+      <c r="X21" s="168"/>
+      <c r="Y21" s="170"/>
+      <c r="Z21" s="94"/>
+      <c r="AA21" s="153"/>
     </row>
     <row r="22" spans="1:27" ht="15.95" customHeight="1">
-      <c r="A22" s="109" t="s">
+      <c r="A22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="122" t="s">
+      <c r="C22" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="93" t="s">
+      <c r="D22" s="123" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="108">
+      <c r="E22" s="104">
         <v>90</v>
       </c>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="111" t="s">
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="108" t="s">
+      <c r="I22" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="107" t="s">
+      <c r="J22" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10698,24 +10698,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="105"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="114">
+      <c r="X22" s="171"/>
+      <c r="Y22" s="130"/>
+      <c r="Z22" s="115">
         <v>46257</v>
       </c>
-      <c r="AA22" s="162"/>
+      <c r="AA22" s="113"/>
     </row>
     <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A23" s="169"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="107"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="106"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10747,40 +10747,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="106"/>
-      <c r="Y23" s="96"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="163"/>
+      <c r="X23" s="110"/>
+      <c r="Y23" s="131"/>
+      <c r="Z23" s="116"/>
+      <c r="AA23" s="114"/>
     </row>
     <row r="24" spans="1:27" ht="17.45" customHeight="1">
-      <c r="A24" s="143" t="s">
+      <c r="A24" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="93" t="s">
+      <c r="B24" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="122" t="s">
+      <c r="C24" s="124" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="90" t="s">
+      <c r="D24" s="105" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="108" t="s">
+      <c r="E24" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="108" t="s">
+      <c r="F24" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="108" t="s">
+      <c r="G24" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H24" s="111" t="s">
+      <c r="H24" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="108" t="s">
+      <c r="I24" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="120" t="s">
+      <c r="J24" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10814,24 +10814,24 @@
         <v>96</v>
       </c>
       <c r="W24" s="39"/>
-      <c r="X24" s="137"/>
-      <c r="Y24" s="152"/>
-      <c r="Z24" s="119"/>
-      <c r="AA24" s="123" t="s">
+      <c r="X24" s="109"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="94"/>
+      <c r="AA24" s="117" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1">
-      <c r="A25" s="168"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="120"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="102"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
@@ -10867,34 +10867,34 @@
         <v>96</v>
       </c>
       <c r="W25" s="57"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="113"/>
-      <c r="Z25" s="153"/>
-      <c r="AA25" s="124"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="101"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="118"/>
     </row>
     <row r="26" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A26" s="168"/>
-      <c r="B26" s="91" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="125" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="161" t="s">
+      <c r="C26" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="90" t="s">
+      <c r="D26" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="108">
+      <c r="E26" s="104">
         <v>34</v>
       </c>
-      <c r="F26" s="159"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="111" t="s">
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="108" t="s">
+      <c r="I26" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="107" t="s">
+      <c r="J26" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10928,24 +10928,24 @@
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="94"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="123" t="s">
+      <c r="X26" s="111"/>
+      <c r="Y26" s="131"/>
+      <c r="Z26" s="116"/>
+      <c r="AA26" s="117" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A27" s="168"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="161"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="159"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="107"/>
+      <c r="A27" s="91"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="106"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10977,34 +10977,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="94"/>
-      <c r="Y27" s="96"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="124"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="131"/>
+      <c r="Z27" s="116"/>
+      <c r="AA27" s="118"/>
     </row>
     <row r="28" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A28" s="168"/>
-      <c r="B28" s="90" t="s">
+      <c r="A28" s="91"/>
+      <c r="B28" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C28" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="90" t="s">
+      <c r="D28" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="108" t="s">
+      <c r="E28" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="111" t="s">
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="108" t="s">
+      <c r="I28" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="107" t="s">
+      <c r="J28" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11038,26 +11038,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="103" t="s">
+      <c r="X28" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="Y28" s="97"/>
-      <c r="Z28" s="119"/>
-      <c r="AA28" s="128" t="s">
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="94"/>
+      <c r="AA28" s="154" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1">
-      <c r="A29" s="168"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="107"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="106"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11089,32 +11089,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="153"/>
-      <c r="AA29" s="129"/>
+      <c r="X29" s="160"/>
+      <c r="Y29" s="97"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="155"/>
     </row>
     <row r="30" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A30" s="168"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="93" t="s">
+      <c r="A30" s="91"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="90" t="s">
+      <c r="D30" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="108" t="s">
+      <c r="E30" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="111" t="s">
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="108" t="s">
+      <c r="I30" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="107" t="s">
+      <c r="J30" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11148,22 +11148,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="103"/>
-      <c r="Y30" s="152"/>
-      <c r="Z30" s="119"/>
-      <c r="AA30" s="166"/>
+      <c r="X30" s="159"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="94"/>
+      <c r="AA30" s="107"/>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="168"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="107"/>
+      <c r="A31" s="91"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="106"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11195,34 +11195,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="113"/>
-      <c r="Z31" s="153"/>
-      <c r="AA31" s="167"/>
+      <c r="X31" s="160"/>
+      <c r="Y31" s="101"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="108"/>
     </row>
     <row r="32" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A32" s="168"/>
-      <c r="B32" s="93" t="s">
+      <c r="A32" s="91"/>
+      <c r="B32" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="122" t="s">
+      <c r="C32" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="90" t="s">
+      <c r="D32" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="108" t="s">
+      <c r="E32" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="111" t="s">
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="108" t="s">
+      <c r="I32" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J32" s="107" t="s">
+      <c r="J32" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11256,28 +11256,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="170" t="s">
+      <c r="X32" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="Y32" s="97" t="s">
+      <c r="Y32" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="Z32" s="119"/>
-      <c r="AA32" s="123" t="s">
+      <c r="Z32" s="94"/>
+      <c r="AA32" s="117" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A33" s="168"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="122"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="107"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="106"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11309,36 +11309,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="171"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="153"/>
-      <c r="AA33" s="124"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="97"/>
+      <c r="Z33" s="95"/>
+      <c r="AA33" s="118"/>
     </row>
     <row r="34" spans="1:29">
-      <c r="A34" s="109" t="s">
+      <c r="A34" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="93" t="s">
+      <c r="C34" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="90" t="s">
+      <c r="D34" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="108">
+      <c r="E34" s="104">
         <v>90</v>
       </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="111" t="s">
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="108" t="s">
+      <c r="I34" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="120" t="s">
+      <c r="J34" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11364,24 +11364,24 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="94"/>
-      <c r="Y34" s="96"/>
-      <c r="Z34" s="115"/>
-      <c r="AA34" s="123" t="s">
+      <c r="X34" s="111"/>
+      <c r="Y34" s="131"/>
+      <c r="Z34" s="116"/>
+      <c r="AA34" s="117" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:29">
-      <c r="A35" s="109"/>
-      <c r="B35" s="148"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="108"/>
-      <c r="J35" s="120"/>
+      <c r="A35" s="92"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="102"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
@@ -11413,34 +11413,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="115"/>
-      <c r="AA35" s="124"/>
+      <c r="X35" s="111"/>
+      <c r="Y35" s="131"/>
+      <c r="Z35" s="116"/>
+      <c r="AA35" s="118"/>
     </row>
     <row r="36" spans="1:29">
-      <c r="A36" s="109"/>
-      <c r="B36" s="148" t="s">
+      <c r="A36" s="92"/>
+      <c r="B36" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="93" t="s">
+      <c r="C36" s="123" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="90" t="s">
+      <c r="D36" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="108">
+      <c r="E36" s="104">
         <v>83</v>
       </c>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="111" t="s">
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="108" t="s">
+      <c r="I36" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="121" t="s">
+      <c r="J36" s="161" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11462,28 +11462,28 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="94" t="s">
+      <c r="X36" s="111" t="s">
         <v>113</v>
       </c>
-      <c r="Y36" s="95" t="s">
+      <c r="Y36" s="130" t="s">
         <v>114</v>
       </c>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="123" t="s">
+      <c r="Z36" s="116"/>
+      <c r="AA36" s="117" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:29">
-      <c r="A37" s="109"/>
-      <c r="B37" s="148"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="108"/>
-      <c r="J37" s="121"/>
+      <c r="A37" s="92"/>
+      <c r="B37" s="144"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="161"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
@@ -11513,45 +11513,45 @@
       <c r="U37" s="58"/>
       <c r="V37" s="58"/>
       <c r="W37" s="59"/>
-      <c r="X37" s="137"/>
-      <c r="Y37" s="97"/>
-      <c r="Z37" s="119"/>
-      <c r="AA37" s="125"/>
+      <c r="X37" s="109"/>
+      <c r="Y37" s="96"/>
+      <c r="Z37" s="94"/>
+      <c r="AA37" s="153"/>
     </row>
     <row r="38" spans="1:29" s="5" customFormat="1">
-      <c r="A38" s="138"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="138"/>
-      <c r="N38" s="138"/>
-      <c r="O38" s="138"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="139"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="139"/>
-      <c r="T38" s="139"/>
-      <c r="U38" s="139"/>
-      <c r="V38" s="139"/>
-      <c r="W38" s="139"/>
-      <c r="X38" s="139"/>
-      <c r="Y38" s="139"/>
-      <c r="Z38" s="139"/>
-      <c r="AA38" s="139"/>
+      <c r="A38" s="147"/>
+      <c r="B38" s="147"/>
+      <c r="C38" s="147"/>
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="147"/>
+      <c r="O38" s="147"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="148"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148"/>
+      <c r="T38" s="148"/>
+      <c r="U38" s="148"/>
+      <c r="V38" s="148"/>
+      <c r="W38" s="148"/>
+      <c r="X38" s="148"/>
+      <c r="Y38" s="148"/>
+      <c r="Z38" s="148"/>
+      <c r="AA38" s="148"/>
     </row>
     <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
-      <c r="A39" s="141" t="s">
+      <c r="A39" s="149" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="141"/>
+      <c r="B39" s="149"/>
       <c r="C39" s="60"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11662,34 +11662,34 @@
       </c>
     </row>
     <row r="41" spans="1:29">
-      <c r="A41" s="142" t="s">
+      <c r="A41" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="145" t="s">
+      <c r="B41" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C41" s="152" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="147" t="s">
+      <c r="D41" s="143" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="140" t="s">
+      <c r="E41" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="F41" s="140" t="s">
+      <c r="F41" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="G41" s="140" t="s">
+      <c r="G41" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="160" t="s">
+      <c r="H41" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="140" t="s">
+      <c r="I41" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="149" t="s">
+      <c r="J41" s="138" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="63" t="s">
@@ -11731,25 +11731,25 @@
       <c r="W41" s="65">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="136"/>
-      <c r="Y41" s="131"/>
-      <c r="Z41" s="131"/>
-      <c r="AA41" s="124" t="s">
+      <c r="X41" s="158"/>
+      <c r="Y41" s="128"/>
+      <c r="Z41" s="128"/>
+      <c r="AA41" s="118" t="s">
         <v>124</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
     <row r="42" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="91"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="108"/>
-      <c r="J42" s="127"/>
+      <c r="A42" s="90"/>
+      <c r="B42" s="125"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="139"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11781,40 +11781,40 @@
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
-      <c r="X42" s="136"/>
-      <c r="Y42" s="131"/>
-      <c r="Z42" s="131"/>
-      <c r="AA42" s="126"/>
+      <c r="X42" s="158"/>
+      <c r="Y42" s="128"/>
+      <c r="Z42" s="128"/>
+      <c r="AA42" s="145"/>
     </row>
     <row r="43" spans="1:29">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="91" t="s">
+      <c r="B43" s="125" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="137" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="90" t="s">
+      <c r="D43" s="105" t="s">
         <v>127</v>
       </c>
-      <c r="E43" s="108" t="s">
+      <c r="E43" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="108" t="s">
+      <c r="F43" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="108" t="s">
+      <c r="G43" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H43" s="111" t="s">
+      <c r="H43" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="108" t="s">
+      <c r="I43" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="120" t="s">
+      <c r="J43" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11836,28 +11836,28 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="130" t="s">
+      <c r="X43" s="146" t="s">
         <v>128</v>
       </c>
-      <c r="Y43" s="132" t="s">
+      <c r="Y43" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="Z43" s="133"/>
-      <c r="AA43" s="134" t="s">
+      <c r="Z43" s="140"/>
+      <c r="AA43" s="156" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:29">
-      <c r="A44" s="144"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="159"/>
-      <c r="J44" s="120"/>
+      <c r="A44" s="136"/>
+      <c r="B44" s="125"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="112"/>
+      <c r="J44" s="102"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
@@ -11893,38 +11893,38 @@
         <v>96</v>
       </c>
       <c r="W44" s="57"/>
-      <c r="X44" s="130"/>
-      <c r="Y44" s="132"/>
-      <c r="Z44" s="133"/>
-      <c r="AA44" s="134"/>
+      <c r="X44" s="146"/>
+      <c r="Y44" s="141"/>
+      <c r="Z44" s="140"/>
+      <c r="AA44" s="156"/>
     </row>
     <row r="45" spans="1:29">
-      <c r="A45" s="144"/>
-      <c r="B45" s="91" t="s">
+      <c r="A45" s="136"/>
+      <c r="B45" s="125" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="92" t="s">
+      <c r="C45" s="137" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="90" t="s">
+      <c r="D45" s="105" t="s">
         <v>132</v>
       </c>
-      <c r="E45" s="108" t="s">
+      <c r="E45" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F45" s="108" t="s">
+      <c r="F45" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="108" t="s">
+      <c r="G45" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="111" t="s">
+      <c r="H45" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="108" t="s">
+      <c r="I45" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="127" t="s">
+      <c r="J45" s="139" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11956,28 +11956,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="130"/>
-      <c r="Y45" s="132" t="s">
+      <c r="X45" s="146"/>
+      <c r="Y45" s="141" t="s">
         <v>133</v>
       </c>
-      <c r="Z45" s="135">
+      <c r="Z45" s="157">
         <v>46188</v>
       </c>
-      <c r="AA45" s="126" t="s">
+      <c r="AA45" s="145" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="16.5" customHeight="1">
-      <c r="A46" s="144"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="127"/>
+      <c r="A46" s="136"/>
+      <c r="B46" s="125"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="139"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12007,38 +12007,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="130"/>
-      <c r="Y46" s="133"/>
-      <c r="Z46" s="133"/>
-      <c r="AA46" s="126"/>
+      <c r="X46" s="146"/>
+      <c r="Y46" s="140"/>
+      <c r="Z46" s="140"/>
+      <c r="AA46" s="145"/>
     </row>
     <row r="47" spans="1:29">
-      <c r="A47" s="144"/>
-      <c r="B47" s="91" t="s">
+      <c r="A47" s="136"/>
+      <c r="B47" s="125" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="92" t="s">
+      <c r="C47" s="137" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="90" t="s">
+      <c r="D47" s="105" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="108" t="s">
+      <c r="E47" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F47" s="108" t="s">
+      <c r="F47" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G47" s="108" t="s">
+      <c r="G47" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H47" s="111" t="s">
+      <c r="H47" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="108" t="s">
+      <c r="I47" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J47" s="127" t="s">
+      <c r="J47" s="139" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12080,24 +12080,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="130"/>
-      <c r="Y47" s="133"/>
-      <c r="Z47" s="133"/>
-      <c r="AA47" s="90" t="s">
+      <c r="X47" s="146"/>
+      <c r="Y47" s="140"/>
+      <c r="Z47" s="140"/>
+      <c r="AA47" s="105" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A48" s="144"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="127"/>
+      <c r="A48" s="136"/>
+      <c r="B48" s="125"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="139"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12130,40 +12130,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="130"/>
-      <c r="Y48" s="133"/>
-      <c r="Z48" s="133"/>
-      <c r="AA48" s="90"/>
+      <c r="X48" s="146"/>
+      <c r="Y48" s="140"/>
+      <c r="Z48" s="140"/>
+      <c r="AA48" s="105"/>
     </row>
     <row r="49" spans="1:27">
-      <c r="A49" s="143" t="s">
+      <c r="A49" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="150" t="s">
+      <c r="B49" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="92" t="s">
+      <c r="C49" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="90" t="s">
+      <c r="D49" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="E49" s="108">
+      <c r="E49" s="104">
         <v>74</v>
       </c>
-      <c r="F49" s="108" t="s">
+      <c r="F49" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G49" s="108" t="s">
+      <c r="G49" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H49" s="111" t="s">
+      <c r="H49" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="108" t="s">
+      <c r="I49" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="107" t="s">
+      <c r="J49" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12205,24 +12205,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="130"/>
-      <c r="Y49" s="132"/>
-      <c r="Z49" s="133"/>
-      <c r="AA49" s="126" t="s">
+      <c r="X49" s="146"/>
+      <c r="Y49" s="141"/>
+      <c r="Z49" s="140"/>
+      <c r="AA49" s="145" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:27">
-      <c r="A50" s="143"/>
-      <c r="B50" s="150"/>
-      <c r="C50" s="92"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="108"/>
-      <c r="J50" s="107"/>
+      <c r="A50" s="90"/>
+      <c r="B50" s="142"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="106"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12254,40 +12254,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="76"/>
-      <c r="X50" s="130"/>
-      <c r="Y50" s="132"/>
-      <c r="Z50" s="133"/>
-      <c r="AA50" s="126"/>
+      <c r="X50" s="146"/>
+      <c r="Y50" s="141"/>
+      <c r="Z50" s="140"/>
+      <c r="AA50" s="145"/>
     </row>
     <row r="51" spans="1:27">
-      <c r="A51" s="144" t="s">
+      <c r="A51" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="91" t="s">
+      <c r="B51" s="125" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="92" t="s">
+      <c r="C51" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="90" t="s">
+      <c r="D51" s="105" t="s">
         <v>142</v>
       </c>
-      <c r="E51" s="108">
+      <c r="E51" s="104">
         <v>33.1</v>
       </c>
-      <c r="F51" s="108" t="s">
+      <c r="F51" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="108" t="s">
+      <c r="G51" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H51" s="111" t="s">
+      <c r="H51" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="108" t="s">
+      <c r="I51" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="107" t="s">
+      <c r="J51" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12321,24 +12321,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="130"/>
-      <c r="Y51" s="133"/>
-      <c r="Z51" s="133"/>
-      <c r="AA51" s="93" t="s">
+      <c r="X51" s="146"/>
+      <c r="Y51" s="140"/>
+      <c r="Z51" s="140"/>
+      <c r="AA51" s="123" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="15" thickBot="1">
-      <c r="A52" s="144"/>
-      <c r="B52" s="91"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="107"/>
+      <c r="A52" s="136"/>
+      <c r="B52" s="125"/>
+      <c r="C52" s="137"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="103"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="106"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12370,10 +12370,10 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="130"/>
-      <c r="Y52" s="133"/>
-      <c r="Z52" s="133"/>
-      <c r="AA52" s="93"/>
+      <c r="X52" s="146"/>
+      <c r="Y52" s="140"/>
+      <c r="Z52" s="140"/>
+      <c r="AA52" s="123"/>
     </row>
     <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
     <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
@@ -12384,28 +12384,230 @@
     <row r="66" ht="14.45" customHeight="1"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="Z10:Z11"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AA30:AA31"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="E30:G31"/>
@@ -12430,230 +12632,28 @@
     <mergeCell ref="I36:I37"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="X26:X27"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -12972,6 +12972,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13109,40 +13129,20 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F488CD-71A3-46BB-878D-37FDAEEAEE94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F488CD-71A3-46BB-878D-37FDAEEAEE94}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1569,251 +1569,251 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9573,10 +9573,10 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
-      <c r="A3" s="162" t="s">
+      <c r="A3" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="162"/>
+      <c r="B3" s="110"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9597,36 +9597,36 @@
       <c r="AA3" s="14"/>
     </row>
     <row r="4" spans="1:27" s="5" customFormat="1">
-      <c r="A4" s="163" t="str">
+      <c r="A4" s="112" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="163"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="163"/>
-      <c r="R4" s="163"/>
-      <c r="S4" s="163"/>
-      <c r="T4" s="163"/>
-      <c r="U4" s="163"/>
-      <c r="V4" s="163"/>
-      <c r="W4" s="163"/>
-      <c r="X4" s="163"/>
-      <c r="Y4" s="163"/>
-      <c r="Z4" s="163"/>
-      <c r="AA4" s="163"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
     </row>
     <row r="5" spans="1:27" ht="27" customHeight="1">
       <c r="A5" s="88" t="s">
@@ -9641,11 +9641,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="164" t="s">
+      <c r="E5" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
       <c r="H5" s="89" t="s">
         <v>8</v>
       </c>
@@ -9708,30 +9708,30 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="137" t="s">
+      <c r="C6" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="105" t="s">
+      <c r="D6" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="104">
+      <c r="E6" s="108">
         <v>10</v>
       </c>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="103" t="s">
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="104" t="s">
+      <c r="I6" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="106" t="s">
+      <c r="J6" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9773,24 +9773,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="101"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="117" t="s">
+      <c r="X6" s="106"/>
+      <c r="Y6" s="113"/>
+      <c r="Z6" s="113"/>
+      <c r="AA6" s="123" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="92"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="106"/>
+      <c r="A7" s="109"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="107"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9826,34 +9826,34 @@
       <c r="W7" s="52">
         <v>0.06</v>
       </c>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="118"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
+      <c r="AA7" s="124"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="92"/>
-      <c r="B8" s="125" t="s">
+      <c r="A8" s="109"/>
+      <c r="B8" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="137" t="s">
+      <c r="C8" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="105" t="s">
+      <c r="D8" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="104">
+      <c r="E8" s="108">
         <v>90</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="103" t="s">
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="106" t="s">
+      <c r="J8" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9885,28 +9885,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="111"/>
-      <c r="Y8" s="130" t="s">
+      <c r="X8" s="94"/>
+      <c r="Y8" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="115">
+      <c r="Z8" s="114">
         <v>46231</v>
       </c>
-      <c r="AA8" s="117" t="s">
+      <c r="AA8" s="123" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="92"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="106"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="107"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9940,34 +9940,34 @@
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="118"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="96"/>
+      <c r="Z9" s="115"/>
+      <c r="AA9" s="124"/>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="92"/>
-      <c r="B10" s="125" t="s">
+      <c r="A10" s="109"/>
+      <c r="B10" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="137" t="s">
+      <c r="C10" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="105" t="s">
+      <c r="D10" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="108">
         <v>1</v>
       </c>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="103" t="s">
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="104" t="s">
+      <c r="I10" s="108" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="106" t="s">
+      <c r="J10" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -10001,24 +10001,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="111"/>
-      <c r="Y10" s="119"/>
-      <c r="Z10" s="165"/>
-      <c r="AA10" s="117" t="s">
+      <c r="X10" s="94"/>
+      <c r="Y10" s="164"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="123" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" thickBot="1">
-      <c r="A11" s="92"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="106"/>
+      <c r="A11" s="109"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="107"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10052,36 +10052,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="111"/>
-      <c r="Y11" s="120"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="118"/>
+      <c r="X11" s="94"/>
+      <c r="Y11" s="165"/>
+      <c r="Z11" s="118"/>
+      <c r="AA11" s="124"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="105" t="s">
+      <c r="D12" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="104">
+      <c r="E12" s="108">
         <v>84</v>
       </c>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="103" t="s">
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="104" t="s">
+      <c r="I12" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="106" t="s">
+      <c r="J12" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10123,24 +10123,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="129"/>
-      <c r="Y12" s="130"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="117" t="s">
+      <c r="X12" s="154"/>
+      <c r="Y12" s="95"/>
+      <c r="Z12" s="96"/>
+      <c r="AA12" s="123" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="92"/>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="106"/>
+      <c r="A13" s="109"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="107"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10172,34 +10172,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="129"/>
-      <c r="Y13" s="131"/>
-      <c r="Z13" s="131"/>
-      <c r="AA13" s="118"/>
+      <c r="X13" s="154"/>
+      <c r="Y13" s="96"/>
+      <c r="Z13" s="96"/>
+      <c r="AA13" s="124"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="92"/>
-      <c r="B14" s="123" t="s">
+      <c r="A14" s="109"/>
+      <c r="B14" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="C14" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="105" t="s">
+      <c r="D14" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="104">
+      <c r="E14" s="108">
         <v>54.6</v>
       </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="103" t="s">
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="104" t="s">
+      <c r="I14" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="106" t="s">
+      <c r="J14" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10233,26 +10233,26 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="109" t="s">
+      <c r="X14" s="137" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="100" t="s">
+      <c r="Y14" s="152" t="s">
         <v>72</v>
       </c>
-      <c r="Z14" s="100"/>
-      <c r="AA14" s="127"/>
+      <c r="Z14" s="152"/>
+      <c r="AA14" s="151"/>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1">
-      <c r="A15" s="92"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="106"/>
+      <c r="A15" s="109"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="107"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10284,36 +10284,36 @@
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-      <c r="AA15" s="128"/>
+      <c r="X15" s="106"/>
+      <c r="Y15" s="113"/>
+      <c r="Z15" s="113"/>
+      <c r="AA15" s="131"/>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="C16" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="105" t="s">
+      <c r="D16" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="104" t="s">
+      <c r="E16" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="103" t="s">
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="104" t="s">
+      <c r="I16" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10347,28 +10347,28 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="111" t="s">
+      <c r="X16" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="Y16" s="130" t="s">
+      <c r="Y16" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="Z16" s="116"/>
-      <c r="AA16" s="117" t="s">
+      <c r="Z16" s="115"/>
+      <c r="AA16" s="123" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="92"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="106"/>
+      <c r="A17" s="109"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="107"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10400,34 +10400,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="111"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="116"/>
-      <c r="AA17" s="118"/>
+      <c r="X17" s="94"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="115"/>
+      <c r="AA17" s="124"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="92"/>
-      <c r="B18" s="123" t="s">
+      <c r="A18" s="109"/>
+      <c r="B18" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="123" t="s">
+      <c r="C18" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="123" t="s">
+      <c r="D18" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="104" t="s">
+      <c r="E18" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="103" t="s">
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="104" t="s">
+      <c r="I18" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="106" t="s">
+      <c r="J18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10462,26 +10462,26 @@
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="135" t="s">
+      <c r="X18" s="158" t="s">
         <v>83</v>
       </c>
-      <c r="Y18" s="135"/>
-      <c r="Z18" s="132">
+      <c r="Y18" s="158"/>
+      <c r="Z18" s="155">
         <v>46108</v>
       </c>
-      <c r="AA18" s="134"/>
+      <c r="AA18" s="157"/>
     </row>
     <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
-      <c r="A19" s="92"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="106"/>
+      <c r="A19" s="109"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="107"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
@@ -10513,34 +10513,34 @@
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="50"/>
-      <c r="X19" s="135"/>
-      <c r="Y19" s="135"/>
-      <c r="Z19" s="133"/>
-      <c r="AA19" s="134"/>
+      <c r="X19" s="158"/>
+      <c r="Y19" s="158"/>
+      <c r="Z19" s="156"/>
+      <c r="AA19" s="157"/>
     </row>
     <row r="20" spans="1:27" ht="21" customHeight="1">
-      <c r="A20" s="92"/>
-      <c r="B20" s="123" t="s">
+      <c r="A20" s="109"/>
+      <c r="B20" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D20" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="104" t="s">
+      <c r="E20" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="103" t="s">
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="104" t="s">
+      <c r="I20" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="106" t="s">
+      <c r="J20" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10574,28 +10574,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="167" t="s">
+      <c r="X20" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="Y20" s="169" t="s">
+      <c r="Y20" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="153" t="s">
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="125" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A21" s="92"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="106"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="107"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10627,36 +10627,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="168"/>
-      <c r="Y21" s="170"/>
-      <c r="Z21" s="94"/>
-      <c r="AA21" s="153"/>
+      <c r="X21" s="100"/>
+      <c r="Y21" s="102"/>
+      <c r="Z21" s="119"/>
+      <c r="AA21" s="125"/>
     </row>
     <row r="22" spans="1:27" ht="15.95" customHeight="1">
-      <c r="A22" s="92" t="s">
+      <c r="A22" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="124" t="s">
+      <c r="C22" s="122" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="93" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="104">
+      <c r="E22" s="108">
         <v>90</v>
       </c>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="103" t="s">
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="104" t="s">
+      <c r="I22" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="106" t="s">
+      <c r="J22" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10698,24 +10698,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="171"/>
-      <c r="Y22" s="130"/>
-      <c r="Z22" s="115">
+      <c r="X22" s="105"/>
+      <c r="Y22" s="95"/>
+      <c r="Z22" s="114">
         <v>46257</v>
       </c>
-      <c r="AA22" s="113"/>
+      <c r="AA22" s="162"/>
     </row>
     <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A23" s="93"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="106"/>
+      <c r="A23" s="169"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="107"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10747,40 +10747,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="131"/>
-      <c r="Z23" s="116"/>
-      <c r="AA23" s="114"/>
+      <c r="X23" s="106"/>
+      <c r="Y23" s="96"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="163"/>
     </row>
     <row r="24" spans="1:27" ht="17.45" customHeight="1">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="124" t="s">
+      <c r="C24" s="122" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="105" t="s">
+      <c r="D24" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="104" t="s">
+      <c r="E24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="104" t="s">
+      <c r="F24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="104" t="s">
+      <c r="G24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H24" s="103" t="s">
+      <c r="H24" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="104" t="s">
+      <c r="I24" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="102" t="s">
+      <c r="J24" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10814,24 +10814,24 @@
         <v>96</v>
       </c>
       <c r="W24" s="39"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="100"/>
-      <c r="Z24" s="94"/>
-      <c r="AA24" s="117" t="s">
+      <c r="X24" s="137"/>
+      <c r="Y24" s="152"/>
+      <c r="Z24" s="119"/>
+      <c r="AA24" s="123" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1">
-      <c r="A25" s="91"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="102"/>
+      <c r="A25" s="168"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="120"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
@@ -10867,34 +10867,34 @@
         <v>96</v>
       </c>
       <c r="W25" s="57"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="118"/>
+      <c r="X25" s="106"/>
+      <c r="Y25" s="113"/>
+      <c r="Z25" s="153"/>
+      <c r="AA25" s="124"/>
     </row>
     <row r="26" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A26" s="91"/>
-      <c r="B26" s="125" t="s">
+      <c r="A26" s="168"/>
+      <c r="B26" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="126" t="s">
+      <c r="C26" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="104">
+      <c r="E26" s="108">
         <v>34</v>
       </c>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="103" t="s">
+      <c r="F26" s="159"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="104" t="s">
+      <c r="I26" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="106" t="s">
+      <c r="J26" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10928,24 +10928,24 @@
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="131"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="117" t="s">
+      <c r="X26" s="94"/>
+      <c r="Y26" s="96"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="123" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A27" s="91"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="106"/>
+      <c r="A27" s="168"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="159"/>
+      <c r="G27" s="159"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="107"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10977,34 +10977,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="131"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="118"/>
+      <c r="X27" s="94"/>
+      <c r="Y27" s="96"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="124"/>
     </row>
     <row r="28" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A28" s="91"/>
-      <c r="B28" s="105" t="s">
+      <c r="A28" s="168"/>
+      <c r="B28" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="123" t="s">
+      <c r="C28" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="105" t="s">
+      <c r="D28" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="104" t="s">
+      <c r="E28" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="103" t="s">
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="106" t="s">
+      <c r="J28" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11038,26 +11038,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="159" t="s">
+      <c r="X28" s="103" t="s">
         <v>103</v>
       </c>
-      <c r="Y28" s="96"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="154" t="s">
+      <c r="Y28" s="97"/>
+      <c r="Z28" s="119"/>
+      <c r="AA28" s="128" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1">
-      <c r="A29" s="91"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="106"/>
+      <c r="A29" s="168"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="107"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11089,32 +11089,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="160"/>
-      <c r="Y29" s="97"/>
-      <c r="Z29" s="95"/>
-      <c r="AA29" s="155"/>
+      <c r="X29" s="104"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="153"/>
+      <c r="AA29" s="129"/>
     </row>
     <row r="30" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A30" s="91"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="123" t="s">
+      <c r="A30" s="168"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="105" t="s">
+      <c r="D30" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="104" t="s">
+      <c r="E30" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="103" t="s">
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="104" t="s">
+      <c r="I30" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11148,22 +11148,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="159"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="94"/>
-      <c r="AA30" s="107"/>
+      <c r="X30" s="103"/>
+      <c r="Y30" s="152"/>
+      <c r="Z30" s="119"/>
+      <c r="AA30" s="166"/>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="91"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="106"/>
+      <c r="A31" s="168"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="107"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11195,34 +11195,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="160"/>
-      <c r="Y31" s="101"/>
-      <c r="Z31" s="95"/>
-      <c r="AA31" s="108"/>
+      <c r="X31" s="104"/>
+      <c r="Y31" s="113"/>
+      <c r="Z31" s="153"/>
+      <c r="AA31" s="167"/>
     </row>
     <row r="32" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A32" s="91"/>
-      <c r="B32" s="123" t="s">
+      <c r="A32" s="168"/>
+      <c r="B32" s="93" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="124" t="s">
+      <c r="C32" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="105" t="s">
+      <c r="D32" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="104" t="s">
+      <c r="E32" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="103" t="s">
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="104" t="s">
+      <c r="I32" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J32" s="106" t="s">
+      <c r="J32" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11256,28 +11256,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="98" t="s">
+      <c r="X32" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="Y32" s="96" t="s">
+      <c r="Y32" s="97" t="s">
         <v>109</v>
       </c>
-      <c r="Z32" s="94"/>
-      <c r="AA32" s="117" t="s">
+      <c r="Z32" s="119"/>
+      <c r="AA32" s="123" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A33" s="91"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="106"/>
+      <c r="A33" s="168"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="107"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11309,36 +11309,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="97"/>
-      <c r="Z33" s="95"/>
-      <c r="AA33" s="118"/>
+      <c r="X33" s="171"/>
+      <c r="Y33" s="98"/>
+      <c r="Z33" s="153"/>
+      <c r="AA33" s="124"/>
     </row>
     <row r="34" spans="1:29">
-      <c r="A34" s="92" t="s">
+      <c r="A34" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="144" t="s">
+      <c r="B34" s="148" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="123" t="s">
+      <c r="C34" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="105" t="s">
+      <c r="D34" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="104">
+      <c r="E34" s="108">
         <v>90</v>
       </c>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="103" t="s">
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="104" t="s">
+      <c r="I34" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="102" t="s">
+      <c r="J34" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11364,24 +11364,24 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="111"/>
-      <c r="Y34" s="131"/>
-      <c r="Z34" s="116"/>
-      <c r="AA34" s="117" t="s">
+      <c r="X34" s="94"/>
+      <c r="Y34" s="96"/>
+      <c r="Z34" s="115"/>
+      <c r="AA34" s="123" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:29">
-      <c r="A35" s="92"/>
-      <c r="B35" s="144"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="102"/>
+      <c r="A35" s="109"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="120"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
@@ -11413,34 +11413,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="131"/>
-      <c r="Z35" s="116"/>
-      <c r="AA35" s="118"/>
+      <c r="X35" s="94"/>
+      <c r="Y35" s="96"/>
+      <c r="Z35" s="115"/>
+      <c r="AA35" s="124"/>
     </row>
     <row r="36" spans="1:29">
-      <c r="A36" s="92"/>
-      <c r="B36" s="144" t="s">
+      <c r="A36" s="109"/>
+      <c r="B36" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="123" t="s">
+      <c r="C36" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="105" t="s">
+      <c r="D36" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="104">
+      <c r="E36" s="108">
         <v>83</v>
       </c>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="103" t="s">
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="104" t="s">
+      <c r="I36" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="161" t="s">
+      <c r="J36" s="121" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11462,28 +11462,28 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="111" t="s">
+      <c r="X36" s="94" t="s">
         <v>113</v>
       </c>
-      <c r="Y36" s="130" t="s">
+      <c r="Y36" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="117" t="s">
+      <c r="Z36" s="115"/>
+      <c r="AA36" s="123" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:29">
-      <c r="A37" s="92"/>
-      <c r="B37" s="144"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="161"/>
+      <c r="A37" s="109"/>
+      <c r="B37" s="148"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="121"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
@@ -11513,45 +11513,45 @@
       <c r="U37" s="58"/>
       <c r="V37" s="58"/>
       <c r="W37" s="59"/>
-      <c r="X37" s="109"/>
-      <c r="Y37" s="96"/>
-      <c r="Z37" s="94"/>
-      <c r="AA37" s="153"/>
+      <c r="X37" s="137"/>
+      <c r="Y37" s="97"/>
+      <c r="Z37" s="119"/>
+      <c r="AA37" s="125"/>
     </row>
     <row r="38" spans="1:29" s="5" customFormat="1">
-      <c r="A38" s="147"/>
-      <c r="B38" s="147"/>
-      <c r="C38" s="147"/>
-      <c r="D38" s="147"/>
-      <c r="E38" s="147"/>
-      <c r="F38" s="147"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="147"/>
-      <c r="I38" s="147"/>
-      <c r="J38" s="147"/>
-      <c r="K38" s="147"/>
-      <c r="L38" s="147"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="147"/>
-      <c r="O38" s="147"/>
-      <c r="P38" s="148"/>
-      <c r="Q38" s="148"/>
-      <c r="R38" s="148"/>
-      <c r="S38" s="148"/>
-      <c r="T38" s="148"/>
-      <c r="U38" s="148"/>
-      <c r="V38" s="148"/>
-      <c r="W38" s="148"/>
-      <c r="X38" s="148"/>
-      <c r="Y38" s="148"/>
-      <c r="Z38" s="148"/>
-      <c r="AA38" s="148"/>
+      <c r="A38" s="138"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="138"/>
+      <c r="K38" s="138"/>
+      <c r="L38" s="138"/>
+      <c r="M38" s="138"/>
+      <c r="N38" s="138"/>
+      <c r="O38" s="138"/>
+      <c r="P38" s="139"/>
+      <c r="Q38" s="139"/>
+      <c r="R38" s="139"/>
+      <c r="S38" s="139"/>
+      <c r="T38" s="139"/>
+      <c r="U38" s="139"/>
+      <c r="V38" s="139"/>
+      <c r="W38" s="139"/>
+      <c r="X38" s="139"/>
+      <c r="Y38" s="139"/>
+      <c r="Z38" s="139"/>
+      <c r="AA38" s="139"/>
     </row>
     <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
-      <c r="A39" s="149" t="s">
+      <c r="A39" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="149"/>
+      <c r="B39" s="141"/>
       <c r="C39" s="60"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11662,34 +11662,34 @@
       </c>
     </row>
     <row r="41" spans="1:29">
-      <c r="A41" s="150" t="s">
+      <c r="A41" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="151" t="s">
+      <c r="B41" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="152" t="s">
+      <c r="C41" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="143" t="s">
+      <c r="D41" s="147" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="121" t="s">
+      <c r="E41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="F41" s="121" t="s">
+      <c r="F41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="G41" s="121" t="s">
+      <c r="G41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="122" t="s">
+      <c r="H41" s="160" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="121" t="s">
+      <c r="I41" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="138" t="s">
+      <c r="J41" s="149" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="63" t="s">
@@ -11731,25 +11731,25 @@
       <c r="W41" s="65">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="158"/>
-      <c r="Y41" s="128"/>
-      <c r="Z41" s="128"/>
-      <c r="AA41" s="118" t="s">
+      <c r="X41" s="136"/>
+      <c r="Y41" s="131"/>
+      <c r="Z41" s="131"/>
+      <c r="AA41" s="124" t="s">
         <v>124</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
     <row r="42" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A42" s="90"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="137"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="139"/>
+      <c r="A42" s="143"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="92"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="108"/>
+      <c r="J42" s="127"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11781,40 +11781,40 @@
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
-      <c r="X42" s="158"/>
-      <c r="Y42" s="128"/>
-      <c r="Z42" s="128"/>
-      <c r="AA42" s="145"/>
+      <c r="X42" s="136"/>
+      <c r="Y42" s="131"/>
+      <c r="Z42" s="131"/>
+      <c r="AA42" s="126"/>
     </row>
     <row r="43" spans="1:29">
-      <c r="A43" s="136" t="s">
+      <c r="A43" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="125" t="s">
+      <c r="B43" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="137" t="s">
+      <c r="C43" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="105" t="s">
+      <c r="D43" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="E43" s="104" t="s">
+      <c r="E43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="104" t="s">
+      <c r="F43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="104" t="s">
+      <c r="G43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H43" s="103" t="s">
+      <c r="H43" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="104" t="s">
+      <c r="I43" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="102" t="s">
+      <c r="J43" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11836,28 +11836,28 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="146" t="s">
+      <c r="X43" s="130" t="s">
         <v>128</v>
       </c>
-      <c r="Y43" s="141" t="s">
+      <c r="Y43" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="Z43" s="140"/>
-      <c r="AA43" s="156" t="s">
+      <c r="Z43" s="133"/>
+      <c r="AA43" s="134" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:29">
-      <c r="A44" s="136"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="112"/>
-      <c r="J44" s="102"/>
+      <c r="A44" s="144"/>
+      <c r="B44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
+      <c r="H44" s="111"/>
+      <c r="I44" s="159"/>
+      <c r="J44" s="120"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
@@ -11893,38 +11893,38 @@
         <v>96</v>
       </c>
       <c r="W44" s="57"/>
-      <c r="X44" s="146"/>
-      <c r="Y44" s="141"/>
-      <c r="Z44" s="140"/>
-      <c r="AA44" s="156"/>
+      <c r="X44" s="130"/>
+      <c r="Y44" s="132"/>
+      <c r="Z44" s="133"/>
+      <c r="AA44" s="134"/>
     </row>
     <row r="45" spans="1:29">
-      <c r="A45" s="136"/>
-      <c r="B45" s="125" t="s">
+      <c r="A45" s="144"/>
+      <c r="B45" s="91" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="137" t="s">
+      <c r="C45" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="105" t="s">
+      <c r="D45" s="90" t="s">
         <v>132</v>
       </c>
-      <c r="E45" s="104" t="s">
+      <c r="E45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F45" s="104" t="s">
+      <c r="F45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="104" t="s">
+      <c r="G45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="103" t="s">
+      <c r="H45" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="104" t="s">
+      <c r="I45" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="139" t="s">
+      <c r="J45" s="127" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11956,28 +11956,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="146"/>
-      <c r="Y45" s="141" t="s">
+      <c r="X45" s="130"/>
+      <c r="Y45" s="132" t="s">
         <v>133</v>
       </c>
-      <c r="Z45" s="157">
+      <c r="Z45" s="135">
         <v>46188</v>
       </c>
-      <c r="AA45" s="145" t="s">
+      <c r="AA45" s="126" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="16.5" customHeight="1">
-      <c r="A46" s="136"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="137"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="139"/>
+      <c r="A46" s="144"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="127"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12007,38 +12007,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="146"/>
-      <c r="Y46" s="140"/>
-      <c r="Z46" s="140"/>
-      <c r="AA46" s="145"/>
+      <c r="X46" s="130"/>
+      <c r="Y46" s="133"/>
+      <c r="Z46" s="133"/>
+      <c r="AA46" s="126"/>
     </row>
     <row r="47" spans="1:29">
-      <c r="A47" s="136"/>
-      <c r="B47" s="125" t="s">
+      <c r="A47" s="144"/>
+      <c r="B47" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="137" t="s">
+      <c r="C47" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="105" t="s">
+      <c r="D47" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="104" t="s">
+      <c r="E47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F47" s="104" t="s">
+      <c r="F47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G47" s="104" t="s">
+      <c r="G47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H47" s="103" t="s">
+      <c r="H47" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="104" t="s">
+      <c r="I47" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J47" s="139" t="s">
+      <c r="J47" s="127" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12080,24 +12080,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="146"/>
-      <c r="Y47" s="140"/>
-      <c r="Z47" s="140"/>
-      <c r="AA47" s="105" t="s">
+      <c r="X47" s="130"/>
+      <c r="Y47" s="133"/>
+      <c r="Z47" s="133"/>
+      <c r="AA47" s="90" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A48" s="136"/>
-      <c r="B48" s="125"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="139"/>
+      <c r="A48" s="144"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108"/>
+      <c r="H48" s="111"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="127"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12130,40 +12130,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="146"/>
-      <c r="Y48" s="140"/>
-      <c r="Z48" s="140"/>
-      <c r="AA48" s="105"/>
+      <c r="X48" s="130"/>
+      <c r="Y48" s="133"/>
+      <c r="Z48" s="133"/>
+      <c r="AA48" s="90"/>
     </row>
     <row r="49" spans="1:27">
-      <c r="A49" s="90" t="s">
+      <c r="A49" s="143" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="142" t="s">
+      <c r="B49" s="150" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="137" t="s">
+      <c r="C49" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="105" t="s">
+      <c r="D49" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="E49" s="104">
+      <c r="E49" s="108">
         <v>74</v>
       </c>
-      <c r="F49" s="104" t="s">
+      <c r="F49" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G49" s="104" t="s">
+      <c r="G49" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H49" s="103" t="s">
+      <c r="H49" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="104" t="s">
+      <c r="I49" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="106" t="s">
+      <c r="J49" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12205,24 +12205,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="146"/>
-      <c r="Y49" s="141"/>
-      <c r="Z49" s="140"/>
-      <c r="AA49" s="145" t="s">
+      <c r="X49" s="130"/>
+      <c r="Y49" s="132"/>
+      <c r="Z49" s="133"/>
+      <c r="AA49" s="126" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:27">
-      <c r="A50" s="90"/>
-      <c r="B50" s="142"/>
-      <c r="C50" s="137"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="106"/>
+      <c r="A50" s="143"/>
+      <c r="B50" s="150"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="111"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="107"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12254,40 +12254,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="76"/>
-      <c r="X50" s="146"/>
-      <c r="Y50" s="141"/>
-      <c r="Z50" s="140"/>
-      <c r="AA50" s="145"/>
+      <c r="X50" s="130"/>
+      <c r="Y50" s="132"/>
+      <c r="Z50" s="133"/>
+      <c r="AA50" s="126"/>
     </row>
     <row r="51" spans="1:27">
-      <c r="A51" s="136" t="s">
+      <c r="A51" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="125" t="s">
+      <c r="B51" s="91" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="137" t="s">
+      <c r="C51" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="105" t="s">
+      <c r="D51" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="E51" s="104">
+      <c r="E51" s="108">
         <v>33.1</v>
       </c>
-      <c r="F51" s="104" t="s">
+      <c r="F51" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="104" t="s">
+      <c r="G51" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H51" s="103" t="s">
+      <c r="H51" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="104" t="s">
+      <c r="I51" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="106" t="s">
+      <c r="J51" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12321,24 +12321,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="146"/>
-      <c r="Y51" s="140"/>
-      <c r="Z51" s="140"/>
-      <c r="AA51" s="123" t="s">
+      <c r="X51" s="130"/>
+      <c r="Y51" s="133"/>
+      <c r="Z51" s="133"/>
+      <c r="AA51" s="93" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="15" thickBot="1">
-      <c r="A52" s="136"/>
-      <c r="B52" s="125"/>
-      <c r="C52" s="137"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="106"/>
+      <c r="A52" s="144"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="108"/>
+      <c r="J52" s="107"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12370,10 +12370,10 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="146"/>
-      <c r="Y52" s="140"/>
-      <c r="Z52" s="140"/>
-      <c r="AA52" s="123"/>
+      <c r="X52" s="130"/>
+      <c r="Y52" s="133"/>
+      <c r="Z52" s="133"/>
+      <c r="AA52" s="93"/>
     </row>
     <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
     <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
@@ -12384,27 +12384,231 @@
     <row r="66" ht="14.45" customHeight="1"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="E32:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G37"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="X26:X27"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A3:B3"/>
@@ -12429,231 +12633,27 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="J8:J9"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="AA30:AA31"/>
-    <mergeCell ref="X24:X25"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G37"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="X26:X27"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -12972,26 +12972,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13129,20 +13109,40 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F488CD-71A3-46BB-878D-37FDAEEAEE94}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F488CD-71A3-46BB-878D-37FDAEEAEE94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13130,7 +13130,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F488CD-71A3-46BB-878D-37FDAEEAEE94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{787F3183-CB79-425C-95EF-899D8AC4EA34}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3207" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E097B0B-CC12-443A-81FF-F45BC921F7B0}"/>
+  <xr:revisionPtr revIDLastSave="3208" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46D14F69-5A49-4F9E-8EA9-3814FCDEEEBE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" state="hidden" r:id="rId1"/>
@@ -834,7 +834,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1569,32 +1569,236 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1608,212 +1812,8 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1862,35 +1862,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1911,35 +1883,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2002,6 +1946,83 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2024,6 +2045,111 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2072,20 +2198,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2094,118 +2206,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2234,6 +2234,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2283,13 +2290,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2447,7 +2447,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>712470</xdr:colOff>
+      <xdr:colOff>715645</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>18415</xdr:rowOff>
     </xdr:to>
@@ -5188,29 +5188,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AD843-49A7-417E-9F24-86908363EFA2}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.5703125" customWidth="1"/>
-    <col min="5" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="55.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.54296875" customWidth="1"/>
+    <col min="5" max="6" width="10.453125" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.95">
+    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5364,7 +5364,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5450,7 +5450,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5536,7 +5536,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5622,7 +5622,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5708,7 +5708,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5794,7 +5794,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5880,7 +5880,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5966,12 +5966,12 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6129,7 +6129,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6219,7 +6219,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6309,7 +6309,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6399,7 +6399,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6489,7 +6489,7 @@
         <v>0.73999999999999966</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6579,12 +6579,12 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6742,7 +6742,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6832,7 +6832,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6905,9 +6905,9 @@
         <f>IF('AOP Critical'!S18="","",'AOP Critical'!S18)</f>
         <v>3.7</v>
       </c>
-      <c r="S25" s="75" t="str">
+      <c r="S25" s="75">
         <f>IF('AOP Critical'!T18="","",'AOP Critical'!T18)</f>
-        <v/>
+        <v>4.5439999999999996</v>
       </c>
       <c r="T25" s="75" t="str">
         <f>IF('AOP Critical'!U18="","",'AOP Critical'!U18)</f>
@@ -6922,7 +6922,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -7012,7 +7012,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7102,7 +7102,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7192,7 +7192,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7282,7 +7282,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7372,12 +7372,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7535,7 +7535,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7625,7 +7625,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7715,7 +7715,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7805,7 +7805,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7895,7 +7895,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7985,7 +7985,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8075,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8165,7 +8165,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8255,7 +8255,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8345,12 +8345,12 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8508,7 +8508,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8598,7 +8598,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8685,7 +8685,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8771,7 +8771,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8861,7 +8861,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8951,7 +8951,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9041,7 +9041,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9131,12 +9131,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -9525,34 +9525,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AC66"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.140625" hidden="1" customWidth="1"/>
-    <col min="17" max="22" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.81640625" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.81640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" customWidth="1"/>
+    <col min="12" max="12" width="5.54296875" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.26953125" customWidth="1"/>
+    <col min="15" max="15" width="7.26953125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.1796875" hidden="1" customWidth="1"/>
+    <col min="17" max="22" width="6.1796875" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="58.85546875" style="20" customWidth="1"/>
-    <col min="25" max="25" width="68.140625" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" customWidth="1"/>
+    <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
+    <col min="25" max="25" width="68.1796875" customWidth="1"/>
+    <col min="26" max="26" width="17.7265625" customWidth="1"/>
     <col min="27" max="27" width="57" style="13" customWidth="1"/>
-    <col min="28" max="46" width="8.5703125" customWidth="1"/>
+    <col min="28" max="46" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9563,7 +9563,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9572,11 +9572,11 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
-      <c r="A3" s="110" t="s">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="110"/>
+      <c r="B3" s="162"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9596,39 +9596,39 @@
       <c r="X3" s="21"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1">
-      <c r="A4" s="112" t="str">
+    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="163" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="163"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="163"/>
+      <c r="K4" s="163"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="163"/>
+      <c r="U4" s="163"/>
+      <c r="V4" s="163"/>
+      <c r="W4" s="163"/>
+      <c r="X4" s="163"/>
+      <c r="Y4" s="163"/>
+      <c r="Z4" s="163"/>
+      <c r="AA4" s="163"/>
     </row>
-    <row r="5" spans="1:27" ht="27" customHeight="1">
+    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="88" t="s">
         <v>0</v>
       </c>
@@ -9641,11 +9641,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="116" t="s">
+      <c r="E5" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="164"/>
       <c r="H5" s="89" t="s">
         <v>8</v>
       </c>
@@ -9707,31 +9707,31 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="109" t="s">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A6" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="108">
+      <c r="E6" s="104">
         <v>10</v>
       </c>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="111" t="s">
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="107" t="s">
+      <c r="J6" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9773,24 +9773,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="106"/>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="123" t="s">
+      <c r="X6" s="110"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="117" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="109"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="107"/>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A7" s="92"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="106"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9826,34 +9826,34 @@
       <c r="W7" s="52">
         <v>0.06</v>
       </c>
-      <c r="X7" s="94"/>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
-      <c r="AA7" s="124"/>
+      <c r="X7" s="111"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="118"/>
     </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="109"/>
-      <c r="B8" s="91" t="s">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A8" s="92"/>
+      <c r="B8" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="108">
+      <c r="E8" s="104">
         <v>90</v>
       </c>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="111" t="s">
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="108" t="s">
+      <c r="I8" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="107" t="s">
+      <c r="J8" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9885,28 +9885,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="95" t="s">
+      <c r="X8" s="111"/>
+      <c r="Y8" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="114">
+      <c r="Z8" s="115">
         <v>46231</v>
       </c>
-      <c r="AA8" s="123" t="s">
+      <c r="AA8" s="117" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="109"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="107"/>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A9" s="92"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="106"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9940,34 +9940,34 @@
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="124"/>
+      <c r="X9" s="111"/>
+      <c r="Y9" s="131"/>
+      <c r="Z9" s="116"/>
+      <c r="AA9" s="118"/>
     </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="109"/>
-      <c r="B10" s="91" t="s">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A10" s="92"/>
+      <c r="B10" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="108">
+      <c r="E10" s="104">
         <v>1</v>
       </c>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="111" t="s">
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="107" t="s">
+      <c r="J10" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -10001,24 +10001,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="94"/>
-      <c r="Y10" s="164"/>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="123" t="s">
+      <c r="X10" s="111"/>
+      <c r="Y10" s="119"/>
+      <c r="Z10" s="165"/>
+      <c r="AA10" s="117" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1">
-      <c r="A11" s="109"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="107"/>
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="92"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="106"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10052,36 +10052,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="94"/>
-      <c r="Y11" s="165"/>
-      <c r="Z11" s="118"/>
-      <c r="AA11" s="124"/>
+      <c r="X11" s="111"/>
+      <c r="Y11" s="120"/>
+      <c r="Z11" s="166"/>
+      <c r="AA11" s="118"/>
     </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="109" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A12" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="108">
+      <c r="E12" s="104">
         <v>84</v>
       </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="111" t="s">
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="108" t="s">
+      <c r="I12" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="107" t="s">
+      <c r="J12" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10123,24 +10123,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="154"/>
-      <c r="Y12" s="95"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="123" t="s">
+      <c r="X12" s="129"/>
+      <c r="Y12" s="130"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="117" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="109"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="107"/>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A13" s="92"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="106"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10172,34 +10172,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="154"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="124"/>
+      <c r="X13" s="129"/>
+      <c r="Y13" s="131"/>
+      <c r="Z13" s="131"/>
+      <c r="AA13" s="118"/>
     </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="109"/>
-      <c r="B14" s="93" t="s">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A14" s="92"/>
+      <c r="B14" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C14" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="108">
+      <c r="E14" s="104">
         <v>54.6</v>
       </c>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="111" t="s">
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="108" t="s">
+      <c r="I14" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="107" t="s">
+      <c r="J14" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10233,26 +10233,26 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="137" t="s">
+      <c r="X14" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="152" t="s">
+      <c r="Y14" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="Z14" s="152"/>
-      <c r="AA14" s="151"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="127"/>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1">
-      <c r="A15" s="109"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="107"/>
+    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="92"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="106"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10284,36 +10284,36 @@
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="106"/>
-      <c r="Y15" s="113"/>
-      <c r="Z15" s="113"/>
-      <c r="AA15" s="131"/>
+      <c r="X15" s="110"/>
+      <c r="Y15" s="101"/>
+      <c r="Z15" s="101"/>
+      <c r="AA15" s="128"/>
     </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="109" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="C16" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="90" t="s">
+      <c r="D16" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="108" t="s">
+      <c r="E16" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="111" t="s">
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="107" t="s">
+      <c r="J16" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10347,28 +10347,28 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="94" t="s">
+      <c r="X16" s="111" t="s">
         <v>77</v>
       </c>
-      <c r="Y16" s="95" t="s">
+      <c r="Y16" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="123" t="s">
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="117" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
-      <c r="A17" s="109"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="107"/>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17" s="92"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="106"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10400,34 +10400,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="94"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="124"/>
+      <c r="X17" s="111"/>
+      <c r="Y17" s="131"/>
+      <c r="Z17" s="116"/>
+      <c r="AA17" s="118"/>
     </row>
-    <row r="18" spans="1:27">
-      <c r="A18" s="109"/>
-      <c r="B18" s="93" t="s">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A18" s="92"/>
+      <c r="B18" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="93" t="s">
+      <c r="D18" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="108" t="s">
+      <c r="E18" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="111" t="s">
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="108" t="s">
+      <c r="I18" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="107" t="s">
+      <c r="J18" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10458,30 +10458,32 @@
       <c r="S18" s="48">
         <v>3.7</v>
       </c>
-      <c r="T18" s="48"/>
+      <c r="T18" s="48">
+        <v>4.5439999999999996</v>
+      </c>
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="158" t="s">
+      <c r="X18" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="Y18" s="158"/>
-      <c r="Z18" s="155">
+      <c r="Y18" s="135"/>
+      <c r="Z18" s="132">
         <v>46108</v>
       </c>
-      <c r="AA18" s="157"/>
+      <c r="AA18" s="134"/>
     </row>
-    <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
-      <c r="A19" s="109"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="107"/>
+    <row r="19" spans="1:27" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="92"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="106"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
@@ -10513,34 +10515,34 @@
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="50"/>
-      <c r="X19" s="158"/>
-      <c r="Y19" s="158"/>
-      <c r="Z19" s="156"/>
-      <c r="AA19" s="157"/>
+      <c r="X19" s="135"/>
+      <c r="Y19" s="135"/>
+      <c r="Z19" s="133"/>
+      <c r="AA19" s="134"/>
     </row>
-    <row r="20" spans="1:27" ht="21" customHeight="1">
-      <c r="A20" s="109"/>
-      <c r="B20" s="93" t="s">
+    <row r="20" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="92"/>
+      <c r="B20" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="90" t="s">
+      <c r="D20" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="108" t="s">
+      <c r="E20" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="108"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="111" t="s">
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="108" t="s">
+      <c r="I20" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="107" t="s">
+      <c r="J20" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10574,28 +10576,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="99" t="s">
+      <c r="X20" s="167" t="s">
         <v>86</v>
       </c>
-      <c r="Y20" s="101" t="s">
+      <c r="Y20" s="169" t="s">
         <v>87</v>
       </c>
-      <c r="Z20" s="153"/>
-      <c r="AA20" s="125" t="s">
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="153" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="107"/>
+    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="92"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="106"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10627,36 +10629,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="100"/>
-      <c r="Y21" s="102"/>
-      <c r="Z21" s="119"/>
-      <c r="AA21" s="125"/>
+      <c r="X21" s="168"/>
+      <c r="Y21" s="170"/>
+      <c r="Z21" s="94"/>
+      <c r="AA21" s="153"/>
     </row>
-    <row r="22" spans="1:27" ht="15.95" customHeight="1">
-      <c r="A22" s="109" t="s">
+    <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="122" t="s">
+      <c r="C22" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="93" t="s">
+      <c r="D22" s="123" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="108">
+      <c r="E22" s="104">
         <v>90</v>
       </c>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="111" t="s">
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="108" t="s">
+      <c r="I22" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="107" t="s">
+      <c r="J22" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10698,24 +10700,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="105"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="114">
+      <c r="X22" s="171"/>
+      <c r="Y22" s="130"/>
+      <c r="Z22" s="115">
         <v>46257</v>
       </c>
-      <c r="AA22" s="162"/>
+      <c r="AA22" s="113"/>
     </row>
-    <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A23" s="169"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="107"/>
+    <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="93"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="106"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10747,40 +10749,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="106"/>
-      <c r="Y23" s="96"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="163"/>
+      <c r="X23" s="110"/>
+      <c r="Y23" s="131"/>
+      <c r="Z23" s="116"/>
+      <c r="AA23" s="114"/>
     </row>
-    <row r="24" spans="1:27" ht="17.45" customHeight="1">
-      <c r="A24" s="143" t="s">
+    <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="93" t="s">
+      <c r="B24" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="122" t="s">
+      <c r="C24" s="124" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="90" t="s">
+      <c r="D24" s="105" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="108" t="s">
+      <c r="E24" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="108" t="s">
+      <c r="F24" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="108" t="s">
+      <c r="G24" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H24" s="111" t="s">
+      <c r="H24" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="108" t="s">
+      <c r="I24" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="120" t="s">
+      <c r="J24" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10814,24 +10816,24 @@
         <v>96</v>
       </c>
       <c r="W24" s="39"/>
-      <c r="X24" s="137"/>
-      <c r="Y24" s="152"/>
-      <c r="Z24" s="119"/>
-      <c r="AA24" s="123" t="s">
+      <c r="X24" s="109"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="94"/>
+      <c r="AA24" s="117" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1">
-      <c r="A25" s="168"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="120"/>
+    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="91"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="102"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
@@ -10867,34 +10869,34 @@
         <v>96</v>
       </c>
       <c r="W25" s="57"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="113"/>
-      <c r="Z25" s="153"/>
-      <c r="AA25" s="124"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="101"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="118"/>
     </row>
-    <row r="26" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A26" s="168"/>
-      <c r="B26" s="91" t="s">
+    <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="91"/>
+      <c r="B26" s="125" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="161" t="s">
+      <c r="C26" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="90" t="s">
+      <c r="D26" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="108">
+      <c r="E26" s="104">
         <v>34</v>
       </c>
-      <c r="F26" s="159"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="111" t="s">
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="108" t="s">
+      <c r="I26" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="107" t="s">
+      <c r="J26" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10928,24 +10930,24 @@
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="94"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="123" t="s">
+      <c r="X26" s="111"/>
+      <c r="Y26" s="131"/>
+      <c r="Z26" s="116"/>
+      <c r="AA26" s="117" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A27" s="168"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="161"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="159"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="107"/>
+    <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="91"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="106"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10977,34 +10979,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="94"/>
-      <c r="Y27" s="96"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="124"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="131"/>
+      <c r="Z27" s="116"/>
+      <c r="AA27" s="118"/>
     </row>
-    <row r="28" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A28" s="168"/>
-      <c r="B28" s="90" t="s">
+    <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="91"/>
+      <c r="B28" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C28" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="90" t="s">
+      <c r="D28" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="108" t="s">
+      <c r="E28" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="111" t="s">
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="108" t="s">
+      <c r="I28" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="107" t="s">
+      <c r="J28" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11038,26 +11040,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="103" t="s">
+      <c r="X28" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="Y28" s="97"/>
-      <c r="Z28" s="119"/>
-      <c r="AA28" s="128" t="s">
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="94"/>
+      <c r="AA28" s="154" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1">
-      <c r="A29" s="168"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="107"/>
+    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="91"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="106"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11089,32 +11091,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="153"/>
-      <c r="AA29" s="129"/>
+      <c r="X29" s="160"/>
+      <c r="Y29" s="97"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="155"/>
     </row>
-    <row r="30" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A30" s="168"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="93" t="s">
+    <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="91"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="90" t="s">
+      <c r="D30" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="108" t="s">
+      <c r="E30" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="111" t="s">
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="108" t="s">
+      <c r="I30" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="107" t="s">
+      <c r="J30" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11148,22 +11150,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="103"/>
-      <c r="Y30" s="152"/>
-      <c r="Z30" s="119"/>
-      <c r="AA30" s="166"/>
+      <c r="X30" s="159"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="94"/>
+      <c r="AA30" s="107"/>
     </row>
-    <row r="31" spans="1:27">
-      <c r="A31" s="168"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="107"/>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A31" s="91"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="106"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11195,34 +11197,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="113"/>
-      <c r="Z31" s="153"/>
-      <c r="AA31" s="167"/>
+      <c r="X31" s="160"/>
+      <c r="Y31" s="101"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="108"/>
     </row>
-    <row r="32" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A32" s="168"/>
-      <c r="B32" s="93" t="s">
+    <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="91"/>
+      <c r="B32" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="122" t="s">
+      <c r="C32" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="90" t="s">
+      <c r="D32" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="108" t="s">
+      <c r="E32" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="111" t="s">
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="108" t="s">
+      <c r="I32" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J32" s="107" t="s">
+      <c r="J32" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11256,28 +11258,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="170" t="s">
+      <c r="X32" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="Y32" s="97" t="s">
+      <c r="Y32" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="Z32" s="119"/>
-      <c r="AA32" s="123" t="s">
+      <c r="Z32" s="94"/>
+      <c r="AA32" s="117" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A33" s="168"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="122"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="107"/>
+    <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="91"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="106"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11309,36 +11311,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="171"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="153"/>
-      <c r="AA33" s="124"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="97"/>
+      <c r="Z33" s="95"/>
+      <c r="AA33" s="118"/>
     </row>
-    <row r="34" spans="1:29">
-      <c r="A34" s="109" t="s">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A34" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="93" t="s">
+      <c r="C34" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="90" t="s">
+      <c r="D34" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="108">
+      <c r="E34" s="104">
         <v>90</v>
       </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="111" t="s">
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="108" t="s">
+      <c r="I34" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="120" t="s">
+      <c r="J34" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11364,24 +11366,24 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="94"/>
-      <c r="Y34" s="96"/>
-      <c r="Z34" s="115"/>
-      <c r="AA34" s="123" t="s">
+      <c r="X34" s="111"/>
+      <c r="Y34" s="131"/>
+      <c r="Z34" s="116"/>
+      <c r="AA34" s="117" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
-      <c r="A35" s="109"/>
-      <c r="B35" s="148"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="108"/>
-      <c r="J35" s="120"/>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A35" s="92"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="102"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
@@ -11413,34 +11415,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="115"/>
-      <c r="AA35" s="124"/>
+      <c r="X35" s="111"/>
+      <c r="Y35" s="131"/>
+      <c r="Z35" s="116"/>
+      <c r="AA35" s="118"/>
     </row>
-    <row r="36" spans="1:29">
-      <c r="A36" s="109"/>
-      <c r="B36" s="148" t="s">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A36" s="92"/>
+      <c r="B36" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="93" t="s">
+      <c r="C36" s="123" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="90" t="s">
+      <c r="D36" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="108">
+      <c r="E36" s="104">
         <v>83</v>
       </c>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="111" t="s">
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="108" t="s">
+      <c r="I36" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="121" t="s">
+      <c r="J36" s="161" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11462,28 +11464,28 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="94" t="s">
+      <c r="X36" s="111" t="s">
         <v>113</v>
       </c>
-      <c r="Y36" s="95" t="s">
+      <c r="Y36" s="130" t="s">
         <v>114</v>
       </c>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="123" t="s">
+      <c r="Z36" s="116"/>
+      <c r="AA36" s="117" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
-      <c r="A37" s="109"/>
-      <c r="B37" s="148"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="108"/>
-      <c r="J37" s="121"/>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A37" s="92"/>
+      <c r="B37" s="144"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="161"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
@@ -11513,45 +11515,45 @@
       <c r="U37" s="58"/>
       <c r="V37" s="58"/>
       <c r="W37" s="59"/>
-      <c r="X37" s="137"/>
-      <c r="Y37" s="97"/>
-      <c r="Z37" s="119"/>
-      <c r="AA37" s="125"/>
+      <c r="X37" s="109"/>
+      <c r="Y37" s="96"/>
+      <c r="Z37" s="94"/>
+      <c r="AA37" s="153"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1">
-      <c r="A38" s="138"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="138"/>
-      <c r="N38" s="138"/>
-      <c r="O38" s="138"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="139"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="139"/>
-      <c r="T38" s="139"/>
-      <c r="U38" s="139"/>
-      <c r="V38" s="139"/>
-      <c r="W38" s="139"/>
-      <c r="X38" s="139"/>
-      <c r="Y38" s="139"/>
-      <c r="Z38" s="139"/>
-      <c r="AA38" s="139"/>
+    <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="147"/>
+      <c r="B38" s="147"/>
+      <c r="C38" s="147"/>
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="147"/>
+      <c r="O38" s="147"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="148"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148"/>
+      <c r="T38" s="148"/>
+      <c r="U38" s="148"/>
+      <c r="V38" s="148"/>
+      <c r="W38" s="148"/>
+      <c r="X38" s="148"/>
+      <c r="Y38" s="148"/>
+      <c r="Z38" s="148"/>
+      <c r="AA38" s="148"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
-      <c r="A39" s="141" t="s">
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="149" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="141"/>
+      <c r="B39" s="149"/>
       <c r="C39" s="60"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11578,7 +11580,7 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="27.6" customHeight="1">
+    <row r="40" spans="1:29" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="44" t="s">
         <v>0</v>
       </c>
@@ -11661,35 +11663,35 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:29">
-      <c r="A41" s="142" t="s">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A41" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="145" t="s">
+      <c r="B41" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C41" s="152" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="147" t="s">
+      <c r="D41" s="143" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="140" t="s">
+      <c r="E41" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="F41" s="140" t="s">
+      <c r="F41" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="G41" s="140" t="s">
+      <c r="G41" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="160" t="s">
+      <c r="H41" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="140" t="s">
+      <c r="I41" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="149" t="s">
+      <c r="J41" s="138" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="63" t="s">
@@ -11731,25 +11733,25 @@
       <c r="W41" s="65">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="136"/>
-      <c r="Y41" s="131"/>
-      <c r="Z41" s="131"/>
-      <c r="AA41" s="124" t="s">
+      <c r="X41" s="158"/>
+      <c r="Y41" s="128"/>
+      <c r="Z41" s="128"/>
+      <c r="AA41" s="118" t="s">
         <v>124</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="91"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="108"/>
-      <c r="J42" s="127"/>
+    <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="90"/>
+      <c r="B42" s="125"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="139"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11781,40 +11783,40 @@
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
-      <c r="X42" s="136"/>
-      <c r="Y42" s="131"/>
-      <c r="Z42" s="131"/>
-      <c r="AA42" s="126"/>
+      <c r="X42" s="158"/>
+      <c r="Y42" s="128"/>
+      <c r="Z42" s="128"/>
+      <c r="AA42" s="145"/>
     </row>
-    <row r="43" spans="1:29">
-      <c r="A43" s="144" t="s">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A43" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="91" t="s">
+      <c r="B43" s="125" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="137" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="90" t="s">
+      <c r="D43" s="105" t="s">
         <v>127</v>
       </c>
-      <c r="E43" s="108" t="s">
+      <c r="E43" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="108" t="s">
+      <c r="F43" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="108" t="s">
+      <c r="G43" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H43" s="111" t="s">
+      <c r="H43" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="108" t="s">
+      <c r="I43" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="120" t="s">
+      <c r="J43" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11836,28 +11838,28 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="130" t="s">
+      <c r="X43" s="146" t="s">
         <v>128</v>
       </c>
-      <c r="Y43" s="132" t="s">
+      <c r="Y43" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="Z43" s="133"/>
-      <c r="AA43" s="134" t="s">
+      <c r="Z43" s="140"/>
+      <c r="AA43" s="156" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:29">
-      <c r="A44" s="144"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="159"/>
-      <c r="J44" s="120"/>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A44" s="136"/>
+      <c r="B44" s="125"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="112"/>
+      <c r="J44" s="102"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
@@ -11893,38 +11895,38 @@
         <v>96</v>
       </c>
       <c r="W44" s="57"/>
-      <c r="X44" s="130"/>
-      <c r="Y44" s="132"/>
-      <c r="Z44" s="133"/>
-      <c r="AA44" s="134"/>
+      <c r="X44" s="146"/>
+      <c r="Y44" s="141"/>
+      <c r="Z44" s="140"/>
+      <c r="AA44" s="156"/>
     </row>
-    <row r="45" spans="1:29">
-      <c r="A45" s="144"/>
-      <c r="B45" s="91" t="s">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A45" s="136"/>
+      <c r="B45" s="125" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="92" t="s">
+      <c r="C45" s="137" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="90" t="s">
+      <c r="D45" s="105" t="s">
         <v>132</v>
       </c>
-      <c r="E45" s="108" t="s">
+      <c r="E45" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F45" s="108" t="s">
+      <c r="F45" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="108" t="s">
+      <c r="G45" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="111" t="s">
+      <c r="H45" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="108" t="s">
+      <c r="I45" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="127" t="s">
+      <c r="J45" s="139" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11956,28 +11958,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="130"/>
-      <c r="Y45" s="132" t="s">
+      <c r="X45" s="146"/>
+      <c r="Y45" s="141" t="s">
         <v>133</v>
       </c>
-      <c r="Z45" s="135">
+      <c r="Z45" s="157">
         <v>46188</v>
       </c>
-      <c r="AA45" s="126" t="s">
+      <c r="AA45" s="145" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="16.5" customHeight="1">
-      <c r="A46" s="144"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="127"/>
+    <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="136"/>
+      <c r="B46" s="125"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="139"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12007,38 +12009,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="130"/>
-      <c r="Y46" s="133"/>
-      <c r="Z46" s="133"/>
-      <c r="AA46" s="126"/>
+      <c r="X46" s="146"/>
+      <c r="Y46" s="140"/>
+      <c r="Z46" s="140"/>
+      <c r="AA46" s="145"/>
     </row>
-    <row r="47" spans="1:29">
-      <c r="A47" s="144"/>
-      <c r="B47" s="91" t="s">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A47" s="136"/>
+      <c r="B47" s="125" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="92" t="s">
+      <c r="C47" s="137" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="90" t="s">
+      <c r="D47" s="105" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="108" t="s">
+      <c r="E47" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F47" s="108" t="s">
+      <c r="F47" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G47" s="108" t="s">
+      <c r="G47" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H47" s="111" t="s">
+      <c r="H47" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="108" t="s">
+      <c r="I47" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J47" s="127" t="s">
+      <c r="J47" s="139" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12080,24 +12082,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="130"/>
-      <c r="Y47" s="133"/>
-      <c r="Z47" s="133"/>
-      <c r="AA47" s="90" t="s">
+      <c r="X47" s="146"/>
+      <c r="Y47" s="140"/>
+      <c r="Z47" s="140"/>
+      <c r="AA47" s="105" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A48" s="144"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="127"/>
+    <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="136"/>
+      <c r="B48" s="125"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="139"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12130,40 +12132,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="130"/>
-      <c r="Y48" s="133"/>
-      <c r="Z48" s="133"/>
-      <c r="AA48" s="90"/>
+      <c r="X48" s="146"/>
+      <c r="Y48" s="140"/>
+      <c r="Z48" s="140"/>
+      <c r="AA48" s="105"/>
     </row>
-    <row r="49" spans="1:27">
-      <c r="A49" s="143" t="s">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A49" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="150" t="s">
+      <c r="B49" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="92" t="s">
+      <c r="C49" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="90" t="s">
+      <c r="D49" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="E49" s="108">
+      <c r="E49" s="104">
         <v>74</v>
       </c>
-      <c r="F49" s="108" t="s">
+      <c r="F49" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G49" s="108" t="s">
+      <c r="G49" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H49" s="111" t="s">
+      <c r="H49" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="108" t="s">
+      <c r="I49" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="107" t="s">
+      <c r="J49" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12205,24 +12207,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="130"/>
-      <c r="Y49" s="132"/>
-      <c r="Z49" s="133"/>
-      <c r="AA49" s="126" t="s">
+      <c r="X49" s="146"/>
+      <c r="Y49" s="141"/>
+      <c r="Z49" s="140"/>
+      <c r="AA49" s="145" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:27">
-      <c r="A50" s="143"/>
-      <c r="B50" s="150"/>
-      <c r="C50" s="92"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="108"/>
-      <c r="J50" s="107"/>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A50" s="90"/>
+      <c r="B50" s="142"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="106"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12254,40 +12256,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="76"/>
-      <c r="X50" s="130"/>
-      <c r="Y50" s="132"/>
-      <c r="Z50" s="133"/>
-      <c r="AA50" s="126"/>
+      <c r="X50" s="146"/>
+      <c r="Y50" s="141"/>
+      <c r="Z50" s="140"/>
+      <c r="AA50" s="145"/>
     </row>
-    <row r="51" spans="1:27">
-      <c r="A51" s="144" t="s">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A51" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="91" t="s">
+      <c r="B51" s="125" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="92" t="s">
+      <c r="C51" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="90" t="s">
+      <c r="D51" s="105" t="s">
         <v>142</v>
       </c>
-      <c r="E51" s="108">
+      <c r="E51" s="104">
         <v>33.1</v>
       </c>
-      <c r="F51" s="108" t="s">
+      <c r="F51" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="108" t="s">
+      <c r="G51" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="H51" s="111" t="s">
+      <c r="H51" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="108" t="s">
+      <c r="I51" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="107" t="s">
+      <c r="J51" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12321,24 +12323,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="130"/>
-      <c r="Y51" s="133"/>
-      <c r="Z51" s="133"/>
-      <c r="AA51" s="93" t="s">
+      <c r="X51" s="146"/>
+      <c r="Y51" s="140"/>
+      <c r="Z51" s="140"/>
+      <c r="AA51" s="123" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="15" thickBot="1">
-      <c r="A52" s="144"/>
-      <c r="B52" s="91"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="107"/>
+    <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="136"/>
+      <c r="B52" s="125"/>
+      <c r="C52" s="137"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="103"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="106"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12370,42 +12372,244 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="130"/>
-      <c r="Y52" s="133"/>
-      <c r="Z52" s="133"/>
-      <c r="AA52" s="93"/>
+      <c r="X52" s="146"/>
+      <c r="Y52" s="140"/>
+      <c r="Z52" s="140"/>
+      <c r="AA52" s="123"/>
     </row>
-    <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="58" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="60" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="62" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="64" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="66" ht="14.45" customHeight="1"/>
+    <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="Z10:Z11"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AA30:AA31"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="E30:G31"/>
@@ -12430,230 +12634,28 @@
     <mergeCell ref="I36:I37"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="X26:X27"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -12702,31 +12704,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="73">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    <cfRule type="expression" dxfId="66" priority="76" stopIfTrue="1">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="74">
+    <cfRule type="expression" dxfId="65" priority="75">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="74">
       <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="75">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="76" stopIfTrue="1">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    <cfRule type="expression" dxfId="63" priority="73">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="expression" dxfId="62" priority="69">
+    <cfRule type="expression" dxfId="62" priority="244">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="69">
       <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="242">
+    <cfRule type="expression" dxfId="60" priority="242">
       <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="243">
+    <cfRule type="expression" dxfId="59" priority="243">
       <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="244">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
@@ -12743,185 +12745,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="168">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="170">
+    <cfRule type="expression" dxfId="55" priority="172">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="170">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="171">
+    <cfRule type="expression" dxfId="53" priority="171">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="172">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="173" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="containsBlanks" dxfId="51" priority="99">
+    <cfRule type="expression" dxfId="51" priority="102">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="101">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="49" priority="99">
       <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="100">
+    <cfRule type="expression" dxfId="48" priority="100">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="101">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="102">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="103" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="containsBlanks" dxfId="46" priority="62">
+    <cfRule type="expression" dxfId="46" priority="66" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="65">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="63">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="43" priority="62">
       <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="63">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="64">
+    <cfRule type="expression" dxfId="42" priority="64">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="65">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="66" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="containsBlanks" dxfId="41" priority="11">
-      <formula>LEN(TRIM(N25))=0</formula>
+    <cfRule type="expression" dxfId="41" priority="13">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="12">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="13">
+    <cfRule type="containsBlanks" dxfId="39" priority="11">
+      <formula>LEN(TRIM(N25))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="20" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="17">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="19">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="35" priority="16">
+      <formula>LEN(TRIM(N25))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="18">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="14">
+    <cfRule type="expression" dxfId="32" priority="14">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="15" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="36" priority="16">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="17">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="18">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="19">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="containsBlanks" dxfId="31" priority="57">
+    <cfRule type="expression" dxfId="31" priority="60">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="61" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="29" priority="57">
       <formula>LEN(TRIM(N44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="58">
+    <cfRule type="expression" dxfId="28" priority="58">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="59">
+    <cfRule type="expression" dxfId="27" priority="59">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="60">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="61" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="containsBlanks" dxfId="26" priority="21">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="26" priority="25" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="22">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="24">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="24">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="22">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="22" priority="21">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="1">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="5">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="20" priority="2">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="20" priority="4">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="3">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="4">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="5">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="17" priority="2">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="containsBlanks" dxfId="16" priority="6">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="16" priority="10" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="7">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="9">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="8">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="9">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="7">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="10" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="12" priority="6">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="containsBlanks" dxfId="11" priority="47">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="11" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="48">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="50">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="49">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="50">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="48">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="7" priority="47">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="containsBlanks" dxfId="6" priority="42">
+    <cfRule type="expression" dxfId="6" priority="43">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="5" priority="42">
       <formula>LEN(TRIM(W44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="43">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="44">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="46" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="45">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="44">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -12972,6 +12974,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13109,40 +13131,41 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{787F3183-CB79-425C-95EF-899D8AC4EA34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B30175AE-D1AB-4BF3-B1A2-8C5D0A906D05}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13165,7 +13165,7 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B30175AE-D1AB-4BF3-B1A2-8C5D0A906D05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A72204-EEBE-4421-8939-DC51335784E1}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3208" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46D14F69-5A49-4F9E-8EA9-3814FCDEEEBE}"/>
+  <xr:revisionPtr revIDLastSave="3207" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E097B0B-CC12-443A-81FF-F45BC921F7B0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" state="hidden" r:id="rId1"/>
@@ -834,7 +834,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1569,251 +1569,251 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1862,7 +1862,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1883,7 +1911,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1946,83 +2002,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2045,111 +2024,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2198,6 +2072,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2206,6 +2094,118 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2234,6 +2234,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2283,13 +2290,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2447,7 +2447,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>715645</xdr:colOff>
+      <xdr:colOff>712470</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>18415</xdr:rowOff>
     </xdr:to>
@@ -5188,29 +5188,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AD843-49A7-417E-9F24-86908363EFA2}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.54296875" customWidth="1"/>
-    <col min="5" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" customWidth="1"/>
+    <col min="5" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15.95">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22">
       <c r="A5" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5364,7 +5364,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22">
       <c r="A6" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5450,7 +5450,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22">
       <c r="A7" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5536,7 +5536,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22">
       <c r="A8" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5622,7 +5622,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5708,7 +5708,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5794,7 +5794,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22">
       <c r="A11" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5880,7 +5880,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22">
       <c r="A12" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5966,12 +5966,12 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22">
       <c r="A15" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6129,7 +6129,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22">
       <c r="A16" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6219,7 +6219,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22">
       <c r="A17" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6309,7 +6309,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22">
       <c r="A18" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6399,7 +6399,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22">
       <c r="A19" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6489,7 +6489,7 @@
         <v>0.73999999999999966</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22">
       <c r="A20" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6579,12 +6579,12 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22">
       <c r="A23" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6742,7 +6742,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22">
       <c r="A24" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6832,7 +6832,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22">
       <c r="A25" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6905,9 +6905,9 @@
         <f>IF('AOP Critical'!S18="","",'AOP Critical'!S18)</f>
         <v>3.7</v>
       </c>
-      <c r="S25" s="75">
+      <c r="S25" s="75" t="str">
         <f>IF('AOP Critical'!T18="","",'AOP Critical'!T18)</f>
-        <v>4.5439999999999996</v>
+        <v/>
       </c>
       <c r="T25" s="75" t="str">
         <f>IF('AOP Critical'!U18="","",'AOP Critical'!U18)</f>
@@ -6922,7 +6922,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22">
       <c r="A26" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -7012,7 +7012,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22">
       <c r="A27" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7102,7 +7102,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22">
       <c r="A28" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7192,7 +7192,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22">
       <c r="A29" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7282,7 +7282,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22">
       <c r="A30" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7372,12 +7372,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22">
       <c r="A33" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7535,7 +7535,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22">
       <c r="A34" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7625,7 +7625,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22">
       <c r="A35" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7715,7 +7715,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22">
       <c r="A36" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7805,7 +7805,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22">
       <c r="A37" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7895,7 +7895,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22">
       <c r="A38" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7985,7 +7985,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22">
       <c r="A39" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8075,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22">
       <c r="A40" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8165,7 +8165,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22">
       <c r="A41" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8255,7 +8255,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22">
       <c r="A42" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8345,12 +8345,12 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22">
       <c r="A43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22">
       <c r="A45" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8508,7 +8508,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22">
       <c r="A46" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8598,7 +8598,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22">
       <c r="A47" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8685,7 +8685,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22">
       <c r="A48" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8771,7 +8771,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22">
       <c r="A49" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8861,7 +8861,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22">
       <c r="A50" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8951,7 +8951,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22">
       <c r="A51" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9041,7 +9041,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22">
       <c r="A52" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9131,12 +9131,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22">
       <c r="A54" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -9525,34 +9525,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AC66"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.81640625" customWidth="1"/>
-    <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.81640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7265625" customWidth="1"/>
-    <col min="12" max="12" width="5.54296875" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="6.81640625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="6.26953125" customWidth="1"/>
-    <col min="15" max="15" width="7.26953125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.1796875" hidden="1" customWidth="1"/>
-    <col min="17" max="22" width="6.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" hidden="1" customWidth="1"/>
+    <col min="17" max="22" width="6.140625" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
-    <col min="25" max="25" width="68.1796875" customWidth="1"/>
-    <col min="26" max="26" width="17.7265625" customWidth="1"/>
+    <col min="24" max="24" width="58.85546875" style="20" customWidth="1"/>
+    <col min="25" max="25" width="68.140625" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" customWidth="1"/>
     <col min="27" max="27" width="57" style="13" customWidth="1"/>
-    <col min="28" max="46" width="8.54296875" customWidth="1"/>
+    <col min="28" max="46" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9563,7 +9563,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9572,11 +9572,11 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="162" t="s">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
+      <c r="A3" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="162"/>
+      <c r="B3" s="110"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9596,39 +9596,39 @@
       <c r="X3" s="21"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="163" t="str">
+    <row r="4" spans="1:27" s="5" customFormat="1">
+      <c r="A4" s="112" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="163"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="163"/>
-      <c r="R4" s="163"/>
-      <c r="S4" s="163"/>
-      <c r="T4" s="163"/>
-      <c r="U4" s="163"/>
-      <c r="V4" s="163"/>
-      <c r="W4" s="163"/>
-      <c r="X4" s="163"/>
-      <c r="Y4" s="163"/>
-      <c r="Z4" s="163"/>
-      <c r="AA4" s="163"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
     </row>
-    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="27" customHeight="1">
       <c r="A5" s="88" t="s">
         <v>0</v>
       </c>
@@ -9641,11 +9641,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="164" t="s">
+      <c r="E5" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
       <c r="H5" s="89" t="s">
         <v>8</v>
       </c>
@@ -9707,31 +9707,31 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A6" s="92" t="s">
+    <row r="6" spans="1:27">
+      <c r="A6" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="137" t="s">
+      <c r="C6" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="105" t="s">
+      <c r="D6" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="104">
+      <c r="E6" s="108">
         <v>10</v>
       </c>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="103" t="s">
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="104" t="s">
+      <c r="I6" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="106" t="s">
+      <c r="J6" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9773,24 +9773,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="101"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="117" t="s">
+      <c r="X6" s="106"/>
+      <c r="Y6" s="113"/>
+      <c r="Z6" s="113"/>
+      <c r="AA6" s="123" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="106"/>
+    <row r="7" spans="1:27">
+      <c r="A7" s="109"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="107"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9826,34 +9826,34 @@
       <c r="W7" s="52">
         <v>0.06</v>
       </c>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="118"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
+      <c r="AA7" s="124"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
-      <c r="B8" s="125" t="s">
+    <row r="8" spans="1:27">
+      <c r="A8" s="109"/>
+      <c r="B8" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="137" t="s">
+      <c r="C8" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="105" t="s">
+      <c r="D8" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="104">
+      <c r="E8" s="108">
         <v>90</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="103" t="s">
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="106" t="s">
+      <c r="J8" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9885,28 +9885,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="111"/>
-      <c r="Y8" s="130" t="s">
+      <c r="X8" s="94"/>
+      <c r="Y8" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="115">
+      <c r="Z8" s="114">
         <v>46231</v>
       </c>
-      <c r="AA8" s="117" t="s">
+      <c r="AA8" s="123" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="106"/>
+    <row r="9" spans="1:27">
+      <c r="A9" s="109"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="107"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9940,34 +9940,34 @@
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="118"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="96"/>
+      <c r="Z9" s="115"/>
+      <c r="AA9" s="124"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A10" s="92"/>
-      <c r="B10" s="125" t="s">
+    <row r="10" spans="1:27">
+      <c r="A10" s="109"/>
+      <c r="B10" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="137" t="s">
+      <c r="C10" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="105" t="s">
+      <c r="D10" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="108">
         <v>1</v>
       </c>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="103" t="s">
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="104" t="s">
+      <c r="I10" s="108" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="106" t="s">
+      <c r="J10" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -10001,24 +10001,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="111"/>
-      <c r="Y10" s="119"/>
-      <c r="Z10" s="165"/>
-      <c r="AA10" s="117" t="s">
+      <c r="X10" s="94"/>
+      <c r="Y10" s="164"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="123" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="92"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="106"/>
+    <row r="11" spans="1:27" ht="15" thickBot="1">
+      <c r="A11" s="109"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="107"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10052,36 +10052,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="111"/>
-      <c r="Y11" s="120"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="118"/>
+      <c r="X11" s="94"/>
+      <c r="Y11" s="165"/>
+      <c r="Z11" s="118"/>
+      <c r="AA11" s="124"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="92" t="s">
+    <row r="12" spans="1:27">
+      <c r="A12" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="105" t="s">
+      <c r="D12" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="104">
+      <c r="E12" s="108">
         <v>84</v>
       </c>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="103" t="s">
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="104" t="s">
+      <c r="I12" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="106" t="s">
+      <c r="J12" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10123,24 +10123,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="129"/>
-      <c r="Y12" s="130"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="117" t="s">
+      <c r="X12" s="154"/>
+      <c r="Y12" s="95"/>
+      <c r="Z12" s="96"/>
+      <c r="AA12" s="123" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A13" s="92"/>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="106"/>
+    <row r="13" spans="1:27">
+      <c r="A13" s="109"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="107"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10172,34 +10172,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="129"/>
-      <c r="Y13" s="131"/>
-      <c r="Z13" s="131"/>
-      <c r="AA13" s="118"/>
+      <c r="X13" s="154"/>
+      <c r="Y13" s="96"/>
+      <c r="Z13" s="96"/>
+      <c r="AA13" s="124"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="92"/>
-      <c r="B14" s="123" t="s">
+    <row r="14" spans="1:27">
+      <c r="A14" s="109"/>
+      <c r="B14" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="C14" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="105" t="s">
+      <c r="D14" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="104">
+      <c r="E14" s="108">
         <v>54.6</v>
       </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="103" t="s">
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="104" t="s">
+      <c r="I14" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="106" t="s">
+      <c r="J14" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10233,26 +10233,26 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="109" t="s">
+      <c r="X14" s="137" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="100" t="s">
+      <c r="Y14" s="152" t="s">
         <v>72</v>
       </c>
-      <c r="Z14" s="100"/>
-      <c r="AA14" s="127"/>
+      <c r="Z14" s="152"/>
+      <c r="AA14" s="151"/>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="92"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="106"/>
+    <row r="15" spans="1:27" ht="15" thickBot="1">
+      <c r="A15" s="109"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="107"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10284,36 +10284,36 @@
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-      <c r="AA15" s="128"/>
+      <c r="X15" s="106"/>
+      <c r="Y15" s="113"/>
+      <c r="Z15" s="113"/>
+      <c r="AA15" s="131"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="92" t="s">
+    <row r="16" spans="1:27">
+      <c r="A16" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="C16" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="105" t="s">
+      <c r="D16" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="104" t="s">
+      <c r="E16" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="103" t="s">
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="104" t="s">
+      <c r="I16" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10347,28 +10347,28 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="111" t="s">
+      <c r="X16" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="Y16" s="130" t="s">
+      <c r="Y16" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="Z16" s="116"/>
-      <c r="AA16" s="117" t="s">
+      <c r="Z16" s="115"/>
+      <c r="AA16" s="123" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A17" s="92"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="106"/>
+    <row r="17" spans="1:27">
+      <c r="A17" s="109"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="107"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10400,34 +10400,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="111"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="116"/>
-      <c r="AA17" s="118"/>
+      <c r="X17" s="94"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="115"/>
+      <c r="AA17" s="124"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A18" s="92"/>
-      <c r="B18" s="123" t="s">
+    <row r="18" spans="1:27">
+      <c r="A18" s="109"/>
+      <c r="B18" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="123" t="s">
+      <c r="C18" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="123" t="s">
+      <c r="D18" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="104" t="s">
+      <c r="E18" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="103" t="s">
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="104" t="s">
+      <c r="I18" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="106" t="s">
+      <c r="J18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10458,32 +10458,30 @@
       <c r="S18" s="48">
         <v>3.7</v>
       </c>
-      <c r="T18" s="48">
-        <v>4.5439999999999996</v>
-      </c>
+      <c r="T18" s="48"/>
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="135" t="s">
+      <c r="X18" s="158" t="s">
         <v>83</v>
       </c>
-      <c r="Y18" s="135"/>
-      <c r="Z18" s="132">
+      <c r="Y18" s="158"/>
+      <c r="Z18" s="155">
         <v>46108</v>
       </c>
-      <c r="AA18" s="134"/>
+      <c r="AA18" s="157"/>
     </row>
-    <row r="19" spans="1:27" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="92"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="106"/>
+    <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
+      <c r="A19" s="109"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="107"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
@@ -10515,34 +10513,34 @@
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="50"/>
-      <c r="X19" s="135"/>
-      <c r="Y19" s="135"/>
-      <c r="Z19" s="133"/>
-      <c r="AA19" s="134"/>
+      <c r="X19" s="158"/>
+      <c r="Y19" s="158"/>
+      <c r="Z19" s="156"/>
+      <c r="AA19" s="157"/>
     </row>
-    <row r="20" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="92"/>
-      <c r="B20" s="123" t="s">
+    <row r="20" spans="1:27" ht="21" customHeight="1">
+      <c r="A20" s="109"/>
+      <c r="B20" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D20" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="104" t="s">
+      <c r="E20" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="103" t="s">
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="104" t="s">
+      <c r="I20" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="106" t="s">
+      <c r="J20" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10576,28 +10574,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="167" t="s">
+      <c r="X20" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="Y20" s="169" t="s">
+      <c r="Y20" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="153" t="s">
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="125" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="92"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="106"/>
+    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A21" s="109"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="107"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10629,36 +10627,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="168"/>
-      <c r="Y21" s="170"/>
-      <c r="Z21" s="94"/>
-      <c r="AA21" s="153"/>
+      <c r="X21" s="100"/>
+      <c r="Y21" s="102"/>
+      <c r="Z21" s="119"/>
+      <c r="AA21" s="125"/>
     </row>
-    <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="92" t="s">
+    <row r="22" spans="1:27" ht="15.95" customHeight="1">
+      <c r="A22" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="124" t="s">
+      <c r="C22" s="122" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="93" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="104">
+      <c r="E22" s="108">
         <v>90</v>
       </c>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="103" t="s">
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="104" t="s">
+      <c r="I22" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="106" t="s">
+      <c r="J22" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10700,24 +10698,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="171"/>
-      <c r="Y22" s="130"/>
-      <c r="Z22" s="115">
+      <c r="X22" s="105"/>
+      <c r="Y22" s="95"/>
+      <c r="Z22" s="114">
         <v>46257</v>
       </c>
-      <c r="AA22" s="113"/>
+      <c r="AA22" s="162"/>
     </row>
-    <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="93"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="106"/>
+    <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
+      <c r="A23" s="169"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="107"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10749,40 +10747,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="131"/>
-      <c r="Z23" s="116"/>
-      <c r="AA23" s="114"/>
+      <c r="X23" s="106"/>
+      <c r="Y23" s="96"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="163"/>
     </row>
-    <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="90" t="s">
+    <row r="24" spans="1:27" ht="17.45" customHeight="1">
+      <c r="A24" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="124" t="s">
+      <c r="C24" s="122" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="105" t="s">
+      <c r="D24" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="104" t="s">
+      <c r="E24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="104" t="s">
+      <c r="F24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="104" t="s">
+      <c r="G24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H24" s="103" t="s">
+      <c r="H24" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="104" t="s">
+      <c r="I24" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="102" t="s">
+      <c r="J24" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10816,24 +10814,24 @@
         <v>96</v>
       </c>
       <c r="W24" s="39"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="100"/>
-      <c r="Z24" s="94"/>
-      <c r="AA24" s="117" t="s">
+      <c r="X24" s="137"/>
+      <c r="Y24" s="152"/>
+      <c r="Z24" s="119"/>
+      <c r="AA24" s="123" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="102"/>
+    <row r="25" spans="1:27" ht="15" thickBot="1">
+      <c r="A25" s="168"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="120"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
@@ -10869,34 +10867,34 @@
         <v>96</v>
       </c>
       <c r="W25" s="57"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="118"/>
+      <c r="X25" s="106"/>
+      <c r="Y25" s="113"/>
+      <c r="Z25" s="153"/>
+      <c r="AA25" s="124"/>
     </row>
-    <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="91"/>
-      <c r="B26" s="125" t="s">
+    <row r="26" spans="1:27" ht="14.45" customHeight="1">
+      <c r="A26" s="168"/>
+      <c r="B26" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="126" t="s">
+      <c r="C26" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="104">
+      <c r="E26" s="108">
         <v>34</v>
       </c>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="103" t="s">
+      <c r="F26" s="159"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="104" t="s">
+      <c r="I26" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="106" t="s">
+      <c r="J26" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10930,24 +10928,24 @@
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="131"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="117" t="s">
+      <c r="X26" s="94"/>
+      <c r="Y26" s="96"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="123" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="91"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="106"/>
+    <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
+      <c r="A27" s="168"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="159"/>
+      <c r="G27" s="159"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="107"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10979,34 +10977,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="131"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="118"/>
+      <c r="X27" s="94"/>
+      <c r="Y27" s="96"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="124"/>
     </row>
-    <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="91"/>
-      <c r="B28" s="105" t="s">
+    <row r="28" spans="1:27" ht="14.45" customHeight="1">
+      <c r="A28" s="168"/>
+      <c r="B28" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="123" t="s">
+      <c r="C28" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="105" t="s">
+      <c r="D28" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="104" t="s">
+      <c r="E28" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="103" t="s">
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="106" t="s">
+      <c r="J28" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11040,26 +11038,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="159" t="s">
+      <c r="X28" s="103" t="s">
         <v>103</v>
       </c>
-      <c r="Y28" s="96"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="154" t="s">
+      <c r="Y28" s="97"/>
+      <c r="Z28" s="119"/>
+      <c r="AA28" s="128" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="91"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="106"/>
+    <row r="29" spans="1:27" ht="15" thickBot="1">
+      <c r="A29" s="168"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="107"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11091,32 +11089,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="160"/>
-      <c r="Y29" s="97"/>
-      <c r="Z29" s="95"/>
-      <c r="AA29" s="155"/>
+      <c r="X29" s="104"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="153"/>
+      <c r="AA29" s="129"/>
     </row>
-    <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="91"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="123" t="s">
+    <row r="30" spans="1:27" ht="14.45" customHeight="1">
+      <c r="A30" s="168"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="105" t="s">
+      <c r="D30" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="104" t="s">
+      <c r="E30" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="103" t="s">
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="104" t="s">
+      <c r="I30" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11150,22 +11148,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="159"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="94"/>
-      <c r="AA30" s="107"/>
+      <c r="X30" s="103"/>
+      <c r="Y30" s="152"/>
+      <c r="Z30" s="119"/>
+      <c r="AA30" s="166"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A31" s="91"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="106"/>
+    <row r="31" spans="1:27">
+      <c r="A31" s="168"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="107"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11197,34 +11195,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="160"/>
-      <c r="Y31" s="101"/>
-      <c r="Z31" s="95"/>
-      <c r="AA31" s="108"/>
+      <c r="X31" s="104"/>
+      <c r="Y31" s="113"/>
+      <c r="Z31" s="153"/>
+      <c r="AA31" s="167"/>
     </row>
-    <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="91"/>
-      <c r="B32" s="123" t="s">
+    <row r="32" spans="1:27" ht="14.45" customHeight="1">
+      <c r="A32" s="168"/>
+      <c r="B32" s="93" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="124" t="s">
+      <c r="C32" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="105" t="s">
+      <c r="D32" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="104" t="s">
+      <c r="E32" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="103" t="s">
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="104" t="s">
+      <c r="I32" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J32" s="106" t="s">
+      <c r="J32" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11258,28 +11256,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="98" t="s">
+      <c r="X32" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="Y32" s="96" t="s">
+      <c r="Y32" s="97" t="s">
         <v>109</v>
       </c>
-      <c r="Z32" s="94"/>
-      <c r="AA32" s="117" t="s">
+      <c r="Z32" s="119"/>
+      <c r="AA32" s="123" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="106"/>
+    <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A33" s="168"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="107"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11311,36 +11309,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="97"/>
-      <c r="Z33" s="95"/>
-      <c r="AA33" s="118"/>
+      <c r="X33" s="171"/>
+      <c r="Y33" s="98"/>
+      <c r="Z33" s="153"/>
+      <c r="AA33" s="124"/>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A34" s="92" t="s">
+    <row r="34" spans="1:29">
+      <c r="A34" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="144" t="s">
+      <c r="B34" s="148" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="123" t="s">
+      <c r="C34" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="105" t="s">
+      <c r="D34" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="104">
+      <c r="E34" s="108">
         <v>90</v>
       </c>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="103" t="s">
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="104" t="s">
+      <c r="I34" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="102" t="s">
+      <c r="J34" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11366,24 +11364,24 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="111"/>
-      <c r="Y34" s="131"/>
-      <c r="Z34" s="116"/>
-      <c r="AA34" s="117" t="s">
+      <c r="X34" s="94"/>
+      <c r="Y34" s="96"/>
+      <c r="Z34" s="115"/>
+      <c r="AA34" s="123" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A35" s="92"/>
-      <c r="B35" s="144"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="102"/>
+    <row r="35" spans="1:29">
+      <c r="A35" s="109"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="120"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
@@ -11415,34 +11413,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="131"/>
-      <c r="Z35" s="116"/>
-      <c r="AA35" s="118"/>
+      <c r="X35" s="94"/>
+      <c r="Y35" s="96"/>
+      <c r="Z35" s="115"/>
+      <c r="AA35" s="124"/>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A36" s="92"/>
-      <c r="B36" s="144" t="s">
+    <row r="36" spans="1:29">
+      <c r="A36" s="109"/>
+      <c r="B36" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="123" t="s">
+      <c r="C36" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="105" t="s">
+      <c r="D36" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="104">
+      <c r="E36" s="108">
         <v>83</v>
       </c>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="103" t="s">
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="104" t="s">
+      <c r="I36" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="161" t="s">
+      <c r="J36" s="121" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11464,28 +11462,28 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="111" t="s">
+      <c r="X36" s="94" t="s">
         <v>113</v>
       </c>
-      <c r="Y36" s="130" t="s">
+      <c r="Y36" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="117" t="s">
+      <c r="Z36" s="115"/>
+      <c r="AA36" s="123" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A37" s="92"/>
-      <c r="B37" s="144"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="161"/>
+    <row r="37" spans="1:29">
+      <c r="A37" s="109"/>
+      <c r="B37" s="148"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="121"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
@@ -11515,45 +11513,45 @@
       <c r="U37" s="58"/>
       <c r="V37" s="58"/>
       <c r="W37" s="59"/>
-      <c r="X37" s="109"/>
-      <c r="Y37" s="96"/>
-      <c r="Z37" s="94"/>
-      <c r="AA37" s="153"/>
+      <c r="X37" s="137"/>
+      <c r="Y37" s="97"/>
+      <c r="Z37" s="119"/>
+      <c r="AA37" s="125"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="147"/>
-      <c r="B38" s="147"/>
-      <c r="C38" s="147"/>
-      <c r="D38" s="147"/>
-      <c r="E38" s="147"/>
-      <c r="F38" s="147"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="147"/>
-      <c r="I38" s="147"/>
-      <c r="J38" s="147"/>
-      <c r="K38" s="147"/>
-      <c r="L38" s="147"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="147"/>
-      <c r="O38" s="147"/>
-      <c r="P38" s="148"/>
-      <c r="Q38" s="148"/>
-      <c r="R38" s="148"/>
-      <c r="S38" s="148"/>
-      <c r="T38" s="148"/>
-      <c r="U38" s="148"/>
-      <c r="V38" s="148"/>
-      <c r="W38" s="148"/>
-      <c r="X38" s="148"/>
-      <c r="Y38" s="148"/>
-      <c r="Z38" s="148"/>
-      <c r="AA38" s="148"/>
+    <row r="38" spans="1:29" s="5" customFormat="1">
+      <c r="A38" s="138"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="138"/>
+      <c r="K38" s="138"/>
+      <c r="L38" s="138"/>
+      <c r="M38" s="138"/>
+      <c r="N38" s="138"/>
+      <c r="O38" s="138"/>
+      <c r="P38" s="139"/>
+      <c r="Q38" s="139"/>
+      <c r="R38" s="139"/>
+      <c r="S38" s="139"/>
+      <c r="T38" s="139"/>
+      <c r="U38" s="139"/>
+      <c r="V38" s="139"/>
+      <c r="W38" s="139"/>
+      <c r="X38" s="139"/>
+      <c r="Y38" s="139"/>
+      <c r="Z38" s="139"/>
+      <c r="AA38" s="139"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="149" t="s">
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
+      <c r="A39" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="149"/>
+      <c r="B39" s="141"/>
       <c r="C39" s="60"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11580,7 +11578,7 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:29" ht="27.6" customHeight="1">
       <c r="A40" s="44" t="s">
         <v>0</v>
       </c>
@@ -11663,35 +11661,35 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A41" s="150" t="s">
+    <row r="41" spans="1:29">
+      <c r="A41" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="151" t="s">
+      <c r="B41" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="152" t="s">
+      <c r="C41" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="143" t="s">
+      <c r="D41" s="147" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="121" t="s">
+      <c r="E41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="F41" s="121" t="s">
+      <c r="F41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="G41" s="121" t="s">
+      <c r="G41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="122" t="s">
+      <c r="H41" s="160" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="121" t="s">
+      <c r="I41" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="138" t="s">
+      <c r="J41" s="149" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="63" t="s">
@@ -11733,25 +11731,25 @@
       <c r="W41" s="65">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="158"/>
-      <c r="Y41" s="128"/>
-      <c r="Z41" s="128"/>
-      <c r="AA41" s="118" t="s">
+      <c r="X41" s="136"/>
+      <c r="Y41" s="131"/>
+      <c r="Z41" s="131"/>
+      <c r="AA41" s="124" t="s">
         <v>124</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="90"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="137"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="139"/>
+    <row r="42" spans="1:29" ht="23.1" customHeight="1">
+      <c r="A42" s="143"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="92"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="108"/>
+      <c r="J42" s="127"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11783,40 +11781,40 @@
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
-      <c r="X42" s="158"/>
-      <c r="Y42" s="128"/>
-      <c r="Z42" s="128"/>
-      <c r="AA42" s="145"/>
+      <c r="X42" s="136"/>
+      <c r="Y42" s="131"/>
+      <c r="Z42" s="131"/>
+      <c r="AA42" s="126"/>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A43" s="136" t="s">
+    <row r="43" spans="1:29">
+      <c r="A43" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="125" t="s">
+      <c r="B43" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="137" t="s">
+      <c r="C43" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="105" t="s">
+      <c r="D43" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="E43" s="104" t="s">
+      <c r="E43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="104" t="s">
+      <c r="F43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="104" t="s">
+      <c r="G43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H43" s="103" t="s">
+      <c r="H43" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="104" t="s">
+      <c r="I43" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="102" t="s">
+      <c r="J43" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11838,28 +11836,28 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="146" t="s">
+      <c r="X43" s="130" t="s">
         <v>128</v>
       </c>
-      <c r="Y43" s="141" t="s">
+      <c r="Y43" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="Z43" s="140"/>
-      <c r="AA43" s="156" t="s">
+      <c r="Z43" s="133"/>
+      <c r="AA43" s="134" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A44" s="136"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="112"/>
-      <c r="J44" s="102"/>
+    <row r="44" spans="1:29">
+      <c r="A44" s="144"/>
+      <c r="B44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
+      <c r="H44" s="111"/>
+      <c r="I44" s="159"/>
+      <c r="J44" s="120"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
@@ -11895,38 +11893,38 @@
         <v>96</v>
       </c>
       <c r="W44" s="57"/>
-      <c r="X44" s="146"/>
-      <c r="Y44" s="141"/>
-      <c r="Z44" s="140"/>
-      <c r="AA44" s="156"/>
+      <c r="X44" s="130"/>
+      <c r="Y44" s="132"/>
+      <c r="Z44" s="133"/>
+      <c r="AA44" s="134"/>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A45" s="136"/>
-      <c r="B45" s="125" t="s">
+    <row r="45" spans="1:29">
+      <c r="A45" s="144"/>
+      <c r="B45" s="91" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="137" t="s">
+      <c r="C45" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="105" t="s">
+      <c r="D45" s="90" t="s">
         <v>132</v>
       </c>
-      <c r="E45" s="104" t="s">
+      <c r="E45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F45" s="104" t="s">
+      <c r="F45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="104" t="s">
+      <c r="G45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="103" t="s">
+      <c r="H45" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="104" t="s">
+      <c r="I45" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="139" t="s">
+      <c r="J45" s="127" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11958,28 +11956,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="146"/>
-      <c r="Y45" s="141" t="s">
+      <c r="X45" s="130"/>
+      <c r="Y45" s="132" t="s">
         <v>133</v>
       </c>
-      <c r="Z45" s="157">
+      <c r="Z45" s="135">
         <v>46188</v>
       </c>
-      <c r="AA45" s="145" t="s">
+      <c r="AA45" s="126" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="136"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="137"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="139"/>
+    <row r="46" spans="1:29" ht="16.5" customHeight="1">
+      <c r="A46" s="144"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="127"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12009,38 +12007,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="146"/>
-      <c r="Y46" s="140"/>
-      <c r="Z46" s="140"/>
-      <c r="AA46" s="145"/>
+      <c r="X46" s="130"/>
+      <c r="Y46" s="133"/>
+      <c r="Z46" s="133"/>
+      <c r="AA46" s="126"/>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A47" s="136"/>
-      <c r="B47" s="125" t="s">
+    <row r="47" spans="1:29">
+      <c r="A47" s="144"/>
+      <c r="B47" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="137" t="s">
+      <c r="C47" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="105" t="s">
+      <c r="D47" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="104" t="s">
+      <c r="E47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F47" s="104" t="s">
+      <c r="F47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G47" s="104" t="s">
+      <c r="G47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H47" s="103" t="s">
+      <c r="H47" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="104" t="s">
+      <c r="I47" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J47" s="139" t="s">
+      <c r="J47" s="127" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12082,24 +12080,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="146"/>
-      <c r="Y47" s="140"/>
-      <c r="Z47" s="140"/>
-      <c r="AA47" s="105" t="s">
+      <c r="X47" s="130"/>
+      <c r="Y47" s="133"/>
+      <c r="Z47" s="133"/>
+      <c r="AA47" s="90" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="136"/>
-      <c r="B48" s="125"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="139"/>
+    <row r="48" spans="1:29" ht="20.45" customHeight="1">
+      <c r="A48" s="144"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108"/>
+      <c r="H48" s="111"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="127"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12132,40 +12130,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="146"/>
-      <c r="Y48" s="140"/>
-      <c r="Z48" s="140"/>
-      <c r="AA48" s="105"/>
+      <c r="X48" s="130"/>
+      <c r="Y48" s="133"/>
+      <c r="Z48" s="133"/>
+      <c r="AA48" s="90"/>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A49" s="90" t="s">
+    <row r="49" spans="1:27">
+      <c r="A49" s="143" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="142" t="s">
+      <c r="B49" s="150" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="137" t="s">
+      <c r="C49" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="105" t="s">
+      <c r="D49" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="E49" s="104">
+      <c r="E49" s="108">
         <v>74</v>
       </c>
-      <c r="F49" s="104" t="s">
+      <c r="F49" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G49" s="104" t="s">
+      <c r="G49" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H49" s="103" t="s">
+      <c r="H49" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="104" t="s">
+      <c r="I49" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="106" t="s">
+      <c r="J49" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12207,24 +12205,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="146"/>
-      <c r="Y49" s="141"/>
-      <c r="Z49" s="140"/>
-      <c r="AA49" s="145" t="s">
+      <c r="X49" s="130"/>
+      <c r="Y49" s="132"/>
+      <c r="Z49" s="133"/>
+      <c r="AA49" s="126" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A50" s="90"/>
-      <c r="B50" s="142"/>
-      <c r="C50" s="137"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="106"/>
+    <row r="50" spans="1:27">
+      <c r="A50" s="143"/>
+      <c r="B50" s="150"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="111"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="107"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12256,40 +12254,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="76"/>
-      <c r="X50" s="146"/>
-      <c r="Y50" s="141"/>
-      <c r="Z50" s="140"/>
-      <c r="AA50" s="145"/>
+      <c r="X50" s="130"/>
+      <c r="Y50" s="132"/>
+      <c r="Z50" s="133"/>
+      <c r="AA50" s="126"/>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A51" s="136" t="s">
+    <row r="51" spans="1:27">
+      <c r="A51" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="125" t="s">
+      <c r="B51" s="91" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="137" t="s">
+      <c r="C51" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="105" t="s">
+      <c r="D51" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="E51" s="104">
+      <c r="E51" s="108">
         <v>33.1</v>
       </c>
-      <c r="F51" s="104" t="s">
+      <c r="F51" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="104" t="s">
+      <c r="G51" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H51" s="103" t="s">
+      <c r="H51" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="104" t="s">
+      <c r="I51" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="106" t="s">
+      <c r="J51" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12323,24 +12321,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="146"/>
-      <c r="Y51" s="140"/>
-      <c r="Z51" s="140"/>
-      <c r="AA51" s="123" t="s">
+      <c r="X51" s="130"/>
+      <c r="Y51" s="133"/>
+      <c r="Z51" s="133"/>
+      <c r="AA51" s="93" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="136"/>
-      <c r="B52" s="125"/>
-      <c r="C52" s="137"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="106"/>
+    <row r="52" spans="1:27" ht="15" thickBot="1">
+      <c r="A52" s="144"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="108"/>
+      <c r="J52" s="107"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12372,41 +12370,245 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="146"/>
-      <c r="Y52" s="140"/>
-      <c r="Z52" s="140"/>
-      <c r="AA52" s="123"/>
+      <c r="X52" s="130"/>
+      <c r="Y52" s="133"/>
+      <c r="Z52" s="133"/>
+      <c r="AA52" s="93"/>
     </row>
-    <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="58" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="60" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="62" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="64" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="66" ht="14.45" customHeight="1"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="E32:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G37"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="X26:X27"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A3:B3"/>
@@ -12431,231 +12633,27 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="J8:J9"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="AA30:AA31"/>
-    <mergeCell ref="X24:X25"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G37"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="X26:X27"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -12704,31 +12702,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="76" stopIfTrue="1">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    <cfRule type="expression" dxfId="66" priority="73">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="75">
+    <cfRule type="expression" dxfId="65" priority="74">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="75">
       <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="74">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="73">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    <cfRule type="expression" dxfId="63" priority="76" stopIfTrue="1">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="expression" dxfId="62" priority="244">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="69">
+    <cfRule type="expression" dxfId="62" priority="69">
       <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="242">
+    <cfRule type="expression" dxfId="61" priority="242">
       <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="243">
+    <cfRule type="expression" dxfId="60" priority="243">
       <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="244">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
@@ -12745,185 +12743,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="168">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="172">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="170">
+    <cfRule type="expression" dxfId="55" priority="170">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="171">
+    <cfRule type="expression" dxfId="54" priority="171">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="172">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="173" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="expression" dxfId="51" priority="102">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    <cfRule type="containsBlanks" dxfId="51" priority="99">
+      <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="101">
+    <cfRule type="expression" dxfId="50" priority="100">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="101">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="49" priority="99">
-      <formula>LEN(TRIM(L52))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="100">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    <cfRule type="expression" dxfId="48" priority="102">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="103" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="expression" dxfId="46" priority="66" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+    <cfRule type="containsBlanks" dxfId="46" priority="62">
+      <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="65">
+    <cfRule type="expression" dxfId="45" priority="63">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="64">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="65">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="63">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="43" priority="62">
-      <formula>LEN(TRIM(L25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="64">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    <cfRule type="expression" dxfId="42" priority="66" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="41" priority="13">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    <cfRule type="containsBlanks" dxfId="41" priority="11">
+      <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="12">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="39" priority="11">
+    <cfRule type="expression" dxfId="39" priority="13">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="14">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="36" priority="16">
       <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="20" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="17">
+    <cfRule type="expression" dxfId="35" priority="17">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="19">
+    <cfRule type="expression" dxfId="34" priority="18">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="19">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="35" priority="16">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="18">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="14">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="expression" dxfId="31" priority="60">
+    <cfRule type="containsBlanks" dxfId="31" priority="57">
+      <formula>LEN(TRIM(N44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="58">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="59">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="60">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="61" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="29" priority="57">
-      <formula>LEN(TRIM(N44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="58">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="59">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="expression" dxfId="26" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="26" priority="21">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="24">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="22">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="22">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="22" priority="21">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="22" priority="25" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="5">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="4">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="20" priority="2">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="3">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="1">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="4">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="17" priority="2">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="17" priority="5">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="expression" dxfId="16" priority="10" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="16" priority="6">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="9">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="7">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="8">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="9">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="12" priority="6">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="12" priority="10" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="expression" dxfId="11" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="11" priority="47">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="50">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="48">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="49">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="48">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="50">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="7" priority="47">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="7" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="expression" dxfId="6" priority="43">
+    <cfRule type="containsBlanks" dxfId="6" priority="42">
+      <formula>LEN(TRIM(W44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="43">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="5" priority="42">
-      <formula>LEN(TRIM(W44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="46" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="44">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="45">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="44">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -12974,26 +12972,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13131,41 +13109,40 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F488CD-71A3-46BB-878D-37FDAEEAEE94}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A72204-EEBE-4421-8939-DC51335784E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3207" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E097B0B-CC12-443A-81FF-F45BC921F7B0}"/>
+  <xr:revisionPtr revIDLastSave="3219" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A8860E4-9AF7-475C-9DE7-CE9E67B41F90}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView minimized="1" xWindow="33225" yWindow="1230" windowWidth="14400" windowHeight="8175" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" state="hidden" r:id="rId1"/>
     <sheet name="AOP Critical" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -622,9 +622,6 @@
     <t>Mn</t>
   </si>
   <si>
-    <t>YTD Aug Productivity no's on track.</t>
-  </si>
-  <si>
     <t>Inventory MAT sales</t>
   </si>
   <si>
@@ -821,6 +818,9 @@
   </si>
   <si>
     <t>Focus on optimizing FCP, pricing, and product mix to drive margin expansion</t>
+  </si>
+  <si>
+    <t>YTD Sept Productivity no's on track.Good Realization from E&amp;E savings of Pune and also a gap reduction of R&amp;D Budget YTD.</t>
   </si>
 </sst>
 </file>
@@ -834,7 +834,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,7 +961,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="7"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1569,250 +1569,250 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1862,35 +1862,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1911,35 +1883,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2002,6 +1946,83 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2024,6 +2045,111 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2072,20 +2198,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2094,118 +2206,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2234,6 +2234,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2283,13 +2290,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2447,7 +2447,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>712470</xdr:colOff>
+      <xdr:colOff>715645</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>18415</xdr:rowOff>
     </xdr:to>
@@ -4632,6 +4632,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}" name="Customer_Focus" displayName="Customer_Focus" ref="A14:V20" totalsRowShown="0">
   <autoFilter ref="A14:V20" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}"/>
@@ -5188,29 +5192,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AD843-49A7-417E-9F24-86908363EFA2}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.5703125" customWidth="1"/>
-    <col min="5" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="55.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.54296875" customWidth="1"/>
+    <col min="5" max="6" width="10.453125" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.95">
+    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5278,7 +5282,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5364,7 +5368,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5445,12 +5449,12 @@
         <f>IF('AOP Critical'!V7="","",'AOP Critical'!V7)</f>
         <v/>
       </c>
-      <c r="V6" s="69">
+      <c r="V6" s="69" t="str">
         <f>IF('AOP Critical'!W7="","",'AOP Critical'!W7)</f>
-        <v>0.06</v>
+        <v/>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5536,7 +5540,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5622,7 +5626,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5708,7 +5712,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5794,7 +5798,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5880,7 +5884,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5966,12 +5970,12 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -6039,7 +6043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6129,7 +6133,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6219,7 +6223,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6309,7 +6313,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6399,7 +6403,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6489,7 +6493,7 @@
         <v>0.73999999999999966</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6579,12 +6583,12 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -6652,7 +6656,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6742,7 +6746,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6832,7 +6836,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6905,9 +6909,9 @@
         <f>IF('AOP Critical'!S18="","",'AOP Critical'!S18)</f>
         <v>3.7</v>
       </c>
-      <c r="S25" s="75" t="str">
+      <c r="S25" s="75">
         <f>IF('AOP Critical'!T18="","",'AOP Critical'!T18)</f>
-        <v/>
+        <v>4.5439999999999996</v>
       </c>
       <c r="T25" s="75" t="str">
         <f>IF('AOP Critical'!U18="","",'AOP Critical'!U18)</f>
@@ -6922,7 +6926,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6995,9 +6999,9 @@
         <f>IF('AOP Critical'!S19="","",'AOP Critical'!S19)</f>
         <v>3.895</v>
       </c>
-      <c r="S26" s="75" t="str">
+      <c r="S26" s="75">
         <f>IF('AOP Critical'!T19="","",'AOP Critical'!T19)</f>
-        <v/>
+        <v>4.92</v>
       </c>
       <c r="T26" s="75" t="str">
         <f>IF('AOP Critical'!U19="","",'AOP Critical'!U19)</f>
@@ -7012,7 +7016,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7102,7 +7106,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7192,7 +7196,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7282,7 +7286,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7372,12 +7376,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -7445,7 +7449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7535,7 +7539,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7625,7 +7629,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7715,7 +7719,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7805,7 +7809,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7895,7 +7899,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7985,7 +7989,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8075,7 +8079,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8165,7 +8169,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8255,7 +8259,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8345,12 +8349,12 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -8418,7 +8422,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8508,7 +8512,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8598,7 +8602,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8685,7 +8689,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8771,7 +8775,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8861,7 +8865,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8951,7 +8955,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9041,7 +9045,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9131,12 +9135,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -9204,7 +9208,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -9279,7 +9283,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -9354,7 +9358,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -9429,7 +9433,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -9525,34 +9529,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AC66"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.140625" hidden="1" customWidth="1"/>
-    <col min="17" max="22" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.81640625" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.81640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" customWidth="1"/>
+    <col min="12" max="12" width="5.54296875" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.26953125" customWidth="1"/>
+    <col min="15" max="15" width="7.26953125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.1796875" hidden="1" customWidth="1"/>
+    <col min="17" max="22" width="6.1796875" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="58.85546875" style="20" customWidth="1"/>
-    <col min="25" max="25" width="68.140625" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" customWidth="1"/>
+    <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
+    <col min="25" max="25" width="68.1796875" customWidth="1"/>
+    <col min="26" max="26" width="17.7265625" customWidth="1"/>
     <col min="27" max="27" width="57" style="13" customWidth="1"/>
-    <col min="28" max="46" width="8.5703125" customWidth="1"/>
+    <col min="28" max="46" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9563,7 +9567,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9572,11 +9576,11 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
-      <c r="A3" s="110" t="s">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="110"/>
+      <c r="B3" s="162"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9596,39 +9600,39 @@
       <c r="X3" s="21"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1">
-      <c r="A4" s="112" t="str">
+    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="163" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="163"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="163"/>
+      <c r="K4" s="163"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="163"/>
+      <c r="U4" s="163"/>
+      <c r="V4" s="163"/>
+      <c r="W4" s="163"/>
+      <c r="X4" s="163"/>
+      <c r="Y4" s="163"/>
+      <c r="Z4" s="163"/>
+      <c r="AA4" s="163"/>
     </row>
-    <row r="5" spans="1:27" ht="27" customHeight="1">
+    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="88" t="s">
         <v>0</v>
       </c>
@@ -9641,11 +9645,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="116" t="s">
+      <c r="E5" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="164"/>
       <c r="H5" s="89" t="s">
         <v>8</v>
       </c>
@@ -9707,31 +9711,31 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="109" t="s">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A6" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="108">
+      <c r="E6" s="104">
         <v>10</v>
       </c>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="111" t="s">
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="107" t="s">
+      <c r="J6" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9773,24 +9777,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="106"/>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="123" t="s">
+      <c r="X6" s="110"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="117" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="109"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="107"/>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A7" s="92"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="106"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9823,37 +9827,35 @@
       </c>
       <c r="U7" s="52"/>
       <c r="V7" s="52"/>
-      <c r="W7" s="52">
-        <v>0.06</v>
-      </c>
-      <c r="X7" s="94"/>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
-      <c r="AA7" s="124"/>
+      <c r="W7" s="52"/>
+      <c r="X7" s="111"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="118"/>
     </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="109"/>
-      <c r="B8" s="91" t="s">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A8" s="92"/>
+      <c r="B8" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="108">
+      <c r="E8" s="104">
         <v>90</v>
       </c>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="111" t="s">
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="108" t="s">
+      <c r="I8" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="107" t="s">
+      <c r="J8" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9885,28 +9887,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="95" t="s">
+      <c r="X8" s="111"/>
+      <c r="Y8" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="114">
+      <c r="Z8" s="115">
         <v>46231</v>
       </c>
-      <c r="AA8" s="123" t="s">
+      <c r="AA8" s="117" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="109"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="107"/>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A9" s="92"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="106"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9940,34 +9942,34 @@
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="124"/>
+      <c r="X9" s="111"/>
+      <c r="Y9" s="131"/>
+      <c r="Z9" s="116"/>
+      <c r="AA9" s="118"/>
     </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="109"/>
-      <c r="B10" s="91" t="s">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A10" s="92"/>
+      <c r="B10" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="137" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="108">
+      <c r="E10" s="104">
         <v>1</v>
       </c>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="111" t="s">
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="107" t="s">
+      <c r="J10" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -10001,24 +10003,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="94"/>
-      <c r="Y10" s="164"/>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="123" t="s">
+      <c r="X10" s="111"/>
+      <c r="Y10" s="119"/>
+      <c r="Z10" s="165"/>
+      <c r="AA10" s="117" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1">
-      <c r="A11" s="109"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="107"/>
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="92"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="106"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10052,36 +10054,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="94"/>
-      <c r="Y11" s="165"/>
-      <c r="Z11" s="118"/>
-      <c r="AA11" s="124"/>
+      <c r="X11" s="111"/>
+      <c r="Y11" s="120"/>
+      <c r="Z11" s="166"/>
+      <c r="AA11" s="118"/>
     </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="109" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A12" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="108">
+      <c r="E12" s="104">
         <v>84</v>
       </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="111" t="s">
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="108" t="s">
+      <c r="I12" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="107" t="s">
+      <c r="J12" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10123,24 +10125,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="154"/>
-      <c r="Y12" s="95"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="123" t="s">
+      <c r="X12" s="129"/>
+      <c r="Y12" s="130"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="117" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="109"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="107"/>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A13" s="92"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="106"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10172,34 +10174,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="154"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="124"/>
+      <c r="X13" s="129"/>
+      <c r="Y13" s="131"/>
+      <c r="Z13" s="131"/>
+      <c r="AA13" s="118"/>
     </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="109"/>
-      <c r="B14" s="93" t="s">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A14" s="92"/>
+      <c r="B14" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C14" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="108">
+      <c r="E14" s="104">
         <v>54.6</v>
       </c>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="111" t="s">
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="108" t="s">
+      <c r="I14" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="107" t="s">
+      <c r="J14" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10233,26 +10235,26 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="137" t="s">
+      <c r="X14" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="152" t="s">
+      <c r="Y14" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="Z14" s="152"/>
-      <c r="AA14" s="151"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="127"/>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1">
-      <c r="A15" s="109"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="107"/>
+    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="92"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="106"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10284,36 +10286,36 @@
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="106"/>
-      <c r="Y15" s="113"/>
-      <c r="Z15" s="113"/>
-      <c r="AA15" s="131"/>
+      <c r="X15" s="110"/>
+      <c r="Y15" s="101"/>
+      <c r="Z15" s="101"/>
+      <c r="AA15" s="128"/>
     </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="109" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="C16" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="90" t="s">
+      <c r="D16" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="108" t="s">
+      <c r="E16" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="111" t="s">
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="107" t="s">
+      <c r="J16" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10347,28 +10349,28 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="94" t="s">
+      <c r="X16" s="111" t="s">
         <v>77</v>
       </c>
-      <c r="Y16" s="95" t="s">
+      <c r="Y16" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="123" t="s">
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="117" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
-      <c r="A17" s="109"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="107"/>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17" s="92"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="106"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10400,34 +10402,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="94"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="124"/>
+      <c r="X17" s="111"/>
+      <c r="Y17" s="131"/>
+      <c r="Z17" s="116"/>
+      <c r="AA17" s="118"/>
     </row>
-    <row r="18" spans="1:27">
-      <c r="A18" s="109"/>
-      <c r="B18" s="93" t="s">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A18" s="92"/>
+      <c r="B18" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="93" t="s">
+      <c r="D18" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="108" t="s">
+      <c r="E18" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="111" t="s">
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="108" t="s">
+      <c r="I18" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="107" t="s">
+      <c r="J18" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10458,30 +10460,32 @@
       <c r="S18" s="48">
         <v>3.7</v>
       </c>
-      <c r="T18" s="48"/>
+      <c r="T18" s="48">
+        <v>4.5439999999999996</v>
+      </c>
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="158" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y18" s="158"/>
-      <c r="Z18" s="155">
+      <c r="X18" s="135" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y18" s="135"/>
+      <c r="Z18" s="132">
         <v>46108</v>
       </c>
-      <c r="AA18" s="157"/>
+      <c r="AA18" s="134"/>
     </row>
-    <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
-      <c r="A19" s="109"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="107"/>
+    <row r="19" spans="1:27" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="92"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="106"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
@@ -10509,38 +10513,40 @@
       <c r="S19" s="86">
         <v>3.895</v>
       </c>
-      <c r="T19" s="47"/>
+      <c r="T19" s="47">
+        <v>4.92</v>
+      </c>
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="50"/>
-      <c r="X19" s="158"/>
-      <c r="Y19" s="158"/>
-      <c r="Z19" s="156"/>
-      <c r="AA19" s="157"/>
+      <c r="X19" s="135"/>
+      <c r="Y19" s="135"/>
+      <c r="Z19" s="133"/>
+      <c r="AA19" s="134"/>
     </row>
-    <row r="20" spans="1:27" ht="21" customHeight="1">
-      <c r="A20" s="109"/>
-      <c r="B20" s="93" t="s">
+    <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="92"/>
+      <c r="B20" s="123" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="93" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="90" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" s="108" t="s">
+      <c r="E20" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="108"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="111" t="s">
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="108" t="s">
+      <c r="I20" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="107" t="s">
+      <c r="J20" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10574,28 +10580,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="99" t="s">
+      <c r="X20" s="170" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y20" s="167" t="s">
         <v>86</v>
       </c>
-      <c r="Y20" s="101" t="s">
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="153" t="s">
         <v>87</v>
       </c>
-      <c r="Z20" s="153"/>
-      <c r="AA20" s="125" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="107"/>
+    <row r="21" spans="1:27" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="92"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="106"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10627,36 +10633,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="100"/>
-      <c r="Y21" s="102"/>
-      <c r="Z21" s="119"/>
-      <c r="AA21" s="125"/>
+      <c r="X21" s="171"/>
+      <c r="Y21" s="168"/>
+      <c r="Z21" s="94"/>
+      <c r="AA21" s="153"/>
     </row>
-    <row r="22" spans="1:27" ht="15.95" customHeight="1">
-      <c r="A22" s="109" t="s">
+    <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="123" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="124" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="122" t="s">
+      <c r="D22" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="93" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" s="108">
+      <c r="E22" s="104">
         <v>90</v>
       </c>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="111" t="s">
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="108" t="s">
+      <c r="I22" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="107" t="s">
+      <c r="J22" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10698,24 +10704,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="105"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="114">
+      <c r="X22" s="169"/>
+      <c r="Y22" s="130"/>
+      <c r="Z22" s="115">
         <v>46257</v>
       </c>
-      <c r="AA22" s="162"/>
+      <c r="AA22" s="113"/>
     </row>
-    <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A23" s="169"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="107"/>
+    <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="93"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="106"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10747,40 +10753,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="106"/>
-      <c r="Y23" s="96"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="163"/>
+      <c r="X23" s="110"/>
+      <c r="Y23" s="131"/>
+      <c r="Z23" s="116"/>
+      <c r="AA23" s="114"/>
     </row>
-    <row r="24" spans="1:27" ht="17.45" customHeight="1">
-      <c r="A24" s="143" t="s">
+    <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="93" t="s">
+      <c r="B24" s="123" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="124" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="122" t="s">
+      <c r="D24" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="90" t="s">
+      <c r="E24" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="111" t="s">
+      <c r="F24" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="108" t="s">
+      <c r="I24" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="120" t="s">
+      <c r="J24" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10792,109 +10798,109 @@
         <v>0.104</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="38">
         <v>0.11799999999999999</v>
       </c>
       <c r="R24" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S24" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T24" s="36"/>
       <c r="U24" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="V24" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="W24" s="39"/>
+      <c r="X24" s="109"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="94"/>
+      <c r="AA24" s="117" t="s">
         <v>96</v>
       </c>
-      <c r="V24" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="W24" s="39"/>
-      <c r="X24" s="137"/>
-      <c r="Y24" s="152"/>
-      <c r="Z24" s="119"/>
-      <c r="AA24" s="123" t="s">
-        <v>97</v>
-      </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1">
-      <c r="A25" s="168"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="120"/>
+    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="91"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="102"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N25" s="52">
         <v>0.115</v>
       </c>
       <c r="O25" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P25" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="17">
         <v>0.121</v>
       </c>
       <c r="R25" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S25" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T25" s="57"/>
       <c r="U25" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="V25" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W25" s="57"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="113"/>
-      <c r="Z25" s="153"/>
-      <c r="AA25" s="124"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="101"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="118"/>
     </row>
-    <row r="26" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A26" s="168"/>
-      <c r="B26" s="91" t="s">
+    <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="91"/>
+      <c r="B26" s="125" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="126" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="161" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" s="90" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" s="108">
+      <c r="E26" s="104">
         <v>34</v>
       </c>
-      <c r="F26" s="159"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="111" t="s">
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="108" t="s">
+      <c r="I26" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="107" t="s">
+      <c r="J26" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10928,24 +10934,24 @@
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="94"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="123" t="s">
-        <v>100</v>
+      <c r="X26" s="111"/>
+      <c r="Y26" s="131"/>
+      <c r="Z26" s="116"/>
+      <c r="AA26" s="117" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A27" s="168"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="161"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="159"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="107"/>
+    <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="91"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="106"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10977,34 +10983,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="94"/>
-      <c r="Y27" s="96"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="124"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="131"/>
+      <c r="Z27" s="116"/>
+      <c r="AA27" s="118"/>
     </row>
-    <row r="28" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A28" s="168"/>
-      <c r="B28" s="90" t="s">
+    <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="91"/>
+      <c r="B28" s="105" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="93" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" s="90" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="108" t="s">
+      <c r="E28" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="111" t="s">
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="108" t="s">
+      <c r="I28" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="107" t="s">
+      <c r="J28" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11038,26 +11044,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="103" t="s">
+      <c r="X28" s="159" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="94"/>
+      <c r="AA28" s="154" t="s">
         <v>103</v>
       </c>
-      <c r="Y28" s="97"/>
-      <c r="Z28" s="119"/>
-      <c r="AA28" s="128" t="s">
-        <v>104</v>
-      </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1">
-      <c r="A29" s="168"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="107"/>
+    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="91"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="106"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11089,32 +11095,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="153"/>
-      <c r="AA29" s="129"/>
+      <c r="X29" s="160"/>
+      <c r="Y29" s="97"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="155"/>
     </row>
-    <row r="30" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A30" s="168"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="93" t="s">
+    <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="91"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="90" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" s="108" t="s">
+      <c r="D30" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="111" t="s">
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="108" t="s">
+      <c r="I30" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="107" t="s">
+      <c r="J30" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11148,22 +11154,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="103"/>
-      <c r="Y30" s="152"/>
-      <c r="Z30" s="119"/>
-      <c r="AA30" s="166"/>
+      <c r="X30" s="159"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="94"/>
+      <c r="AA30" s="107"/>
     </row>
-    <row r="31" spans="1:27">
-      <c r="A31" s="168"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="107"/>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A31" s="91"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="106"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11195,34 +11201,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="113"/>
-      <c r="Z31" s="153"/>
-      <c r="AA31" s="167"/>
+      <c r="X31" s="160"/>
+      <c r="Y31" s="101"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="108"/>
     </row>
-    <row r="32" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A32" s="168"/>
-      <c r="B32" s="93" t="s">
+    <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="91"/>
+      <c r="B32" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="124" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="122" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="90" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" s="108" t="s">
+      <c r="E32" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="111" t="s">
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="108" t="s">
+      <c r="I32" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J32" s="107" t="s">
+      <c r="J32" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11256,28 +11262,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="170" t="s">
+      <c r="X32" s="98" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y32" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="Y32" s="97" t="s">
+      <c r="Z32" s="94"/>
+      <c r="AA32" s="117" t="s">
         <v>109</v>
       </c>
-      <c r="Z32" s="119"/>
-      <c r="AA32" s="123" t="s">
-        <v>110</v>
-      </c>
     </row>
-    <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A33" s="168"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="122"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="107"/>
+    <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="91"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="106"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11309,36 +11315,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="171"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="153"/>
-      <c r="AA33" s="124"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="97"/>
+      <c r="Z33" s="95"/>
+      <c r="AA33" s="118"/>
     </row>
-    <row r="34" spans="1:29">
-      <c r="A34" s="109" t="s">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A34" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="93" t="s">
+      <c r="C34" s="123" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="105" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="104">
         <v>90</v>
       </c>
-      <c r="D34" s="90" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="108">
-        <v>90</v>
-      </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="111" t="s">
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="108" t="s">
+      <c r="I34" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="120" t="s">
+      <c r="J34" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11364,83 +11370,83 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="94"/>
-      <c r="Y34" s="96"/>
-      <c r="Z34" s="115"/>
-      <c r="AA34" s="123" t="s">
-        <v>111</v>
+      <c r="X34" s="111"/>
+      <c r="Y34" s="131"/>
+      <c r="Z34" s="116"/>
+      <c r="AA34" s="117" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
-      <c r="A35" s="109"/>
-      <c r="B35" s="148"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="108"/>
-      <c r="J35" s="120"/>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A35" s="92"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="102"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
       <c r="O35" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P35" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
       <c r="R35" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S35" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T35" s="19"/>
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="115"/>
-      <c r="AA35" s="124"/>
+      <c r="X35" s="111"/>
+      <c r="Y35" s="131"/>
+      <c r="Z35" s="116"/>
+      <c r="AA35" s="118"/>
     </row>
-    <row r="36" spans="1:29">
-      <c r="A36" s="109"/>
-      <c r="B36" s="148" t="s">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A36" s="92"/>
+      <c r="B36" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="93" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="90" t="s">
+      <c r="C36" s="123" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="108">
+      <c r="E36" s="104">
         <v>83</v>
       </c>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="111" t="s">
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="108" t="s">
+      <c r="I36" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="121" t="s">
+      <c r="J36" s="161" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11462,96 +11468,96 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="94" t="s">
+      <c r="X36" s="111" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y36" s="130" t="s">
         <v>113</v>
       </c>
-      <c r="Y36" s="95" t="s">
+      <c r="Z36" s="116"/>
+      <c r="AA36" s="117" t="s">
         <v>114</v>
       </c>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="123" t="s">
-        <v>115</v>
-      </c>
     </row>
-    <row r="37" spans="1:29">
-      <c r="A37" s="109"/>
-      <c r="B37" s="148"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="108"/>
-      <c r="J37" s="121"/>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A37" s="92"/>
+      <c r="B37" s="144"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="161"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
       <c r="P37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
       <c r="R37" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S37" s="58"/>
       <c r="T37" s="58"/>
       <c r="U37" s="58"/>
       <c r="V37" s="58"/>
       <c r="W37" s="59"/>
-      <c r="X37" s="137"/>
-      <c r="Y37" s="97"/>
-      <c r="Z37" s="119"/>
-      <c r="AA37" s="125"/>
+      <c r="X37" s="109"/>
+      <c r="Y37" s="96"/>
+      <c r="Z37" s="94"/>
+      <c r="AA37" s="153"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1">
-      <c r="A38" s="138"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="138"/>
-      <c r="N38" s="138"/>
-      <c r="O38" s="138"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="139"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="139"/>
-      <c r="T38" s="139"/>
-      <c r="U38" s="139"/>
-      <c r="V38" s="139"/>
-      <c r="W38" s="139"/>
-      <c r="X38" s="139"/>
-      <c r="Y38" s="139"/>
-      <c r="Z38" s="139"/>
-      <c r="AA38" s="139"/>
+    <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="147"/>
+      <c r="B38" s="147"/>
+      <c r="C38" s="147"/>
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="147"/>
+      <c r="O38" s="147"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="148"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148"/>
+      <c r="T38" s="148"/>
+      <c r="U38" s="148"/>
+      <c r="V38" s="148"/>
+      <c r="W38" s="148"/>
+      <c r="X38" s="148"/>
+      <c r="Y38" s="148"/>
+      <c r="Z38" s="148"/>
+      <c r="AA38" s="148"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
-      <c r="A39" s="141" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" s="141"/>
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="149" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="149"/>
       <c r="C39" s="60"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11578,12 +11584,12 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="27.6" customHeight="1">
+    <row r="40" spans="1:29" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
@@ -11592,13 +11598,13 @@
         <v>4</v>
       </c>
       <c r="E40" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="G40" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>8</v>
@@ -11619,7 +11625,7 @@
         <v>13</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>15</v>
@@ -11628,7 +11634,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R40" s="10" t="s">
         <v>18</v>
@@ -11661,35 +11667,35 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:29">
-      <c r="A41" s="142" t="s">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A41" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="145" t="s">
+      <c r="B41" s="151" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="152" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="146" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="147" t="s">
-        <v>125</v>
-      </c>
-      <c r="E41" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F41" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="G41" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="H41" s="160" t="s">
+      <c r="E41" s="121" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="121" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="121" t="s">
+        <v>94</v>
+      </c>
+      <c r="H41" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="140" t="s">
+      <c r="I41" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="149" t="s">
+      <c r="J41" s="138" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="63" t="s">
@@ -11731,25 +11737,25 @@
       <c r="W41" s="65">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="136"/>
-      <c r="Y41" s="131"/>
-      <c r="Z41" s="131"/>
-      <c r="AA41" s="124" t="s">
-        <v>124</v>
+      <c r="X41" s="158"/>
+      <c r="Y41" s="128"/>
+      <c r="Z41" s="128"/>
+      <c r="AA41" s="118" t="s">
+        <v>123</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="91"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="108"/>
-      <c r="J42" s="127"/>
+    <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="90"/>
+      <c r="B42" s="125"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="139"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11781,40 +11787,40 @@
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
-      <c r="X42" s="136"/>
-      <c r="Y42" s="131"/>
-      <c r="Z42" s="131"/>
-      <c r="AA42" s="126"/>
+      <c r="X42" s="158"/>
+      <c r="Y42" s="128"/>
+      <c r="Z42" s="128"/>
+      <c r="AA42" s="145"/>
     </row>
-    <row r="43" spans="1:29">
-      <c r="A43" s="144" t="s">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A43" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="91" t="s">
+      <c r="B43" s="125" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="105" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="92" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" s="90" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="F43" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="G43" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="H43" s="111" t="s">
+      <c r="E43" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="G43" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="H43" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="108" t="s">
+      <c r="I43" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="120" t="s">
+      <c r="J43" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11836,95 +11842,95 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="130" t="s">
+      <c r="X43" s="146" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y43" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="Y43" s="132" t="s">
+      <c r="Z43" s="140"/>
+      <c r="AA43" s="156" t="s">
         <v>129</v>
       </c>
-      <c r="Z43" s="133"/>
-      <c r="AA43" s="134" t="s">
-        <v>130</v>
-      </c>
     </row>
-    <row r="44" spans="1:29">
-      <c r="A44" s="144"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="159"/>
-      <c r="J44" s="120"/>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A44" s="136"/>
+      <c r="B44" s="125"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="112"/>
+      <c r="J44" s="102"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
       <c r="R44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T44" s="57"/>
       <c r="U44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="V44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W44" s="57"/>
-      <c r="X44" s="130"/>
-      <c r="Y44" s="132"/>
-      <c r="Z44" s="133"/>
-      <c r="AA44" s="134"/>
+      <c r="X44" s="146"/>
+      <c r="Y44" s="141"/>
+      <c r="Z44" s="140"/>
+      <c r="AA44" s="156"/>
     </row>
-    <row r="45" spans="1:29">
-      <c r="A45" s="144"/>
-      <c r="B45" s="91" t="s">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A45" s="136"/>
+      <c r="B45" s="125" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="105" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="92" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" s="90" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="F45" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="G45" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="H45" s="111" t="s">
+      <c r="E45" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="G45" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="H45" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="108" t="s">
+      <c r="I45" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="127" t="s">
+      <c r="J45" s="139" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11956,28 +11962,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="130"/>
-      <c r="Y45" s="132" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z45" s="135">
+      <c r="X45" s="146"/>
+      <c r="Y45" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z45" s="157">
         <v>46188</v>
       </c>
-      <c r="AA45" s="126" t="s">
-        <v>131</v>
+      <c r="AA45" s="145" t="s">
+        <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="16.5" customHeight="1">
-      <c r="A46" s="144"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="127"/>
+    <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="136"/>
+      <c r="B46" s="125"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="139"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12007,38 +12013,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="130"/>
-      <c r="Y46" s="133"/>
-      <c r="Z46" s="133"/>
-      <c r="AA46" s="126"/>
+      <c r="X46" s="146"/>
+      <c r="Y46" s="140"/>
+      <c r="Z46" s="140"/>
+      <c r="AA46" s="145"/>
     </row>
-    <row r="47" spans="1:29">
-      <c r="A47" s="144"/>
-      <c r="B47" s="91" t="s">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A47" s="136"/>
+      <c r="B47" s="125" t="s">
+        <v>133</v>
+      </c>
+      <c r="C47" s="137" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="105" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" s="90" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="F47" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="G47" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="H47" s="111" t="s">
+      <c r="E47" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="G47" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="H47" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="108" t="s">
+      <c r="I47" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="J47" s="127" t="s">
+      <c r="J47" s="139" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12080,24 +12086,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="130"/>
-      <c r="Y47" s="133"/>
-      <c r="Z47" s="133"/>
-      <c r="AA47" s="90" t="s">
-        <v>136</v>
+      <c r="X47" s="146"/>
+      <c r="Y47" s="140"/>
+      <c r="Z47" s="140"/>
+      <c r="AA47" s="105" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A48" s="144"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="127"/>
+    <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="136"/>
+      <c r="B48" s="125"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="139"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12130,40 +12136,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="130"/>
-      <c r="Y48" s="133"/>
-      <c r="Z48" s="133"/>
-      <c r="AA48" s="90"/>
+      <c r="X48" s="146"/>
+      <c r="Y48" s="140"/>
+      <c r="Z48" s="140"/>
+      <c r="AA48" s="105"/>
     </row>
-    <row r="49" spans="1:27">
-      <c r="A49" s="143" t="s">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A49" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="150" t="s">
+      <c r="C49" s="137" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="105" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="92" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="90" t="s">
-        <v>139</v>
-      </c>
-      <c r="E49" s="108">
+      <c r="E49" s="104">
         <v>74</v>
       </c>
-      <c r="F49" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="G49" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="H49" s="111" t="s">
+      <c r="F49" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="G49" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="H49" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="108" t="s">
+      <c r="I49" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="107" t="s">
+      <c r="J49" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12205,24 +12211,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="130"/>
-      <c r="Y49" s="132"/>
-      <c r="Z49" s="133"/>
-      <c r="AA49" s="126" t="s">
-        <v>140</v>
+      <c r="X49" s="146"/>
+      <c r="Y49" s="141"/>
+      <c r="Z49" s="140"/>
+      <c r="AA49" s="145" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:27">
-      <c r="A50" s="143"/>
-      <c r="B50" s="150"/>
-      <c r="C50" s="92"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="108"/>
-      <c r="J50" s="107"/>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A50" s="90"/>
+      <c r="B50" s="142"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="106"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12254,40 +12260,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="76"/>
-      <c r="X50" s="130"/>
-      <c r="Y50" s="132"/>
-      <c r="Z50" s="133"/>
-      <c r="AA50" s="126"/>
+      <c r="X50" s="146"/>
+      <c r="Y50" s="141"/>
+      <c r="Z50" s="140"/>
+      <c r="AA50" s="145"/>
     </row>
-    <row r="51" spans="1:27">
-      <c r="A51" s="144" t="s">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A51" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="91" t="s">
+      <c r="B51" s="125" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" s="137" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" s="105" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="92" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" s="90" t="s">
-        <v>142</v>
-      </c>
-      <c r="E51" s="108">
+      <c r="E51" s="104">
         <v>33.1</v>
       </c>
-      <c r="F51" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="G51" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="H51" s="111" t="s">
+      <c r="F51" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="G51" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="H51" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="108" t="s">
+      <c r="I51" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="107" t="s">
+      <c r="J51" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12321,24 +12327,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="130"/>
-      <c r="Y51" s="133"/>
-      <c r="Z51" s="133"/>
-      <c r="AA51" s="93" t="s">
-        <v>143</v>
+      <c r="X51" s="146"/>
+      <c r="Y51" s="140"/>
+      <c r="Z51" s="140"/>
+      <c r="AA51" s="123" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="15" thickBot="1">
-      <c r="A52" s="144"/>
-      <c r="B52" s="91"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="107"/>
+    <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="136"/>
+      <c r="B52" s="125"/>
+      <c r="C52" s="137"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="103"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="106"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12370,42 +12376,244 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="130"/>
-      <c r="Y52" s="133"/>
-      <c r="Z52" s="133"/>
-      <c r="AA52" s="93"/>
+      <c r="X52" s="146"/>
+      <c r="Y52" s="140"/>
+      <c r="Z52" s="140"/>
+      <c r="AA52" s="123"/>
     </row>
-    <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="58" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="60" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="62" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="64" spans="1:27" ht="14.45" customHeight="1"/>
-    <row r="66" ht="14.45" customHeight="1"/>
+    <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="Z10:Z11"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AA30:AA31"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="E30:G31"/>
@@ -12430,230 +12638,28 @@
     <mergeCell ref="I36:I37"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="X26:X27"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -12702,31 +12708,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="73">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    <cfRule type="expression" dxfId="66" priority="76" stopIfTrue="1">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="74">
+    <cfRule type="expression" dxfId="65" priority="75">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="74">
       <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="75">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="76" stopIfTrue="1">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    <cfRule type="expression" dxfId="63" priority="73">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="expression" dxfId="62" priority="69">
+    <cfRule type="expression" dxfId="62" priority="244">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="69">
       <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="242">
+    <cfRule type="expression" dxfId="60" priority="242">
       <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="243">
+    <cfRule type="expression" dxfId="59" priority="243">
       <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="244">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
@@ -12743,185 +12749,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="168">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="170">
+    <cfRule type="expression" dxfId="55" priority="172">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="170">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="171">
+    <cfRule type="expression" dxfId="53" priority="171">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="172">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="173" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="containsBlanks" dxfId="51" priority="99">
+    <cfRule type="expression" dxfId="51" priority="102">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="101">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="49" priority="99">
       <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="100">
+    <cfRule type="expression" dxfId="48" priority="100">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="101">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="102">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="103" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="containsBlanks" dxfId="46" priority="62">
+    <cfRule type="expression" dxfId="46" priority="66" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="65">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="63">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="43" priority="62">
       <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="63">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="64">
+    <cfRule type="expression" dxfId="42" priority="64">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="65">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="66" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="containsBlanks" dxfId="41" priority="11">
-      <formula>LEN(TRIM(N25))=0</formula>
+    <cfRule type="expression" dxfId="41" priority="13">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="12">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="13">
+    <cfRule type="containsBlanks" dxfId="39" priority="11">
+      <formula>LEN(TRIM(N25))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="20" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="17">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="19">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="35" priority="16">
+      <formula>LEN(TRIM(N25))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="18">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="14">
+    <cfRule type="expression" dxfId="32" priority="14">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="15" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="36" priority="16">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="17">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="18">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="19">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="containsBlanks" dxfId="31" priority="57">
+    <cfRule type="expression" dxfId="31" priority="60">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="61" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="29" priority="57">
       <formula>LEN(TRIM(N44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="58">
+    <cfRule type="expression" dxfId="28" priority="58">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="59">
+    <cfRule type="expression" dxfId="27" priority="59">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="60">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="61" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="containsBlanks" dxfId="26" priority="21">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="26" priority="25" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="22">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="24">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="24">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="22">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="22" priority="21">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="1">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="5">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="20" priority="2">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="20" priority="4">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="3">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="4">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="5">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="17" priority="2">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="containsBlanks" dxfId="16" priority="6">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="16" priority="10" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="7">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="9">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="8">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="9">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="7">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="10" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="12" priority="6">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="containsBlanks" dxfId="11" priority="47">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="11" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="48">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="50">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="49">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="50">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="48">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="7" priority="47">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="containsBlanks" dxfId="6" priority="42">
+    <cfRule type="expression" dxfId="6" priority="43">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="5" priority="42">
       <formula>LEN(TRIM(W44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="43">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="44">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="46" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="45">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="44">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -12972,6 +12978,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13109,40 +13135,41 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F488CD-71A3-46BB-878D-37FDAEEAEE94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF732A51-DEFE-4FD4-960B-551AC5CA7313}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3219" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A8860E4-9AF7-475C-9DE7-CE9E67B41F90}"/>
+  <xr:revisionPtr revIDLastSave="3221" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86449509-AF17-4824-B839-5CB6DCB808DF}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="33225" yWindow="1230" windowWidth="14400" windowHeight="8175" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" state="hidden" r:id="rId1"/>
     <sheet name="AOP Critical" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -828,11 +828,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="mmm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="mmm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1320,7 +1320,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1331,14 +1331,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1368,7 +1368,7 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1431,7 +1431,7 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1440,13 +1440,13 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1470,13 +1470,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1513,21 +1513,21 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1536,31 +1536,31 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1862,7 +1862,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1883,7 +1911,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1946,83 +2002,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDA9694"/>
         </patternFill>
       </fill>
@@ -2045,111 +2024,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDEDDF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2198,6 +2072,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -2206,6 +2094,118 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDA9694"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2234,6 +2234,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDEDDF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2283,13 +2290,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDA9694"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2447,7 +2447,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>715645</xdr:colOff>
+      <xdr:colOff>712470</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>18415</xdr:rowOff>
     </xdr:to>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="S26" s="75">
         <f>IF('AOP Critical'!T19="","",'AOP Critical'!T19)</f>
-        <v>4.92</v>
+        <v>5.0119999999999996</v>
       </c>
       <c r="T26" s="75" t="str">
         <f>IF('AOP Critical'!U19="","",'AOP Critical'!U19)</f>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="AA18" s="134"/>
     </row>
-    <row r="19" spans="1:27" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="92"/>
       <c r="B19" s="123"/>
       <c r="C19" s="123"/>
@@ -10513,8 +10513,8 @@
       <c r="S19" s="86">
         <v>3.895</v>
       </c>
-      <c r="T19" s="47">
-        <v>4.92</v>
+      <c r="T19" s="86">
+        <v>5.0119999999999996</v>
       </c>
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
@@ -12708,31 +12708,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="76" stopIfTrue="1">
-      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
+    <cfRule type="expression" dxfId="66" priority="73">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="75">
+    <cfRule type="expression" dxfId="65" priority="74">
+      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="75">
       <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="74">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="73">
-      <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
+    <cfRule type="expression" dxfId="63" priority="76" stopIfTrue="1">
+      <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="expression" dxfId="62" priority="244">
-      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="69">
+    <cfRule type="expression" dxfId="62" priority="69">
       <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="242">
+    <cfRule type="expression" dxfId="61" priority="242">
       <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="243">
+    <cfRule type="expression" dxfId="60" priority="243">
       <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="244">
+      <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
@@ -12749,185 +12749,185 @@
     <cfRule type="containsBlanks" dxfId="56" priority="168">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="172">
-      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="170">
+    <cfRule type="expression" dxfId="55" priority="170">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="171">
+    <cfRule type="expression" dxfId="54" priority="171">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="172">
+      <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="173" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="expression" dxfId="51" priority="102">
-      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
+    <cfRule type="containsBlanks" dxfId="51" priority="99">
+      <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="101">
+    <cfRule type="expression" dxfId="50" priority="100">
+      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="101">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="49" priority="99">
-      <formula>LEN(TRIM(L52))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="100">
-      <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
+    <cfRule type="expression" dxfId="48" priority="102">
+      <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="103" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="expression" dxfId="46" priority="66" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
+    <cfRule type="containsBlanks" dxfId="46" priority="62">
+      <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="65">
+    <cfRule type="expression" dxfId="45" priority="63">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="64">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="65">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="63">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="43" priority="62">
-      <formula>LEN(TRIM(L25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="64">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
+    <cfRule type="expression" dxfId="42" priority="66" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="41" priority="13">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    <cfRule type="containsBlanks" dxfId="41" priority="11">
+      <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="12">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="39" priority="11">
+    <cfRule type="expression" dxfId="39" priority="13">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="14">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="15" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="36" priority="16">
       <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="20" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="17">
+    <cfRule type="expression" dxfId="35" priority="17">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="19">
+    <cfRule type="expression" dxfId="34" priority="18">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="19">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="35" priority="16">
-      <formula>LEN(TRIM(N25))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="18">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="14">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="expression" dxfId="31" priority="60">
+    <cfRule type="containsBlanks" dxfId="31" priority="57">
+      <formula>LEN(TRIM(N44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="58">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="59">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="60">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="61" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="29" priority="57">
-      <formula>LEN(TRIM(N44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="58">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="59">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="expression" dxfId="26" priority="25" stopIfTrue="1">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
+    <cfRule type="containsBlanks" dxfId="26" priority="21">
+      <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="24">
-      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
+    <cfRule type="expression" dxfId="25" priority="22">
+      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="22">
-      <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="22" priority="21">
-      <formula>LEN(TRIM(Q25))=0</formula>
+    <cfRule type="expression" dxfId="22" priority="25" stopIfTrue="1">
+      <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="5">
-      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="4">
-      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
+    <cfRule type="containsBlanks" dxfId="20" priority="2">
+      <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="3">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="1">
-      <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
+    <cfRule type="expression" dxfId="18" priority="4">
+      <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="17" priority="2">
-      <formula>LEN(TRIM(Q37))=0</formula>
+    <cfRule type="expression" dxfId="17" priority="5">
+      <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="expression" dxfId="16" priority="10" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
+    <cfRule type="containsBlanks" dxfId="16" priority="6">
+      <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="9">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
+    <cfRule type="expression" dxfId="15" priority="7">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="8">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
+    <cfRule type="expression" dxfId="13" priority="9">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="12" priority="6">
-      <formula>LEN(TRIM(Q44))=0</formula>
+    <cfRule type="expression" dxfId="12" priority="10" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="expression" dxfId="11" priority="51" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
+    <cfRule type="containsBlanks" dxfId="11" priority="47">
+      <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="50">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
+    <cfRule type="expression" dxfId="10" priority="48">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="49">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="48">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
+    <cfRule type="expression" dxfId="8" priority="50">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="7" priority="47">
-      <formula>LEN(TRIM(T44))=0</formula>
+    <cfRule type="expression" dxfId="7" priority="51" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="expression" dxfId="6" priority="43">
+    <cfRule type="containsBlanks" dxfId="6" priority="42">
+      <formula>LEN(TRIM(W44))=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="43">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="5" priority="42">
-      <formula>LEN(TRIM(W44))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="46" stopIfTrue="1">
-      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
+    <cfRule type="expression" dxfId="4" priority="44">
+      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="45">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="44">
-      <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
+    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
+      <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
@@ -12978,26 +12978,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13135,24 +13115,48 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BA554D2-8EEF-404F-8AFB-A47DCAC86FAD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -13160,7 +13164,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
@@ -13168,10 +13172,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF732A51-DEFE-4FD4-960B-551AC5CA7313}"/>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{1a407a2d-7675-4d17-8692-b3ac285306e4}" enabled="0" method="" siteId="{1a407a2d-7675-4d17-8692-b3ac285306e4}" removed="1"/>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3221" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86449509-AF17-4824-B839-5CB6DCB808DF}"/>
+  <xr:revisionPtr revIDLastSave="3222" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE0314EB-60F3-4B25-B9B1-52581604284F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
@@ -5953,9 +5953,9 @@
         <f>IF('AOP Critical'!S42="","",'AOP Critical'!S42)</f>
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="S12" s="73" t="str">
+      <c r="S12" s="73">
         <f>IF('AOP Critical'!T42="","",'AOP Critical'!T42)</f>
-        <v/>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="T12" s="73" t="str">
         <f>IF('AOP Critical'!U42="","",'AOP Critical'!U42)</f>
@@ -11783,7 +11783,9 @@
       <c r="S42" s="57">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="T42" s="57"/>
+      <c r="T42" s="57">
+        <v>1.7000000000000001E-2</v>
+      </c>
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
@@ -13136,7 +13138,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BA554D2-8EEF-404F-8AFB-A47DCAC86FAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F13D5286-4418-4512-B027-21DE0652EFE6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13138,7 +13138,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F13D5286-4418-4512-B027-21DE0652EFE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5245F4-B03F-4E5D-AA1F-5F641D3F41D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3222" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE0314EB-60F3-4B25-B9B1-52581604284F}"/>
+  <xr:revisionPtr revIDLastSave="3233" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAE97006-85EC-4024-8602-2E985E083A89}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mastersheet" sheetId="5" state="hidden" r:id="rId1"/>
@@ -586,9 +586,6 @@
     <t>Increase contract penetration %</t>
   </si>
   <si>
-    <t>0.9% Gap VS AOP. YoY improvement by 0.4%. Expected turnaround is Sep 2026. GRC CP% dropped significantly. NAR to catch up in Q3</t>
-  </si>
-  <si>
     <t>Funnel focus actions driven across regions for same</t>
   </si>
   <si>
@@ -822,17 +819,20 @@
   <si>
     <t>YTD Sept Productivity no's on track.Good Realization from E&amp;E savings of Pune and also a gap reduction of R&amp;D Budget YTD.</t>
   </si>
+  <si>
+    <t>0.8% Gap VS AOP. YoY improvement by 0.7% excluding GRC, Win back campaign impact in Q4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="mmm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="mmm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1320,9 +1320,9 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1331,14 +1331,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1368,87 +1368,87 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1470,13 +1470,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1513,21 +1513,21 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1536,31 +1536,31 @@
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1569,245 +1569,242 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6296,9 +6293,9 @@
         <f>IF('AOP Critical'!S14="","",'AOP Critical'!S14)</f>
         <v>0.54510000000000003</v>
       </c>
-      <c r="S17" s="72" t="str">
+      <c r="S17" s="72">
         <f>IF('AOP Critical'!T14="","",'AOP Critical'!T14)</f>
-        <v/>
+        <v>0.54610000000000003</v>
       </c>
       <c r="T17" s="72" t="str">
         <f>IF('AOP Critical'!U14="","",'AOP Critical'!U14)</f>
@@ -6386,9 +6383,9 @@
         <f>IF('AOP Critical'!S15="","",'AOP Critical'!S15)</f>
         <v>0.5363</v>
       </c>
-      <c r="S18" s="72" t="str">
+      <c r="S18" s="72">
         <f>IF('AOP Critical'!T15="","",'AOP Critical'!T15)</f>
-        <v/>
+        <v>0.53749999999999998</v>
       </c>
       <c r="T18" s="72" t="str">
         <f>IF('AOP Critical'!U15="","",'AOP Critical'!U15)</f>
@@ -6566,9 +6563,9 @@
         <f>IF('AOP Critical'!S50="","",'AOP Critical'!S50)</f>
         <v>0.74450000000000005</v>
       </c>
-      <c r="S20" s="73" t="str">
+      <c r="S20" s="73">
         <f>IF('AOP Critical'!T50="","",'AOP Critical'!T50)</f>
-        <v/>
+        <v>0.74770000000000003</v>
       </c>
       <c r="T20" s="73" t="str">
         <f>IF('AOP Critical'!U50="","",'AOP Critical'!U50)</f>
@@ -9542,12 +9539,11 @@
     <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.7265625" customWidth="1"/>
-    <col min="12" max="12" width="5.54296875" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="6.81640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="5.54296875" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" customWidth="1"/>
     <col min="14" max="14" width="6.26953125" customWidth="1"/>
-    <col min="15" max="15" width="7.26953125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.1796875" hidden="1" customWidth="1"/>
-    <col min="17" max="22" width="6.1796875" customWidth="1"/>
+    <col min="15" max="15" width="7.26953125" customWidth="1"/>
+    <col min="16" max="22" width="6.1796875" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
     <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
     <col min="25" max="25" width="68.1796875" customWidth="1"/>
@@ -9577,10 +9573,10 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="162" t="s">
+      <c r="A3" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="162"/>
+      <c r="B3" s="108"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9601,36 +9597,36 @@
       <c r="AA3" s="14"/>
     </row>
     <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="163" t="str">
+      <c r="A4" s="110" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="163"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="163"/>
-      <c r="R4" s="163"/>
-      <c r="S4" s="163"/>
-      <c r="T4" s="163"/>
-      <c r="U4" s="163"/>
-      <c r="V4" s="163"/>
-      <c r="W4" s="163"/>
-      <c r="X4" s="163"/>
-      <c r="Y4" s="163"/>
-      <c r="Z4" s="163"/>
-      <c r="AA4" s="163"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110"/>
+      <c r="V4" s="110"/>
+      <c r="W4" s="110"/>
+      <c r="X4" s="110"/>
+      <c r="Y4" s="110"/>
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
     </row>
     <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="88" t="s">
@@ -9645,11 +9641,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="164" t="s">
+      <c r="E5" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
       <c r="H5" s="89" t="s">
         <v>8</v>
       </c>
@@ -9712,30 +9708,30 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="137" t="s">
+      <c r="C6" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="105" t="s">
+      <c r="D6" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="104">
+      <c r="E6" s="106">
         <v>10</v>
       </c>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="103" t="s">
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="104" t="s">
+      <c r="I6" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="106" t="s">
+      <c r="J6" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9777,24 +9773,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="101"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="117" t="s">
+      <c r="X6" s="104"/>
+      <c r="Y6" s="111"/>
+      <c r="Z6" s="111"/>
+      <c r="AA6" s="121" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="106"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="105"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9828,34 +9824,34 @@
       <c r="U7" s="52"/>
       <c r="V7" s="52"/>
       <c r="W7" s="52"/>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="118"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
+      <c r="AA7" s="122"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
-      <c r="B8" s="125" t="s">
+      <c r="A8" s="107"/>
+      <c r="B8" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="137" t="s">
+      <c r="C8" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="105" t="s">
+      <c r="D8" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="104">
+      <c r="E8" s="106">
         <v>90</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="103" t="s">
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="106" t="s">
+      <c r="J8" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9887,28 +9883,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="111"/>
-      <c r="Y8" s="130" t="s">
+      <c r="X8" s="94"/>
+      <c r="Y8" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="115">
+      <c r="Z8" s="112">
         <v>46231</v>
       </c>
-      <c r="AA8" s="117" t="s">
+      <c r="AA8" s="121" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="106"/>
+      <c r="A9" s="107"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="105"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9942,34 +9938,34 @@
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="118"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="96"/>
+      <c r="Z9" s="113"/>
+      <c r="AA9" s="122"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A10" s="92"/>
-      <c r="B10" s="125" t="s">
+      <c r="A10" s="107"/>
+      <c r="B10" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="137" t="s">
+      <c r="C10" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="105" t="s">
+      <c r="D10" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="106">
         <v>1</v>
       </c>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="103" t="s">
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="104" t="s">
+      <c r="I10" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="106" t="s">
+      <c r="J10" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -10003,24 +9999,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="111"/>
-      <c r="Y10" s="119"/>
-      <c r="Z10" s="165"/>
-      <c r="AA10" s="117" t="s">
+      <c r="X10" s="94"/>
+      <c r="Y10" s="161"/>
+      <c r="Z10" s="115"/>
+      <c r="AA10" s="121" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="92"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="106"/>
+      <c r="A11" s="107"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="105"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10054,36 +10050,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="111"/>
-      <c r="Y11" s="120"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="118"/>
+      <c r="X11" s="94"/>
+      <c r="Y11" s="162"/>
+      <c r="Z11" s="116"/>
+      <c r="AA11" s="122"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="105" t="s">
+      <c r="D12" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="104">
+      <c r="E12" s="106">
         <v>84</v>
       </c>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="103" t="s">
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="104" t="s">
+      <c r="I12" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="106" t="s">
+      <c r="J12" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10125,24 +10121,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="129"/>
-      <c r="Y12" s="130"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="117" t="s">
+      <c r="X12" s="94"/>
+      <c r="Y12" s="95"/>
+      <c r="Z12" s="96"/>
+      <c r="AA12" s="121" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A13" s="92"/>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="106"/>
+      <c r="A13" s="107"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="105"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10174,34 +10170,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="129"/>
-      <c r="Y13" s="131"/>
-      <c r="Z13" s="131"/>
-      <c r="AA13" s="118"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="96"/>
+      <c r="Z13" s="96"/>
+      <c r="AA13" s="122"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="92"/>
-      <c r="B14" s="123" t="s">
+      <c r="A14" s="107"/>
+      <c r="B14" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="C14" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="105" t="s">
+      <c r="D14" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="104">
+      <c r="E14" s="106">
         <v>54.6</v>
       </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="103" t="s">
+      <c r="F14" s="106"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="104" t="s">
+      <c r="I14" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="106" t="s">
+      <c r="J14" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10231,30 +10227,32 @@
       <c r="S14" s="38">
         <v>0.54510000000000003</v>
       </c>
-      <c r="T14" s="38"/>
+      <c r="T14" s="38">
+        <v>0.54610000000000003</v>
+      </c>
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="109" t="s">
+      <c r="X14" s="94" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y14" s="150" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="100" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z14" s="100"/>
-      <c r="AA14" s="127"/>
+      <c r="Z14" s="150"/>
+      <c r="AA14" s="149"/>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="92"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="106"/>
+      <c r="A15" s="107"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="105"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10282,40 +10280,42 @@
       <c r="S15" s="79">
         <v>0.5363</v>
       </c>
-      <c r="T15" s="32"/>
+      <c r="T15" s="79">
+        <v>0.53749999999999998</v>
+      </c>
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-      <c r="AA15" s="128"/>
+      <c r="X15" s="94"/>
+      <c r="Y15" s="111"/>
+      <c r="Z15" s="111"/>
+      <c r="AA15" s="129"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="93" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="D16" s="90" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="105" t="s">
+      <c r="E16" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="103" t="s">
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="104" t="s">
+      <c r="I16" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10349,28 +10349,28 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="111" t="s">
+      <c r="X16" s="94" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y16" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="Y16" s="130" t="s">
+      <c r="Z16" s="113"/>
+      <c r="AA16" s="121" t="s">
         <v>78</v>
-      </c>
-      <c r="Z16" s="116"/>
-      <c r="AA16" s="117" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A17" s="92"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="106"/>
+      <c r="A17" s="107"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="105"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10402,34 +10402,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="111"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="116"/>
-      <c r="AA17" s="118"/>
+      <c r="X17" s="94"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="113"/>
+      <c r="AA17" s="122"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A18" s="92"/>
-      <c r="B18" s="123" t="s">
+      <c r="A18" s="107"/>
+      <c r="B18" s="93" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="123" t="s">
+      <c r="E18" s="106" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="106"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="106" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="103" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="104" t="s">
-        <v>82</v>
-      </c>
-      <c r="J18" s="106" t="s">
+      <c r="J18" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10466,26 +10466,26 @@
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="135" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y18" s="135"/>
-      <c r="Z18" s="132">
+      <c r="X18" s="155" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y18" s="155"/>
+      <c r="Z18" s="152">
         <v>46108</v>
       </c>
-      <c r="AA18" s="134"/>
+      <c r="AA18" s="154"/>
     </row>
     <row r="19" spans="1:27" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="92"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="106"/>
+      <c r="A19" s="107"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="105"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
@@ -10519,34 +10519,34 @@
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="50"/>
-      <c r="X19" s="135"/>
-      <c r="Y19" s="135"/>
-      <c r="Z19" s="133"/>
-      <c r="AA19" s="134"/>
+      <c r="X19" s="155"/>
+      <c r="Y19" s="155"/>
+      <c r="Z19" s="153"/>
+      <c r="AA19" s="154"/>
     </row>
     <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="92"/>
-      <c r="B20" s="123" t="s">
+      <c r="A20" s="107"/>
+      <c r="B20" s="93" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="93" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="105" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="103" t="s">
+      <c r="E20" s="106" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="104" t="s">
+      <c r="I20" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="106" t="s">
+      <c r="J20" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10580,28 +10580,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="170" t="s">
+      <c r="X20" s="169" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y20" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="Y20" s="167" t="s">
+      <c r="Z20" s="151"/>
+      <c r="AA20" s="123" t="s">
         <v>86</v>
-      </c>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="153" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="92"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="106"/>
+      <c r="A21" s="107"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="105"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10633,36 +10633,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="171"/>
-      <c r="Y21" s="168"/>
-      <c r="Z21" s="94"/>
-      <c r="AA21" s="153"/>
+      <c r="X21" s="170"/>
+      <c r="Y21" s="100"/>
+      <c r="Z21" s="117"/>
+      <c r="AA21" s="123"/>
     </row>
     <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="92" t="s">
+      <c r="A22" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="93" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="120" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="124" t="s">
+      <c r="D22" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="123" t="s">
+      <c r="E22" s="106">
         <v>90</v>
       </c>
-      <c r="E22" s="104">
-        <v>90</v>
-      </c>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="103" t="s">
+      <c r="F22" s="106"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="104" t="s">
+      <c r="I22" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="106" t="s">
+      <c r="J22" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10704,24 +10704,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="169"/>
-      <c r="Y22" s="130"/>
-      <c r="Z22" s="115">
+      <c r="X22" s="103"/>
+      <c r="Y22" s="95"/>
+      <c r="Z22" s="112">
         <v>46257</v>
       </c>
-      <c r="AA22" s="113"/>
+      <c r="AA22" s="159"/>
     </row>
     <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="93"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="106"/>
+      <c r="A23" s="166"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="105"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10753,40 +10753,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="131"/>
-      <c r="Z23" s="116"/>
-      <c r="AA23" s="114"/>
+      <c r="X23" s="104"/>
+      <c r="Y23" s="96"/>
+      <c r="Z23" s="113"/>
+      <c r="AA23" s="160"/>
     </row>
     <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="93" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="120" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="124" t="s">
+      <c r="D24" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="105" t="s">
+      <c r="E24" s="106" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="G24" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="103" t="s">
+      <c r="F24" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="G24" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="104" t="s">
+      <c r="I24" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="102" t="s">
+      <c r="J24" s="118" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10798,109 +10798,109 @@
         <v>0.104</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="38">
         <v>0.11799999999999999</v>
       </c>
       <c r="R24" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S24" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T24" s="36"/>
       <c r="U24" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="V24" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="W24" s="39"/>
+      <c r="X24" s="135"/>
+      <c r="Y24" s="150"/>
+      <c r="Z24" s="117"/>
+      <c r="AA24" s="121" t="s">
         <v>95</v>
-      </c>
-      <c r="V24" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="W24" s="39"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="100"/>
-      <c r="Z24" s="94"/>
-      <c r="AA24" s="117" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="102"/>
+      <c r="A25" s="165"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="118"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N25" s="52">
         <v>0.115</v>
       </c>
       <c r="O25" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P25" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q25" s="17">
         <v>0.121</v>
       </c>
       <c r="R25" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S25" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T25" s="57"/>
       <c r="U25" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="V25" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W25" s="57"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="118"/>
+      <c r="X25" s="104"/>
+      <c r="Y25" s="111"/>
+      <c r="Z25" s="151"/>
+      <c r="AA25" s="122"/>
     </row>
     <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="91"/>
-      <c r="B26" s="125" t="s">
+      <c r="A26" s="165"/>
+      <c r="B26" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="158" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="126" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="105" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="104">
+      <c r="E26" s="106">
         <v>34</v>
       </c>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="103" t="s">
+      <c r="F26" s="156"/>
+      <c r="G26" s="156"/>
+      <c r="H26" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="104" t="s">
+      <c r="I26" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="106" t="s">
+      <c r="J26" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10934,24 +10934,24 @@
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="131"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="117" t="s">
-        <v>99</v>
+      <c r="X26" s="94"/>
+      <c r="Y26" s="96"/>
+      <c r="Z26" s="113"/>
+      <c r="AA26" s="121" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="91"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="106"/>
+      <c r="A27" s="165"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="158"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="156"/>
+      <c r="G27" s="156"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="105"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10983,34 +10983,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="131"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="118"/>
+      <c r="X27" s="94"/>
+      <c r="Y27" s="96"/>
+      <c r="Z27" s="113"/>
+      <c r="AA27" s="122"/>
     </row>
     <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="91"/>
-      <c r="B28" s="105" t="s">
+      <c r="A28" s="165"/>
+      <c r="B28" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" s="105" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="103" t="s">
+      <c r="E28" s="106" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="106"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="106" t="s">
+      <c r="J28" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11044,26 +11044,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="159" t="s">
+      <c r="X28" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y28" s="97"/>
+      <c r="Z28" s="117"/>
+      <c r="AA28" s="126" t="s">
         <v>102</v>
-      </c>
-      <c r="Y28" s="96"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="154" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="91"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="106"/>
+      <c r="A29" s="165"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="105"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11095,32 +11095,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="160"/>
-      <c r="Y29" s="97"/>
-      <c r="Z29" s="95"/>
-      <c r="AA29" s="155"/>
+      <c r="X29" s="102"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="151"/>
+      <c r="AA29" s="127"/>
     </row>
     <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="91"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="105" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="103" t="s">
+      <c r="A30" s="165"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="90" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="106" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="104" t="s">
+      <c r="I30" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11154,22 +11154,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="159"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="94"/>
-      <c r="AA30" s="107"/>
+      <c r="X30" s="101"/>
+      <c r="Y30" s="150"/>
+      <c r="Z30" s="117"/>
+      <c r="AA30" s="163"/>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A31" s="91"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="106"/>
+      <c r="A31" s="165"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="105"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11201,34 +11201,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="160"/>
-      <c r="Y31" s="101"/>
-      <c r="Z31" s="95"/>
-      <c r="AA31" s="108"/>
+      <c r="X31" s="102"/>
+      <c r="Y31" s="111"/>
+      <c r="Z31" s="151"/>
+      <c r="AA31" s="164"/>
     </row>
     <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="91"/>
-      <c r="B32" s="123" t="s">
+      <c r="A32" s="165"/>
+      <c r="B32" s="93" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="124" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="105" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="103" t="s">
+      <c r="E32" s="106" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="106"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="104" t="s">
-        <v>82</v>
-      </c>
-      <c r="J32" s="106" t="s">
+      <c r="I32" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="J32" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11262,28 +11262,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="98" t="s">
+      <c r="X32" s="167" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y32" s="97" t="s">
         <v>107</v>
       </c>
-      <c r="Y32" s="96" t="s">
+      <c r="Z32" s="117"/>
+      <c r="AA32" s="121" t="s">
         <v>108</v>
-      </c>
-      <c r="Z32" s="94"/>
-      <c r="AA32" s="117" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="106"/>
+      <c r="A33" s="165"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="120"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="105"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11315,36 +11315,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="97"/>
-      <c r="Z33" s="95"/>
-      <c r="AA33" s="118"/>
+      <c r="X33" s="168"/>
+      <c r="Y33" s="98"/>
+      <c r="Z33" s="151"/>
+      <c r="AA33" s="122"/>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A34" s="92" t="s">
+      <c r="A34" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="144" t="s">
+      <c r="B34" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="123" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" s="105" t="s">
+      <c r="C34" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="104">
+      <c r="E34" s="106">
         <v>90</v>
       </c>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="103" t="s">
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="104" t="s">
+      <c r="I34" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="102" t="s">
+      <c r="J34" s="118" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11370,83 +11370,83 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="111"/>
-      <c r="Y34" s="131"/>
-      <c r="Z34" s="116"/>
-      <c r="AA34" s="117" t="s">
-        <v>110</v>
+      <c r="X34" s="94"/>
+      <c r="Y34" s="96"/>
+      <c r="Z34" s="113"/>
+      <c r="AA34" s="121" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A35" s="92"/>
-      <c r="B35" s="144"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="102"/>
+      <c r="A35" s="107"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="118"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
       <c r="O35" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P35" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
       <c r="R35" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S35" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T35" s="19"/>
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="131"/>
-      <c r="Z35" s="116"/>
-      <c r="AA35" s="118"/>
+      <c r="X35" s="94"/>
+      <c r="Y35" s="96"/>
+      <c r="Z35" s="113"/>
+      <c r="AA35" s="122"/>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A36" s="92"/>
-      <c r="B36" s="144" t="s">
+      <c r="A36" s="107"/>
+      <c r="B36" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="123" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="105" t="s">
+      <c r="C36" s="93" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="104">
+      <c r="E36" s="106">
         <v>83</v>
       </c>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="103" t="s">
+      <c r="F36" s="106"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="104" t="s">
+      <c r="I36" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="161" t="s">
+      <c r="J36" s="119" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11468,96 +11468,96 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="111" t="s">
+      <c r="X36" s="94" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y36" s="95" t="s">
         <v>112</v>
       </c>
-      <c r="Y36" s="130" t="s">
+      <c r="Z36" s="113"/>
+      <c r="AA36" s="121" t="s">
         <v>113</v>
-      </c>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="117" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A37" s="92"/>
-      <c r="B37" s="144"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="161"/>
+      <c r="A37" s="107"/>
+      <c r="B37" s="146"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="119"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N37" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
       <c r="P37" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
       <c r="R37" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S37" s="58"/>
       <c r="T37" s="58"/>
       <c r="U37" s="58"/>
       <c r="V37" s="58"/>
       <c r="W37" s="59"/>
-      <c r="X37" s="109"/>
-      <c r="Y37" s="96"/>
-      <c r="Z37" s="94"/>
-      <c r="AA37" s="153"/>
+      <c r="X37" s="135"/>
+      <c r="Y37" s="97"/>
+      <c r="Z37" s="117"/>
+      <c r="AA37" s="123"/>
     </row>
     <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="147"/>
-      <c r="B38" s="147"/>
-      <c r="C38" s="147"/>
-      <c r="D38" s="147"/>
-      <c r="E38" s="147"/>
-      <c r="F38" s="147"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="147"/>
-      <c r="I38" s="147"/>
-      <c r="J38" s="147"/>
-      <c r="K38" s="147"/>
-      <c r="L38" s="147"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="147"/>
-      <c r="O38" s="147"/>
-      <c r="P38" s="148"/>
-      <c r="Q38" s="148"/>
-      <c r="R38" s="148"/>
-      <c r="S38" s="148"/>
-      <c r="T38" s="148"/>
-      <c r="U38" s="148"/>
-      <c r="V38" s="148"/>
-      <c r="W38" s="148"/>
-      <c r="X38" s="148"/>
-      <c r="Y38" s="148"/>
-      <c r="Z38" s="148"/>
-      <c r="AA38" s="148"/>
+      <c r="A38" s="136"/>
+      <c r="B38" s="136"/>
+      <c r="C38" s="136"/>
+      <c r="D38" s="136"/>
+      <c r="E38" s="136"/>
+      <c r="F38" s="136"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="136"/>
+      <c r="I38" s="136"/>
+      <c r="J38" s="136"/>
+      <c r="K38" s="136"/>
+      <c r="L38" s="136"/>
+      <c r="M38" s="136"/>
+      <c r="N38" s="136"/>
+      <c r="O38" s="136"/>
+      <c r="P38" s="137"/>
+      <c r="Q38" s="137"/>
+      <c r="R38" s="137"/>
+      <c r="S38" s="137"/>
+      <c r="T38" s="137"/>
+      <c r="U38" s="137"/>
+      <c r="V38" s="137"/>
+      <c r="W38" s="137"/>
+      <c r="X38" s="137"/>
+      <c r="Y38" s="137"/>
+      <c r="Z38" s="137"/>
+      <c r="AA38" s="137"/>
     </row>
     <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="149" t="s">
-        <v>116</v>
-      </c>
-      <c r="B39" s="149"/>
+      <c r="A39" s="139" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="139"/>
       <c r="C39" s="60"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11589,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
@@ -11598,13 +11598,13 @@
         <v>4</v>
       </c>
       <c r="E40" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="G40" s="10" t="s">
         <v>119</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>120</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>8</v>
@@ -11625,7 +11625,7 @@
         <v>13</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>15</v>
@@ -11634,7 +11634,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R40" s="10" t="s">
         <v>18</v>
@@ -11668,34 +11668,34 @@
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A41" s="150" t="s">
+      <c r="A41" s="140" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="151" t="s">
+      <c r="B41" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="144" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="145" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="152" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="143" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" s="121" t="s">
-        <v>94</v>
-      </c>
-      <c r="F41" s="121" t="s">
-        <v>94</v>
-      </c>
-      <c r="G41" s="121" t="s">
-        <v>94</v>
-      </c>
-      <c r="H41" s="122" t="s">
+      <c r="E41" s="138" t="s">
+        <v>93</v>
+      </c>
+      <c r="F41" s="138" t="s">
+        <v>93</v>
+      </c>
+      <c r="G41" s="138" t="s">
+        <v>93</v>
+      </c>
+      <c r="H41" s="157" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="121" t="s">
+      <c r="I41" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="138" t="s">
+      <c r="J41" s="147" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="63" t="s">
@@ -11737,25 +11737,25 @@
       <c r="W41" s="65">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="158"/>
-      <c r="Y41" s="128"/>
-      <c r="Z41" s="128"/>
-      <c r="AA41" s="118" t="s">
-        <v>123</v>
+      <c r="X41" s="134"/>
+      <c r="Y41" s="129"/>
+      <c r="Z41" s="129"/>
+      <c r="AA41" s="122" t="s">
+        <v>122</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
     <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="90"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="137"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="139"/>
+      <c r="A42" s="141"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="92"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="106"/>
+      <c r="H42" s="109"/>
+      <c r="I42" s="106"/>
+      <c r="J42" s="125"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11789,40 +11789,40 @@
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
-      <c r="X42" s="158"/>
-      <c r="Y42" s="128"/>
-      <c r="Z42" s="128"/>
-      <c r="AA42" s="145"/>
+      <c r="X42" s="134"/>
+      <c r="Y42" s="129"/>
+      <c r="Z42" s="129"/>
+      <c r="AA42" s="124"/>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A43" s="136" t="s">
+      <c r="A43" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="125" t="s">
+      <c r="B43" s="91" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="C43" s="137" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" s="105" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="F43" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="G43" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="H43" s="103" t="s">
+      <c r="E43" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="G43" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="H43" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="104" t="s">
+      <c r="I43" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="102" t="s">
+      <c r="J43" s="118" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11844,95 +11844,95 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="146" t="s">
+      <c r="X43" s="128" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y43" s="130" t="s">
         <v>127</v>
       </c>
-      <c r="Y43" s="141" t="s">
+      <c r="Z43" s="131"/>
+      <c r="AA43" s="132" t="s">
         <v>128</v>
-      </c>
-      <c r="Z43" s="140"/>
-      <c r="AA43" s="156" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A44" s="136"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="112"/>
-      <c r="J44" s="102"/>
+      <c r="A44" s="142"/>
+      <c r="B44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="106"/>
+      <c r="H44" s="109"/>
+      <c r="I44" s="156"/>
+      <c r="J44" s="118"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M44" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P44" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
       <c r="R44" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S44" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T44" s="57"/>
       <c r="U44" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="V44" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W44" s="57"/>
-      <c r="X44" s="146"/>
-      <c r="Y44" s="141"/>
-      <c r="Z44" s="140"/>
-      <c r="AA44" s="156"/>
+      <c r="X44" s="128"/>
+      <c r="Y44" s="130"/>
+      <c r="Z44" s="131"/>
+      <c r="AA44" s="132"/>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A45" s="136"/>
-      <c r="B45" s="125" t="s">
+      <c r="A45" s="142"/>
+      <c r="B45" s="91" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="90" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="137" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" s="105" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="G45" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="H45" s="103" t="s">
+      <c r="E45" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="F45" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="G45" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="H45" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="104" t="s">
+      <c r="I45" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="139" t="s">
+      <c r="J45" s="125" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11964,28 +11964,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="146"/>
-      <c r="Y45" s="141" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z45" s="157">
+      <c r="X45" s="128"/>
+      <c r="Y45" s="130" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z45" s="133">
         <v>46188</v>
       </c>
-      <c r="AA45" s="145" t="s">
-        <v>130</v>
+      <c r="AA45" s="124" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="136"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="137"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="139"/>
+      <c r="A46" s="142"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="106"/>
+      <c r="H46" s="109"/>
+      <c r="I46" s="106"/>
+      <c r="J46" s="125"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12015,38 +12015,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="146"/>
-      <c r="Y46" s="140"/>
-      <c r="Z46" s="140"/>
-      <c r="AA46" s="145"/>
+      <c r="X46" s="128"/>
+      <c r="Y46" s="131"/>
+      <c r="Z46" s="131"/>
+      <c r="AA46" s="124"/>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A47" s="136"/>
-      <c r="B47" s="125" t="s">
+      <c r="A47" s="142"/>
+      <c r="B47" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="92" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" s="90" t="s">
         <v>133</v>
       </c>
-      <c r="C47" s="137" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" s="105" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="G47" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="H47" s="103" t="s">
+      <c r="E47" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="F47" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="G47" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="H47" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="104" t="s">
-        <v>82</v>
-      </c>
-      <c r="J47" s="139" t="s">
+      <c r="I47" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="J47" s="125" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12088,24 +12088,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="146"/>
-      <c r="Y47" s="140"/>
-      <c r="Z47" s="140"/>
-      <c r="AA47" s="105" t="s">
-        <v>135</v>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="131"/>
+      <c r="Z47" s="131"/>
+      <c r="AA47" s="90" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="136"/>
-      <c r="B48" s="125"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="139"/>
+      <c r="A48" s="142"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="106"/>
+      <c r="F48" s="106"/>
+      <c r="G48" s="106"/>
+      <c r="H48" s="109"/>
+      <c r="I48" s="106"/>
+      <c r="J48" s="125"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12138,40 +12138,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="146"/>
-      <c r="Y48" s="140"/>
-      <c r="Z48" s="140"/>
-      <c r="AA48" s="105"/>
+      <c r="X48" s="128"/>
+      <c r="Y48" s="131"/>
+      <c r="Z48" s="131"/>
+      <c r="AA48" s="90"/>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A49" s="90" t="s">
+      <c r="A49" s="141" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="148" t="s">
         <v>136</v>
       </c>
-      <c r="B49" s="142" t="s">
+      <c r="C49" s="92" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="C49" s="137" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="105" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" s="104">
+      <c r="E49" s="106">
         <v>74</v>
       </c>
-      <c r="F49" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="G49" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="H49" s="103" t="s">
+      <c r="F49" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="G49" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="H49" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="104" t="s">
+      <c r="I49" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="106" t="s">
+      <c r="J49" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12213,24 +12213,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="146"/>
-      <c r="Y49" s="141"/>
-      <c r="Z49" s="140"/>
-      <c r="AA49" s="145" t="s">
-        <v>139</v>
+      <c r="X49" s="128"/>
+      <c r="Y49" s="130"/>
+      <c r="Z49" s="131"/>
+      <c r="AA49" s="124" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A50" s="90"/>
-      <c r="B50" s="142"/>
-      <c r="C50" s="137"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="106"/>
+      <c r="A50" s="141"/>
+      <c r="B50" s="148"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="106"/>
+      <c r="H50" s="109"/>
+      <c r="I50" s="106"/>
+      <c r="J50" s="105"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12258,44 +12258,46 @@
       <c r="S50" s="17">
         <v>0.74450000000000005</v>
       </c>
-      <c r="T50" s="17"/>
+      <c r="T50" s="17">
+        <v>0.74770000000000003</v>
+      </c>
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="76"/>
-      <c r="X50" s="146"/>
-      <c r="Y50" s="141"/>
-      <c r="Z50" s="140"/>
-      <c r="AA50" s="145"/>
+      <c r="X50" s="128"/>
+      <c r="Y50" s="130"/>
+      <c r="Z50" s="131"/>
+      <c r="AA50" s="124"/>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A51" s="136" t="s">
+      <c r="A51" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="125" t="s">
+      <c r="B51" s="91" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="C51" s="137" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" s="105" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" s="104">
+      <c r="E51" s="106">
         <v>33.1</v>
       </c>
-      <c r="F51" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="G51" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="H51" s="103" t="s">
+      <c r="F51" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="G51" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="H51" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="104" t="s">
+      <c r="I51" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="106" t="s">
+      <c r="J51" s="105" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12329,24 +12331,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="146"/>
-      <c r="Y51" s="140"/>
-      <c r="Z51" s="140"/>
-      <c r="AA51" s="123" t="s">
-        <v>142</v>
+      <c r="X51" s="128"/>
+      <c r="Y51" s="131"/>
+      <c r="Z51" s="131"/>
+      <c r="AA51" s="93" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="136"/>
-      <c r="B52" s="125"/>
-      <c r="C52" s="137"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="106"/>
+      <c r="A52" s="142"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="106"/>
+      <c r="F52" s="106"/>
+      <c r="G52" s="106"/>
+      <c r="H52" s="109"/>
+      <c r="I52" s="106"/>
+      <c r="J52" s="105"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12378,10 +12380,10 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="146"/>
-      <c r="Y52" s="140"/>
-      <c r="Z52" s="140"/>
-      <c r="AA52" s="123"/>
+      <c r="X52" s="128"/>
+      <c r="Y52" s="131"/>
+      <c r="Z52" s="131"/>
+      <c r="AA52" s="93"/>
     </row>
     <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -12392,27 +12394,231 @@
     <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="E32:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G37"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="X26:X27"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A3:B3"/>
@@ -12437,508 +12643,304 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="J8:J9"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="AA30:AA31"/>
-    <mergeCell ref="X24:X25"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G37"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="X26:X27"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
-    <cfRule type="containsBlanks" dxfId="75" priority="155">
+    <cfRule type="containsBlanks" dxfId="75" priority="160">
       <formula>LEN(TRIM(B6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="containsBlanks" dxfId="74" priority="71">
+    <cfRule type="containsBlanks" dxfId="74" priority="76">
       <formula>LEN(TRIM(B26))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41 B45 B47 B49 B51">
-    <cfRule type="containsBlanks" dxfId="73" priority="135">
+    <cfRule type="containsBlanks" dxfId="73" priority="140">
       <formula>LEN(TRIM(B41))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:E24">
-    <cfRule type="containsBlanks" dxfId="72" priority="70">
+    <cfRule type="containsBlanks" dxfId="72" priority="75">
       <formula>LEN(TRIM(B24))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="containsBlanks" dxfId="71" priority="68">
+    <cfRule type="containsBlanks" dxfId="71" priority="73">
       <formula>LEN(TRIM(C18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E6 D8:E8 D10:E10 D12:E12 B14:E14 B16:E16 E18 B20:E20 E22 B28:E28 C30:E30 B32:E32 B34:E34 B36:E36">
-    <cfRule type="containsBlanks" dxfId="70" priority="131">
+    <cfRule type="containsBlanks" dxfId="70" priority="136">
       <formula>LEN(TRIM(B6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H43">
-    <cfRule type="containsBlanks" dxfId="69" priority="122">
+    <cfRule type="containsBlanks" dxfId="69" priority="127">
       <formula>LEN(TRIM(H43))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:J18">
-    <cfRule type="containsBlanks" dxfId="68" priority="85">
+    <cfRule type="containsBlanks" dxfId="68" priority="90">
       <formula>LEN(TRIM(H18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J43">
-    <cfRule type="containsBlanks" dxfId="67" priority="26">
+    <cfRule type="containsBlanks" dxfId="67" priority="31">
       <formula>LEN(TRIM(J43))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="expression" dxfId="66" priority="73">
+    <cfRule type="expression" dxfId="66" priority="78">
       <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&gt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="74">
+    <cfRule type="expression" dxfId="65" priority="79">
       <formula>AND(OR($H26="Lower the better", $H26="Lower the Better"), L27&lt;=L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="75">
+    <cfRule type="expression" dxfId="64" priority="80">
       <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&lt;L26)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="81" stopIfTrue="1">
       <formula>AND(OR($H26="Higher the better", $H26="Higher the Better"), L27&gt;=L26)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="expression" dxfId="62" priority="69">
+  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L23:W23 M27:W27 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15">
+    <cfRule type="expression" dxfId="62" priority="74">
       <formula>AND(OR($H6="Lower the better", $H6="Lower the better"), L7&gt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="242">
+    <cfRule type="expression" dxfId="61" priority="247">
       <formula>AND(OR($H6="Lower the better", $H6= "Lower the Better"), L7 &lt;= L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="243">
+    <cfRule type="expression" dxfId="60" priority="248">
       <formula>AND(OR($H6="Higher the better", $H6="Higher the Better"), L7 &lt; L6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="244">
+    <cfRule type="expression" dxfId="59" priority="249">
       <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L15:W15 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37">
-    <cfRule type="containsBlanks" dxfId="58" priority="240">
+  <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15">
+    <cfRule type="containsBlanks" dxfId="58" priority="245">
       <formula>LEN(TRIM(L7))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27:W27">
-    <cfRule type="containsBlanks" dxfId="57" priority="72">
+    <cfRule type="containsBlanks" dxfId="57" priority="77">
       <formula>LEN(TRIM(L27))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L46:W46 L48:W48 L50:W50">
-    <cfRule type="containsBlanks" dxfId="56" priority="168">
+    <cfRule type="containsBlanks" dxfId="56" priority="173">
       <formula>LEN(TRIM(L46))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="170">
+    <cfRule type="expression" dxfId="55" priority="175">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&gt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="171">
+    <cfRule type="expression" dxfId="54" priority="176">
       <formula>AND(OR($H45="Lower the better", $H45="Lower the Better"), L46&lt;=L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="172">
+    <cfRule type="expression" dxfId="53" priority="177">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&lt;L45)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="178" stopIfTrue="1">
       <formula>AND(OR($H45="Higher the better", $H45="Higher the Better"), L46&gt;=L45)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:W52">
-    <cfRule type="containsBlanks" dxfId="51" priority="99">
+    <cfRule type="containsBlanks" dxfId="51" priority="104">
       <formula>LEN(TRIM(L52))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="100">
+    <cfRule type="expression" dxfId="50" priority="105">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&gt;L51)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="101">
+    <cfRule type="expression" dxfId="49" priority="106">
       <formula>AND(OR($H51="Lower the better", $H51="Lower the Better"), L52&lt;=L51)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="102">
+    <cfRule type="expression" dxfId="48" priority="107">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&lt;L51)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="108" stopIfTrue="1">
       <formula>AND(OR($H51="Higher the better", $H51="Higher the Better"), L52&gt;=L51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 T25 W25 L42:W42">
-    <cfRule type="containsBlanks" dxfId="46" priority="62">
+    <cfRule type="containsBlanks" dxfId="46" priority="67">
       <formula>LEN(TRIM(L25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="63">
+    <cfRule type="expression" dxfId="45" priority="68">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&gt;L24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="64">
+    <cfRule type="expression" dxfId="44" priority="69">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), L25&lt;=L24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="65">
+    <cfRule type="expression" dxfId="43" priority="70">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&lt;L24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="71" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), L25&gt;=L24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="containsBlanks" dxfId="41" priority="11">
+    <cfRule type="containsBlanks" dxfId="41" priority="16">
       <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="12">
+    <cfRule type="expression" dxfId="40" priority="17">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="13">
+    <cfRule type="expression" dxfId="39" priority="18">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="14">
+    <cfRule type="expression" dxfId="38" priority="19">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="20" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="36" priority="16">
+    <cfRule type="containsBlanks" dxfId="36" priority="21">
       <formula>LEN(TRIM(N25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="17">
+    <cfRule type="expression" dxfId="35" priority="22">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&gt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="18">
+    <cfRule type="expression" dxfId="34" priority="23">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), N25&lt;=N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="19">
+    <cfRule type="expression" dxfId="33" priority="24">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&lt;N24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="25" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), N25&gt;=N24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="containsBlanks" dxfId="31" priority="57">
+    <cfRule type="containsBlanks" dxfId="31" priority="62">
       <formula>LEN(TRIM(N44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="58">
+    <cfRule type="expression" dxfId="30" priority="63">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&gt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="59">
+    <cfRule type="expression" dxfId="29" priority="64">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), N44&lt;=N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="60">
+    <cfRule type="expression" dxfId="28" priority="65">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&lt;N43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="66" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), N44&gt;=N43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="containsBlanks" dxfId="26" priority="21">
+    <cfRule type="containsBlanks" dxfId="26" priority="26">
       <formula>LEN(TRIM(Q25))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="22">
+    <cfRule type="expression" dxfId="25" priority="27">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&gt;Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="23">
+    <cfRule type="expression" dxfId="24" priority="28">
       <formula>AND(OR($H24="Lower the better", $H24="Lower the Better"), Q25&lt;=Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="23" priority="29">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&lt;Q24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
       <formula>AND(OR($H24="Higher the better", $H24="Higher the Better"), Q25&gt;=Q24)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="21" priority="6">
       <formula>AND(OR($H36="Lower the better", $H36="Lower the better"), Q37&gt; Q36)</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="20" priority="2">
+    <cfRule type="containsBlanks" dxfId="20" priority="7">
       <formula>LEN(TRIM(Q37))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="3">
+    <cfRule type="expression" dxfId="19" priority="8">
       <formula>AND(OR($H36="Lower the better", $H36= "Lower the Better"), Q37 &lt;= Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="4">
+    <cfRule type="expression" dxfId="18" priority="9">
       <formula>AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37 &lt; Q36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="5">
+    <cfRule type="expression" dxfId="17" priority="10">
       <formula xml:space="preserve"> AND(OR($H36="Higher the better", $H36="Higher the Better"), Q37&gt;= Q36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q44">
-    <cfRule type="containsBlanks" dxfId="16" priority="6">
+    <cfRule type="containsBlanks" dxfId="16" priority="11">
       <formula>LEN(TRIM(Q44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="15" priority="12">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&gt;Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="8">
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), Q44&lt;=Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="9">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&lt;Q43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="15" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), Q44&gt;=Q43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="containsBlanks" dxfId="11" priority="47">
+    <cfRule type="containsBlanks" dxfId="11" priority="52">
       <formula>LEN(TRIM(T44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="48">
+    <cfRule type="expression" dxfId="10" priority="53">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&gt;T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="49">
+    <cfRule type="expression" dxfId="9" priority="54">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), T44&lt;=T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="50">
+    <cfRule type="expression" dxfId="8" priority="55">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&lt;T43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="56" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), T44&gt;=T43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W44">
-    <cfRule type="containsBlanks" dxfId="6" priority="42">
+    <cfRule type="containsBlanks" dxfId="6" priority="47">
       <formula>LEN(TRIM(W44))=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="43">
+    <cfRule type="expression" dxfId="5" priority="48">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&gt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="44">
+    <cfRule type="expression" dxfId="4" priority="49">
       <formula>AND(OR($H43="Lower the better", $H43="Lower the Better"), W44&lt;=W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="45">
+    <cfRule type="expression" dxfId="3" priority="50">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&lt;W43)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="51" stopIfTrue="1">
       <formula>AND(OR($H43="Higher the better", $H43="Higher the Better"), W44&gt;=W43)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA47">
-    <cfRule type="containsBlanks" dxfId="1" priority="128">
+    <cfRule type="containsBlanks" dxfId="1" priority="133">
       <formula>LEN(TRIM(AA47))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA51">
-    <cfRule type="containsBlanks" dxfId="0" priority="127">
+    <cfRule type="containsBlanks" dxfId="0" priority="132">
       <formula>LEN(TRIM(AA51))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13118,9 +13120,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13133,27 +13134,19 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5245F4-B03F-4E5D-AA1F-5F641D3F41D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{815CA4AF-3EDA-4A7D-AE64-A6B36CF4E6B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13167,9 +13160,18 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -13140,7 +13140,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{815CA4AF-3EDA-4A7D-AE64-A6B36CF4E6B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A947F7A-4B36-444A-8EB5-D7532A79A0CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/GlobalMoSMT-2023/Shared Documents/General/2026/Goals Alignment 2026/Strategic Execution 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3233" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAE97006-85EC-4024-8602-2E985E083A89}"/>
+  <xr:revisionPtr revIDLastSave="3237" documentId="8_{9B9C04DA-ABE2-4E9B-9FCF-AA5C7C703189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{748366EC-4437-42B7-8A5F-962600F38AC1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{31EBE344-35EA-49FE-9828-AF06217AD86D}"/>
   </bookViews>
@@ -586,6 +586,9 @@
     <t>Increase contract penetration %</t>
   </si>
   <si>
+    <t>0.8% Gap VS AOP. YoY improvement by 0.7% excluding GRC, Win back campaign impact in Q4</t>
+  </si>
+  <si>
     <t>Funnel focus actions driven across regions for same</t>
   </si>
   <si>
@@ -617,6 +620,9 @@
   </si>
   <si>
     <t>Mn</t>
+  </si>
+  <si>
+    <t>YTD Sept Productivity no's on track.Good Realization from E&amp;E savings of Pune and also a gap reduction of R&amp;D Budget YTD.</t>
   </si>
   <si>
     <t>Inventory MAT sales</t>
@@ -815,12 +821,6 @@
   </si>
   <si>
     <t>Focus on optimizing FCP, pricing, and product mix to drive margin expansion</t>
-  </si>
-  <si>
-    <t>YTD Sept Productivity no's on track.Good Realization from E&amp;E savings of Pune and also a gap reduction of R&amp;D Budget YTD.</t>
-  </si>
-  <si>
-    <t>0.8% Gap VS AOP. YoY improvement by 0.7% excluding GRC, Win back campaign impact in Q4</t>
   </si>
 </sst>
 </file>
@@ -834,7 +834,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1569,32 +1569,239 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1602,215 +1809,8 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4629,10 +4629,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}" name="Customer_Focus" displayName="Customer_Focus" ref="A14:V20" totalsRowShown="0">
   <autoFilter ref="A14:V20" xr:uid="{BD41CE00-E924-4733-B76A-3C4E09FA89B8}"/>
@@ -5189,29 +5185,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AD843-49A7-417E-9F24-86908363EFA2}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.54296875" customWidth="1"/>
-    <col min="5" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" customWidth="1"/>
+    <col min="5" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15.95">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5279,7 +5275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22">
       <c r="A5" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5365,7 +5361,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22">
       <c r="A6" t="str">
         <f>IF('AOP Critical'!B6="","",'AOP Critical'!B6)</f>
         <v>Complaint Closure</v>
@@ -5451,7 +5447,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22">
       <c r="A7" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5537,7 +5533,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22">
       <c r="A8" t="str">
         <f>IF('AOP Critical'!B8="","",'AOP Critical'!B8)</f>
         <v>% of CAPA investgation</v>
@@ -5623,7 +5619,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5709,7 +5705,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" t="str">
         <f>IF('AOP Critical'!B10="","",'AOP Critical'!B10)</f>
         <v xml:space="preserve"># of Corrections &amp; Removals </v>
@@ -5795,7 +5791,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22">
       <c r="A11" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5881,7 +5877,7 @@
         <v>3.32E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22">
       <c r="A12" t="str">
         <f>IF('AOP Critical'!B41="","",'AOP Critical'!B41)</f>
         <v>Cost Of Non-Quality as % of Sales</v>
@@ -5967,12 +5963,12 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -6040,7 +6036,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22">
       <c r="A15" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6130,7 +6126,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22">
       <c r="A16" t="str">
         <f>IF('AOP Critical'!B12="","",'AOP Critical'!B12)</f>
         <v>Ontime In Full</v>
@@ -6220,7 +6216,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22">
       <c r="A17" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6310,7 +6306,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22">
       <c r="A18" t="str">
         <f>IF('AOP Critical'!B14="","",'AOP Critical'!B14)</f>
         <v>Contract Penetration</v>
@@ -6400,7 +6396,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22">
       <c r="A19" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6490,7 +6486,7 @@
         <v>0.73999999999999966</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22">
       <c r="A20" t="str">
         <f>IF('AOP Critical'!B49="","",'AOP Critical'!B49)</f>
         <v>Services - Time To System Up (TTSU)</v>
@@ -6580,12 +6576,12 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -6653,7 +6649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22">
       <c r="A23" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6743,7 +6739,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22">
       <c r="A24" t="str">
         <f>IF('AOP Critical'!B16="","",'AOP Critical'!B16)</f>
         <v>Adjusted EBITA %</v>
@@ -6833,7 +6829,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22">
       <c r="A25" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -6923,7 +6919,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22">
       <c r="A26" t="str">
         <f>IF('AOP Critical'!B18="","",'AOP Critical'!B18)</f>
         <v>Productivity</v>
@@ -7013,7 +7009,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22">
       <c r="A27" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7103,7 +7099,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22">
       <c r="A28" t="str">
         <f>IF('AOP Critical'!B20="","",'AOP Critical'!B20)</f>
         <v>Inventory MAT sales</v>
@@ -7193,7 +7189,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22">
       <c r="A29" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7283,7 +7279,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22">
       <c r="A30" t="str">
         <f>IF('AOP Critical'!B51="","",'AOP Critical'!B51)</f>
         <v>Profitability - Margin Expansion</v>
@@ -7373,12 +7369,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -7446,7 +7442,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22">
       <c r="A33" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7519,9 +7515,9 @@
         <f>IF('AOP Critical'!S26="","",'AOP Critical'!S26)</f>
         <v>0.34</v>
       </c>
-      <c r="S33" s="71" t="str">
+      <c r="S33" s="71">
         <f>IF('AOP Critical'!T26="","",'AOP Critical'!T26)</f>
-        <v/>
+        <v>0.34</v>
       </c>
       <c r="T33" s="71" t="str">
         <f>IF('AOP Critical'!U26="","",'AOP Critical'!U26)</f>
@@ -7536,7 +7532,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22">
       <c r="A34" t="str">
         <f>IF('AOP Critical'!B26="","",'AOP Critical'!B26)</f>
         <v xml:space="preserve">Win Rate </v>
@@ -7609,9 +7605,9 @@
         <f>IF('AOP Critical'!S27="","",'AOP Critical'!S27)</f>
         <v>0.35</v>
       </c>
-      <c r="S34" s="71" t="str">
+      <c r="S34" s="71">
         <f>IF('AOP Critical'!T27="","",'AOP Critical'!T27)</f>
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="T34" s="71" t="str">
         <f>IF('AOP Critical'!U27="","",'AOP Critical'!U27)</f>
@@ -7626,7 +7622,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22">
       <c r="A35" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7716,7 +7712,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22">
       <c r="A36" t="str">
         <f>IF('AOP Critical'!B22="","",'AOP Critical'!B22)</f>
         <v>NPI Schedule Adherence</v>
@@ -7806,7 +7802,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22">
       <c r="A37" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7896,7 +7892,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22">
       <c r="A38" t="str">
         <f>IF('AOP Critical'!B43="","",'AOP Critical'!B43)</f>
         <v>Competitive Roadmap</v>
@@ -7986,7 +7982,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22">
       <c r="A39" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8076,7 +8072,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22">
       <c r="A40" t="str">
         <f>IF('AOP Critical'!B45="","",'AOP Critical'!B45)</f>
         <v>Vitality index</v>
@@ -8145,13 +8141,13 @@
         <f>IF('AOP Critical'!R46="","",'AOP Critical'!R46)</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R40" s="72" t="str">
+      <c r="R40" s="72">
         <f>IF('AOP Critical'!S46="","",'AOP Critical'!S46)</f>
-        <v/>
-      </c>
-      <c r="S40" s="72" t="str">
+        <v>0.39</v>
+      </c>
+      <c r="S40" s="72">
         <f>IF('AOP Critical'!T46="","",'AOP Critical'!T46)</f>
-        <v/>
+        <v>0.37</v>
       </c>
       <c r="T40" s="72" t="str">
         <f>IF('AOP Critical'!U46="","",'AOP Critical'!U46)</f>
@@ -8166,7 +8162,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22">
       <c r="A41" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8256,7 +8252,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22">
       <c r="A42" t="str">
         <f>IF('AOP Critical'!B47="","",'AOP Critical'!B47)</f>
         <v>I2M Value Creation</v>
@@ -8346,12 +8342,12 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22">
       <c r="A43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -8419,7 +8415,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22">
       <c r="A45" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8509,7 +8505,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22">
       <c r="A46" t="str">
         <f>IF('AOP Critical'!D28="","",'AOP Critical'!D28)</f>
         <v>OIT Growth % (EQ)</v>
@@ -8599,7 +8595,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22">
       <c r="A47" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8686,7 +8682,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22">
       <c r="A48" t="str">
         <f>IF('AOP Critical'!D30="","",'AOP Critical'!D30)</f>
         <v>OIT Growth % (CS)</v>
@@ -8772,7 +8768,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22">
       <c r="A49" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8862,7 +8858,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22">
       <c r="A50" t="str">
         <f>IF('AOP Critical'!B32="","",'AOP Critical'!B32)</f>
         <v>Comparable Sales</v>
@@ -8952,7 +8948,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22">
       <c r="A51" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9042,7 +9038,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22">
       <c r="A52" t="str">
         <f>IF('AOP Critical'!B24="","",'AOP Critical'!B24)</f>
         <v>Implied Market Share Gain</v>
@@ -9132,12 +9128,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22">
       <c r="A54" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -9205,7 +9201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -9280,7 +9276,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -9355,7 +9351,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -9430,7 +9426,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -9526,33 +9522,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632542D1-52E6-4116-B536-B17D5839DF19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AC66"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.81640625" customWidth="1"/>
-    <col min="5" max="5" width="5.1796875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.81640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7265625" customWidth="1"/>
-    <col min="12" max="12" width="5.54296875" customWidth="1"/>
-    <col min="13" max="13" width="6.81640625" customWidth="1"/>
-    <col min="14" max="14" width="6.26953125" customWidth="1"/>
-    <col min="15" max="15" width="7.26953125" customWidth="1"/>
-    <col min="16" max="22" width="6.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" customWidth="1"/>
+    <col min="14" max="14" width="6.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" customWidth="1"/>
+    <col min="16" max="22" width="6.140625" customWidth="1"/>
     <col min="23" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="58.81640625" style="20" customWidth="1"/>
-    <col min="25" max="25" width="68.1796875" customWidth="1"/>
-    <col min="26" max="26" width="17.7265625" customWidth="1"/>
+    <col min="24" max="24" width="58.85546875" style="20" customWidth="1"/>
+    <col min="25" max="25" width="68.140625" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" customWidth="1"/>
     <col min="27" max="27" width="57" style="13" customWidth="1"/>
-    <col min="28" max="46" width="8.54296875" customWidth="1"/>
+    <col min="28" max="46" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -9563,7 +9559,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="E2" s="6"/>
@@ -9572,11 +9568,11 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="108" t="s">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
+      <c r="A3" s="161" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="108"/>
+      <c r="B3" s="161"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9596,39 +9592,39 @@
       <c r="X3" s="21"/>
       <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="110" t="str">
+    <row r="4" spans="1:27" s="5" customFormat="1">
+      <c r="A4" s="162" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110"/>
-      <c r="V4" s="110"/>
-      <c r="W4" s="110"/>
-      <c r="X4" s="110"/>
-      <c r="Y4" s="110"/>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
+      <c r="B4" s="162"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="162"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="162"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="162"/>
+      <c r="I4" s="162"/>
+      <c r="J4" s="162"/>
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="162"/>
+      <c r="P4" s="162"/>
+      <c r="Q4" s="162"/>
+      <c r="R4" s="162"/>
+      <c r="S4" s="162"/>
+      <c r="T4" s="162"/>
+      <c r="U4" s="162"/>
+      <c r="V4" s="162"/>
+      <c r="W4" s="162"/>
+      <c r="X4" s="162"/>
+      <c r="Y4" s="162"/>
+      <c r="Z4" s="162"/>
+      <c r="AA4" s="162"/>
     </row>
-    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="27" customHeight="1">
       <c r="A5" s="88" t="s">
         <v>0</v>
       </c>
@@ -9641,11 +9637,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="114" t="s">
+      <c r="E5" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="163"/>
       <c r="H5" s="89" t="s">
         <v>8</v>
       </c>
@@ -9707,31 +9703,31 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A6" s="107" t="s">
+    <row r="6" spans="1:27">
+      <c r="A6" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="106">
+      <c r="E6" s="104">
         <v>10</v>
       </c>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="109" t="s">
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="106" t="s">
+      <c r="I6" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="105" t="s">
+      <c r="J6" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9773,24 +9769,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="104"/>
-      <c r="Y6" s="111"/>
-      <c r="Z6" s="111"/>
-      <c r="AA6" s="121" t="s">
+      <c r="X6" s="110"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="117" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A7" s="107"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="105"/>
+    <row r="7" spans="1:27">
+      <c r="A7" s="92"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="106"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9824,34 +9820,34 @@
       <c r="U7" s="52"/>
       <c r="V7" s="52"/>
       <c r="W7" s="52"/>
-      <c r="X7" s="94"/>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
-      <c r="AA7" s="122"/>
+      <c r="X7" s="111"/>
+      <c r="Y7" s="130"/>
+      <c r="Z7" s="130"/>
+      <c r="AA7" s="118"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A8" s="107"/>
-      <c r="B8" s="91" t="s">
+    <row r="8" spans="1:27">
+      <c r="A8" s="92"/>
+      <c r="B8" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="106">
+      <c r="E8" s="104">
         <v>90</v>
       </c>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="109" t="s">
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="106" t="s">
+      <c r="I8" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="105" t="s">
+      <c r="J8" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9883,28 +9879,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="95" t="s">
+      <c r="X8" s="111"/>
+      <c r="Y8" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="112">
+      <c r="Z8" s="115">
         <v>46231</v>
       </c>
-      <c r="AA8" s="121" t="s">
+      <c r="AA8" s="117" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A9" s="107"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="109"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="105"/>
+    <row r="9" spans="1:27">
+      <c r="A9" s="92"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="106"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9938,34 +9934,34 @@
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="113"/>
-      <c r="AA9" s="122"/>
+      <c r="X9" s="111"/>
+      <c r="Y9" s="130"/>
+      <c r="Z9" s="116"/>
+      <c r="AA9" s="118"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A10" s="107"/>
-      <c r="B10" s="91" t="s">
+    <row r="10" spans="1:27">
+      <c r="A10" s="92"/>
+      <c r="B10" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="106">
+      <c r="E10" s="104">
         <v>1</v>
       </c>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="109" t="s">
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="106" t="s">
+      <c r="I10" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="105" t="s">
+      <c r="J10" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -9999,24 +9995,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="94"/>
-      <c r="Y10" s="161"/>
-      <c r="Z10" s="115"/>
-      <c r="AA10" s="121" t="s">
+      <c r="X10" s="111"/>
+      <c r="Y10" s="119"/>
+      <c r="Z10" s="164"/>
+      <c r="AA10" s="117" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="107"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="105"/>
+    <row r="11" spans="1:27" ht="15" thickBot="1">
+      <c r="A11" s="92"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="136"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="106"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10050,36 +10046,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="94"/>
-      <c r="Y11" s="162"/>
-      <c r="Z11" s="116"/>
-      <c r="AA11" s="122"/>
+      <c r="X11" s="111"/>
+      <c r="Y11" s="120"/>
+      <c r="Z11" s="165"/>
+      <c r="AA11" s="118"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="107" t="s">
+    <row r="12" spans="1:27">
+      <c r="A12" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="106">
+      <c r="E12" s="104">
         <v>84</v>
       </c>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="109" t="s">
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="106" t="s">
+      <c r="I12" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="105" t="s">
+      <c r="J12" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10121,24 +10117,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="94"/>
-      <c r="Y12" s="95"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="121" t="s">
+      <c r="X12" s="111"/>
+      <c r="Y12" s="129"/>
+      <c r="Z12" s="130"/>
+      <c r="AA12" s="117" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A13" s="107"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="105"/>
+    <row r="13" spans="1:27">
+      <c r="A13" s="92"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="106"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10170,34 +10166,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="94"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="122"/>
+      <c r="X13" s="111"/>
+      <c r="Y13" s="130"/>
+      <c r="Z13" s="130"/>
+      <c r="AA13" s="118"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="93" t="s">
+    <row r="14" spans="1:27">
+      <c r="A14" s="92"/>
+      <c r="B14" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="106">
+      <c r="E14" s="104">
         <v>54.6</v>
       </c>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="109" t="s">
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="106" t="s">
+      <c r="I14" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="105" t="s">
+      <c r="J14" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10233,26 +10229,26 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="94" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y14" s="150" t="s">
+      <c r="X14" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="Z14" s="150"/>
-      <c r="AA14" s="149"/>
+      <c r="Y14" s="100" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="127"/>
     </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="107"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="105"/>
+    <row r="15" spans="1:27" ht="15" thickBot="1">
+      <c r="A15" s="92"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="106"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10286,36 +10282,36 @@
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="94"/>
-      <c r="Y15" s="111"/>
-      <c r="Z15" s="111"/>
-      <c r="AA15" s="129"/>
+      <c r="X15" s="111"/>
+      <c r="Y15" s="101"/>
+      <c r="Z15" s="101"/>
+      <c r="AA15" s="128"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="107" t="s">
+    <row r="16" spans="1:27">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="93" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="93" t="s">
+      <c r="B16" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="90" t="s">
+      <c r="C16" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="106" t="s">
+      <c r="D16" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="109" t="s">
+      <c r="E16" s="104" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="106" t="s">
+      <c r="I16" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="105" t="s">
+      <c r="J16" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10349,28 +10345,28 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="94" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y16" s="95" t="s">
+      <c r="X16" s="111" t="s">
         <v>77</v>
       </c>
-      <c r="Z16" s="113"/>
-      <c r="AA16" s="121" t="s">
+      <c r="Y16" s="129" t="s">
         <v>78</v>
       </c>
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="117" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A17" s="107"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="105"/>
+    <row r="17" spans="1:27">
+      <c r="A17" s="92"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="106"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10402,34 +10398,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="94"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="113"/>
-      <c r="AA17" s="122"/>
+      <c r="X17" s="111"/>
+      <c r="Y17" s="130"/>
+      <c r="Z17" s="116"/>
+      <c r="AA17" s="118"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A18" s="107"/>
-      <c r="B18" s="93" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="93" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="93" t="s">
+    <row r="18" spans="1:27">
+      <c r="A18" s="92"/>
+      <c r="B18" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="106"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="109" t="s">
+      <c r="C18" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="123" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="104" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="106" t="s">
-        <v>81</v>
-      </c>
-      <c r="J18" s="105" t="s">
+      <c r="I18" s="104" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10466,26 +10462,26 @@
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="155" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y18" s="155"/>
-      <c r="Z18" s="152">
+      <c r="X18" s="134" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y18" s="134"/>
+      <c r="Z18" s="131">
         <v>46108</v>
       </c>
-      <c r="AA18" s="154"/>
+      <c r="AA18" s="133"/>
     </row>
-    <row r="19" spans="1:27" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="107"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="105"/>
+    <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
+      <c r="A19" s="92"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="106"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
@@ -10519,34 +10515,34 @@
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="50"/>
-      <c r="X19" s="155"/>
-      <c r="Y19" s="155"/>
-      <c r="Z19" s="153"/>
-      <c r="AA19" s="154"/>
+      <c r="X19" s="134"/>
+      <c r="Y19" s="134"/>
+      <c r="Z19" s="132"/>
+      <c r="AA19" s="133"/>
     </row>
-    <row r="20" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="107"/>
-      <c r="B20" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="93" t="s">
+    <row r="20" spans="1:27" ht="24" customHeight="1">
+      <c r="A20" s="92"/>
+      <c r="B20" s="123" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="90" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="109" t="s">
+      <c r="D20" s="105" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="104" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="106" t="s">
+      <c r="I20" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="105" t="s">
+      <c r="J20" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10580,28 +10576,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="169" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y20" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z20" s="151"/>
-      <c r="AA20" s="123" t="s">
+      <c r="X20" s="166" t="s">
         <v>86</v>
       </c>
+      <c r="Y20" s="168" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="152" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="21" spans="1:27" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="107"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="105"/>
+    <row r="21" spans="1:27" ht="32.1" customHeight="1" thickBot="1">
+      <c r="A21" s="92"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="106"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10633,36 +10629,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="170"/>
-      <c r="Y21" s="100"/>
-      <c r="Z21" s="117"/>
-      <c r="AA21" s="123"/>
+      <c r="X21" s="167"/>
+      <c r="Y21" s="169"/>
+      <c r="Z21" s="94"/>
+      <c r="AA21" s="152"/>
     </row>
-    <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107" t="s">
+    <row r="22" spans="1:27" ht="15.95" customHeight="1">
+      <c r="A22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="93" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="120" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="93" t="s">
+      <c r="B22" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="106">
+      <c r="C22" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="109" t="s">
+      <c r="D22" s="123" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="104">
+        <v>90</v>
+      </c>
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="106" t="s">
+      <c r="I22" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="105" t="s">
+      <c r="J22" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10704,24 +10700,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="103"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="112">
+      <c r="X22" s="170"/>
+      <c r="Y22" s="129"/>
+      <c r="Z22" s="115">
         <v>46257</v>
       </c>
-      <c r="AA22" s="159"/>
+      <c r="AA22" s="113"/>
     </row>
-    <row r="23" spans="1:27" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="166"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="109"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="105"/>
+    <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
+      <c r="A23" s="93"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="106"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10753,40 +10749,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="104"/>
-      <c r="Y23" s="96"/>
-      <c r="Z23" s="113"/>
-      <c r="AA23" s="160"/>
+      <c r="X23" s="110"/>
+      <c r="Y23" s="130"/>
+      <c r="Z23" s="116"/>
+      <c r="AA23" s="114"/>
     </row>
-    <row r="24" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="141" t="s">
+    <row r="24" spans="1:27" ht="17.45" customHeight="1">
+      <c r="A24" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="93" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="120" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="90" t="s">
+      <c r="B24" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="106" t="s">
+      <c r="C24" s="124" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="109" t="s">
+      <c r="D24" s="105" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="106" t="s">
+      <c r="I24" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="118" t="s">
+      <c r="J24" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10798,109 +10794,109 @@
         <v>0.104</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="38">
         <v>0.11799999999999999</v>
       </c>
       <c r="R24" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S24" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T24" s="36"/>
       <c r="U24" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="V24" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="W24" s="39"/>
-      <c r="X24" s="135"/>
-      <c r="Y24" s="150"/>
-      <c r="Z24" s="117"/>
-      <c r="AA24" s="121" t="s">
-        <v>95</v>
+      <c r="X24" s="109"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="94"/>
+      <c r="AA24" s="117" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="165"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="120"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="109"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="118"/>
+    <row r="25" spans="1:27" ht="15" thickBot="1">
+      <c r="A25" s="91"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="102"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N25" s="52">
         <v>0.115</v>
       </c>
       <c r="O25" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P25" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="17">
         <v>0.121</v>
       </c>
       <c r="R25" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S25" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T25" s="57"/>
       <c r="U25" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="V25" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="W25" s="57"/>
-      <c r="X25" s="104"/>
-      <c r="Y25" s="111"/>
-      <c r="Z25" s="151"/>
-      <c r="AA25" s="122"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="101"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="118"/>
     </row>
-    <row r="26" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="165"/>
-      <c r="B26" s="91" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="158" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="90" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" s="106">
+    <row r="26" spans="1:27" ht="14.45" customHeight="1">
+      <c r="A26" s="91"/>
+      <c r="B26" s="125" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="126" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="105" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="104">
         <v>34</v>
       </c>
-      <c r="F26" s="156"/>
-      <c r="G26" s="156"/>
-      <c r="H26" s="109" t="s">
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="106" t="s">
+      <c r="I26" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="105" t="s">
+      <c r="J26" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10930,28 +10926,30 @@
       <c r="S26" s="25">
         <v>0.34</v>
       </c>
-      <c r="T26" s="25"/>
+      <c r="T26" s="25">
+        <v>0.34</v>
+      </c>
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="94"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="113"/>
-      <c r="AA26" s="121" t="s">
-        <v>98</v>
+      <c r="X26" s="111"/>
+      <c r="Y26" s="130"/>
+      <c r="Z26" s="116"/>
+      <c r="AA26" s="117" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="165"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="156"/>
-      <c r="G27" s="156"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="105"/>
+    <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
+      <c r="A27" s="91"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="106"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10979,38 +10977,40 @@
       <c r="S27" s="19">
         <v>0.35</v>
       </c>
-      <c r="T27" s="19"/>
+      <c r="T27" s="19">
+        <v>0.35</v>
+      </c>
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="94"/>
-      <c r="Y27" s="96"/>
-      <c r="Z27" s="113"/>
-      <c r="AA27" s="122"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="130"/>
+      <c r="Z27" s="116"/>
+      <c r="AA27" s="118"/>
     </row>
-    <row r="28" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="165"/>
-      <c r="B28" s="90" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="93" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="109" t="s">
+    <row r="28" spans="1:27" ht="14.45" customHeight="1">
+      <c r="A28" s="91"/>
+      <c r="B28" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="105" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="104" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="106" t="s">
+      <c r="I28" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="105" t="s">
+      <c r="J28" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11044,26 +11044,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="101" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y28" s="97"/>
-      <c r="Z28" s="117"/>
-      <c r="AA28" s="126" t="s">
-        <v>102</v>
+      <c r="X28" s="158" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="94"/>
+      <c r="AA28" s="153" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="165"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="109"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="105"/>
+    <row r="29" spans="1:27" ht="15" thickBot="1">
+      <c r="A29" s="91"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="106"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11095,32 +11095,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="102"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="151"/>
-      <c r="AA29" s="127"/>
+      <c r="X29" s="159"/>
+      <c r="Y29" s="97"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="154"/>
     </row>
-    <row r="30" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="165"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="93" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" s="90" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="109" t="s">
+    <row r="30" spans="1:27" ht="14.45" customHeight="1">
+      <c r="A30" s="91"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="104" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="106" t="s">
+      <c r="I30" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="105" t="s">
+      <c r="J30" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11154,22 +11154,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="101"/>
-      <c r="Y30" s="150"/>
-      <c r="Z30" s="117"/>
-      <c r="AA30" s="163"/>
+      <c r="X30" s="158"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="94"/>
+      <c r="AA30" s="107"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A31" s="165"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="109"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="105"/>
+    <row r="31" spans="1:27">
+      <c r="A31" s="91"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="106"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11201,34 +11201,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="102"/>
-      <c r="Y31" s="111"/>
-      <c r="Z31" s="151"/>
-      <c r="AA31" s="164"/>
+      <c r="X31" s="159"/>
+      <c r="Y31" s="101"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="108"/>
     </row>
-    <row r="32" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="165"/>
-      <c r="B32" s="93" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="120" t="s">
+    <row r="32" spans="1:27" ht="14.45" customHeight="1">
+      <c r="A32" s="91"/>
+      <c r="B32" s="123" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="90" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="106"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="109" t="s">
+      <c r="D32" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="104" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="106" t="s">
-        <v>81</v>
-      </c>
-      <c r="J32" s="105" t="s">
+      <c r="I32" s="104" t="s">
+        <v>82</v>
+      </c>
+      <c r="J32" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11262,28 +11262,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="167" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y32" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z32" s="117"/>
-      <c r="AA32" s="121" t="s">
+      <c r="X32" s="98" t="s">
         <v>108</v>
       </c>
+      <c r="Y32" s="96" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z32" s="94"/>
+      <c r="AA32" s="117" t="s">
+        <v>110</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="165"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="120"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="109"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="105"/>
+    <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A33" s="91"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="106"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11315,36 +11315,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="168"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="151"/>
-      <c r="AA33" s="122"/>
+      <c r="X33" s="99"/>
+      <c r="Y33" s="97"/>
+      <c r="Z33" s="95"/>
+      <c r="AA33" s="118"/>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A34" s="107" t="s">
+    <row r="34" spans="1:29">
+      <c r="A34" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="146" t="s">
+      <c r="B34" s="143" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="93" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="90" t="s">
+      <c r="C34" s="123" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="106">
+      <c r="E34" s="104">
         <v>90</v>
       </c>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="109" t="s">
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="106" t="s">
+      <c r="I34" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="118" t="s">
+      <c r="J34" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11370,83 +11370,83 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="94"/>
-      <c r="Y34" s="96"/>
-      <c r="Z34" s="113"/>
-      <c r="AA34" s="121" t="s">
-        <v>109</v>
+      <c r="X34" s="111"/>
+      <c r="Y34" s="130"/>
+      <c r="Z34" s="116"/>
+      <c r="AA34" s="117" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A35" s="107"/>
-      <c r="B35" s="146"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="106"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="106"/>
-      <c r="J35" s="118"/>
+    <row r="35" spans="1:29">
+      <c r="A35" s="92"/>
+      <c r="B35" s="143"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="102"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
       </c>
       <c r="O35" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P35" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q35" s="19">
         <v>0.96199999999999997</v>
       </c>
       <c r="R35" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S35" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T35" s="19"/>
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="113"/>
-      <c r="AA35" s="122"/>
+      <c r="X35" s="111"/>
+      <c r="Y35" s="130"/>
+      <c r="Z35" s="116"/>
+      <c r="AA35" s="118"/>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A36" s="107"/>
-      <c r="B36" s="146" t="s">
+    <row r="36" spans="1:29">
+      <c r="A36" s="92"/>
+      <c r="B36" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="93" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="90" t="s">
+      <c r="C36" s="123" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="106">
+      <c r="E36" s="104">
         <v>83</v>
       </c>
-      <c r="F36" s="106"/>
-      <c r="G36" s="106"/>
-      <c r="H36" s="109" t="s">
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="106" t="s">
+      <c r="I36" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="119" t="s">
+      <c r="J36" s="160" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11468,96 +11468,96 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y36" s="95" t="s">
-        <v>112</v>
-      </c>
-      <c r="Z36" s="113"/>
-      <c r="AA36" s="121" t="s">
+      <c r="X36" s="111" t="s">
         <v>113</v>
       </c>
+      <c r="Y36" s="129" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z36" s="116"/>
+      <c r="AA36" s="117" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
-      <c r="B37" s="146"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="106"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="109"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="119"/>
+    <row r="37" spans="1:29">
+      <c r="A37" s="92"/>
+      <c r="B37" s="143"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="160"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N37" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O37" s="19">
         <v>0.79</v>
       </c>
       <c r="P37" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q37" s="19">
         <v>0.79</v>
       </c>
       <c r="R37" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="S37" s="58"/>
       <c r="T37" s="58"/>
       <c r="U37" s="58"/>
       <c r="V37" s="58"/>
       <c r="W37" s="59"/>
-      <c r="X37" s="135"/>
-      <c r="Y37" s="97"/>
-      <c r="Z37" s="117"/>
-      <c r="AA37" s="123"/>
+      <c r="X37" s="109"/>
+      <c r="Y37" s="96"/>
+      <c r="Z37" s="94"/>
+      <c r="AA37" s="152"/>
     </row>
-    <row r="38" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="136"/>
-      <c r="B38" s="136"/>
-      <c r="C38" s="136"/>
-      <c r="D38" s="136"/>
-      <c r="E38" s="136"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="136"/>
-      <c r="L38" s="136"/>
-      <c r="M38" s="136"/>
-      <c r="N38" s="136"/>
-      <c r="O38" s="136"/>
-      <c r="P38" s="137"/>
-      <c r="Q38" s="137"/>
-      <c r="R38" s="137"/>
-      <c r="S38" s="137"/>
-      <c r="T38" s="137"/>
-      <c r="U38" s="137"/>
-      <c r="V38" s="137"/>
-      <c r="W38" s="137"/>
-      <c r="X38" s="137"/>
-      <c r="Y38" s="137"/>
-      <c r="Z38" s="137"/>
-      <c r="AA38" s="137"/>
+    <row r="38" spans="1:29" s="5" customFormat="1">
+      <c r="A38" s="146"/>
+      <c r="B38" s="146"/>
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="146"/>
+      <c r="H38" s="146"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="146"/>
+      <c r="K38" s="146"/>
+      <c r="L38" s="146"/>
+      <c r="M38" s="146"/>
+      <c r="N38" s="146"/>
+      <c r="O38" s="146"/>
+      <c r="P38" s="147"/>
+      <c r="Q38" s="147"/>
+      <c r="R38" s="147"/>
+      <c r="S38" s="147"/>
+      <c r="T38" s="147"/>
+      <c r="U38" s="147"/>
+      <c r="V38" s="147"/>
+      <c r="W38" s="147"/>
+      <c r="X38" s="147"/>
+      <c r="Y38" s="147"/>
+      <c r="Z38" s="147"/>
+      <c r="AA38" s="147"/>
     </row>
-    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="139" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="139"/>
+    <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
+      <c r="A39" s="148" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="148"/>
       <c r="C39" s="60"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11584,12 +11584,12 @@
       <c r="Z39"/>
       <c r="AA39" s="13"/>
     </row>
-    <row r="40" spans="1:29" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:29" ht="27.6" customHeight="1">
       <c r="A40" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
@@ -11598,13 +11598,13 @@
         <v>4</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>8</v>
@@ -11625,7 +11625,7 @@
         <v>13</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>15</v>
@@ -11634,7 +11634,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R40" s="10" t="s">
         <v>18</v>
@@ -11667,35 +11667,35 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A41" s="140" t="s">
+    <row r="41" spans="1:29">
+      <c r="A41" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="143" t="s">
-        <v>122</v>
-      </c>
-      <c r="C41" s="144" t="s">
+      <c r="B41" s="150" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="151" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="145" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" s="138" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="138" t="s">
-        <v>93</v>
-      </c>
-      <c r="G41" s="138" t="s">
-        <v>93</v>
-      </c>
-      <c r="H41" s="157" t="s">
+      <c r="D41" s="142" t="s">
+        <v>125</v>
+      </c>
+      <c r="E41" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="G41" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="H41" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="138" t="s">
+      <c r="I41" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="147" t="s">
+      <c r="J41" s="137" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="63" t="s">
@@ -11737,25 +11737,25 @@
       <c r="W41" s="65">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="134"/>
-      <c r="Y41" s="129"/>
-      <c r="Z41" s="129"/>
-      <c r="AA41" s="122" t="s">
-        <v>122</v>
+      <c r="X41" s="157"/>
+      <c r="Y41" s="128"/>
+      <c r="Z41" s="128"/>
+      <c r="AA41" s="118" t="s">
+        <v>124</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
-    <row r="42" spans="1:29" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="141"/>
-      <c r="B42" s="91"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="106"/>
-      <c r="H42" s="109"/>
-      <c r="I42" s="106"/>
-      <c r="J42" s="125"/>
+    <row r="42" spans="1:29" ht="23.1" customHeight="1">
+      <c r="A42" s="90"/>
+      <c r="B42" s="125"/>
+      <c r="C42" s="136"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="138"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11789,40 +11789,40 @@
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
-      <c r="X42" s="134"/>
-      <c r="Y42" s="129"/>
-      <c r="Z42" s="129"/>
-      <c r="AA42" s="124"/>
+      <c r="X42" s="157"/>
+      <c r="Y42" s="128"/>
+      <c r="Z42" s="128"/>
+      <c r="AA42" s="144"/>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A43" s="142" t="s">
+    <row r="43" spans="1:29">
+      <c r="A43" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="91" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="92" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" s="106" t="s">
+      <c r="B43" s="125" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="136" t="s">
         <v>93</v>
       </c>
-      <c r="F43" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="G43" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="H43" s="109" t="s">
+      <c r="D43" s="105" t="s">
+        <v>127</v>
+      </c>
+      <c r="E43" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="F43" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="G43" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="106" t="s">
+      <c r="I43" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="118" t="s">
+      <c r="J43" s="102" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11844,95 +11844,95 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="128" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y43" s="130" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z43" s="131"/>
-      <c r="AA43" s="132" t="s">
+      <c r="X43" s="145" t="s">
         <v>128</v>
       </c>
+      <c r="Y43" s="140" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z43" s="139"/>
+      <c r="AA43" s="155" t="s">
+        <v>130</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A44" s="142"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="106"/>
-      <c r="H44" s="109"/>
-      <c r="I44" s="156"/>
-      <c r="J44" s="118"/>
+    <row r="44" spans="1:29">
+      <c r="A44" s="135"/>
+      <c r="B44" s="125"/>
+      <c r="C44" s="136"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="112"/>
+      <c r="J44" s="102"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M44" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N44" s="17">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P44" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q44" s="17">
         <v>0.04</v>
       </c>
       <c r="R44" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S44" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T44" s="57"/>
       <c r="U44" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="V44" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="W44" s="57"/>
-      <c r="X44" s="128"/>
-      <c r="Y44" s="130"/>
-      <c r="Z44" s="131"/>
-      <c r="AA44" s="132"/>
+      <c r="X44" s="145"/>
+      <c r="Y44" s="140"/>
+      <c r="Z44" s="139"/>
+      <c r="AA44" s="155"/>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A45" s="142"/>
-      <c r="B45" s="91" t="s">
-        <v>129</v>
-      </c>
-      <c r="C45" s="92" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="90" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" s="106" t="s">
+    <row r="45" spans="1:29">
+      <c r="A45" s="135"/>
+      <c r="B45" s="125" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="136" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="G45" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="H45" s="109" t="s">
+      <c r="D45" s="105" t="s">
+        <v>132</v>
+      </c>
+      <c r="E45" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="F45" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="G45" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="H45" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="106" t="s">
+      <c r="I45" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="125" t="s">
+      <c r="J45" s="138" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11964,28 +11964,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="128"/>
-      <c r="Y45" s="130" t="s">
+      <c r="X45" s="145"/>
+      <c r="Y45" s="140" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z45" s="156">
+        <v>46188</v>
+      </c>
+      <c r="AA45" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="Z45" s="133">
-        <v>46188</v>
-      </c>
-      <c r="AA45" s="124" t="s">
-        <v>129</v>
-      </c>
     </row>
-    <row r="46" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="142"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="106"/>
-      <c r="H46" s="109"/>
-      <c r="I46" s="106"/>
-      <c r="J46" s="125"/>
+    <row r="46" spans="1:29" ht="16.5" customHeight="1">
+      <c r="A46" s="135"/>
+      <c r="B46" s="125"/>
+      <c r="C46" s="136"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="138"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12010,43 +12010,47 @@
       <c r="R46" s="19">
         <v>0.56000000000000005</v>
       </c>
-      <c r="S46" s="19"/>
-      <c r="T46" s="19"/>
+      <c r="S46" s="19">
+        <v>0.39</v>
+      </c>
+      <c r="T46" s="19">
+        <v>0.37</v>
+      </c>
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="128"/>
-      <c r="Y46" s="131"/>
-      <c r="Z46" s="131"/>
-      <c r="AA46" s="124"/>
+      <c r="X46" s="145"/>
+      <c r="Y46" s="139"/>
+      <c r="Z46" s="139"/>
+      <c r="AA46" s="144"/>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A47" s="142"/>
-      <c r="B47" s="91" t="s">
-        <v>132</v>
-      </c>
-      <c r="C47" s="92" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47" s="90" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="F47" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="G47" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="H47" s="109" t="s">
+    <row r="47" spans="1:29">
+      <c r="A47" s="135"/>
+      <c r="B47" s="125" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="105" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="F47" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="G47" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="106" t="s">
-        <v>81</v>
-      </c>
-      <c r="J47" s="125" t="s">
+      <c r="I47" s="104" t="s">
+        <v>82</v>
+      </c>
+      <c r="J47" s="138" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12088,24 +12092,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="128"/>
-      <c r="Y47" s="131"/>
-      <c r="Z47" s="131"/>
-      <c r="AA47" s="90" t="s">
-        <v>134</v>
+      <c r="X47" s="145"/>
+      <c r="Y47" s="139"/>
+      <c r="Z47" s="139"/>
+      <c r="AA47" s="105" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="142"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="106"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="106"/>
-      <c r="H48" s="109"/>
-      <c r="I48" s="106"/>
-      <c r="J48" s="125"/>
+    <row r="48" spans="1:29" ht="20.45" customHeight="1">
+      <c r="A48" s="135"/>
+      <c r="B48" s="125"/>
+      <c r="C48" s="136"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="138"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12138,40 +12142,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="128"/>
-      <c r="Y48" s="131"/>
-      <c r="Z48" s="131"/>
-      <c r="AA48" s="90"/>
+      <c r="X48" s="145"/>
+      <c r="Y48" s="139"/>
+      <c r="Z48" s="139"/>
+      <c r="AA48" s="105"/>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A49" s="141" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="148" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="92" t="s">
+    <row r="49" spans="1:27">
+      <c r="A49" s="90" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" s="141" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" s="136" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="90" t="s">
-        <v>137</v>
-      </c>
-      <c r="E49" s="106">
+      <c r="D49" s="105" t="s">
+        <v>139</v>
+      </c>
+      <c r="E49" s="104">
         <v>74</v>
       </c>
-      <c r="F49" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="G49" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="H49" s="109" t="s">
+      <c r="F49" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="G49" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="106" t="s">
+      <c r="I49" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="105" t="s">
+      <c r="J49" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12213,24 +12217,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="128"/>
-      <c r="Y49" s="130"/>
-      <c r="Z49" s="131"/>
-      <c r="AA49" s="124" t="s">
-        <v>138</v>
+      <c r="X49" s="145"/>
+      <c r="Y49" s="140"/>
+      <c r="Z49" s="139"/>
+      <c r="AA49" s="144" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A50" s="141"/>
-      <c r="B50" s="148"/>
-      <c r="C50" s="92"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="106"/>
-      <c r="F50" s="106"/>
-      <c r="G50" s="106"/>
-      <c r="H50" s="109"/>
-      <c r="I50" s="106"/>
-      <c r="J50" s="105"/>
+    <row r="50" spans="1:27">
+      <c r="A50" s="90"/>
+      <c r="B50" s="141"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="106"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12264,40 +12268,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="76"/>
-      <c r="X50" s="128"/>
-      <c r="Y50" s="130"/>
-      <c r="Z50" s="131"/>
-      <c r="AA50" s="124"/>
+      <c r="X50" s="145"/>
+      <c r="Y50" s="140"/>
+      <c r="Z50" s="139"/>
+      <c r="AA50" s="144"/>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A51" s="142" t="s">
+    <row r="51" spans="1:27">
+      <c r="A51" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="91" t="s">
-        <v>139</v>
-      </c>
-      <c r="C51" s="92" t="s">
-        <v>73</v>
-      </c>
-      <c r="D51" s="90" t="s">
-        <v>140</v>
-      </c>
-      <c r="E51" s="106">
+      <c r="B51" s="125" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="136" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" s="105" t="s">
+        <v>142</v>
+      </c>
+      <c r="E51" s="104">
         <v>33.1</v>
       </c>
-      <c r="F51" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="G51" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="H51" s="109" t="s">
+      <c r="F51" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="G51" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="H51" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="106" t="s">
+      <c r="I51" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="105" t="s">
+      <c r="J51" s="106" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12331,24 +12335,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="128"/>
-      <c r="Y51" s="131"/>
-      <c r="Z51" s="131"/>
-      <c r="AA51" s="93" t="s">
-        <v>141</v>
+      <c r="X51" s="145"/>
+      <c r="Y51" s="139"/>
+      <c r="Z51" s="139"/>
+      <c r="AA51" s="123" t="s">
+        <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="142"/>
-      <c r="B52" s="91"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="106"/>
-      <c r="F52" s="106"/>
-      <c r="G52" s="106"/>
-      <c r="H52" s="109"/>
-      <c r="I52" s="106"/>
-      <c r="J52" s="105"/>
+    <row r="52" spans="1:27" ht="15" thickBot="1">
+      <c r="A52" s="135"/>
+      <c r="B52" s="125"/>
+      <c r="C52" s="136"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="103"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="106"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12380,42 +12384,244 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="128"/>
-      <c r="Y52" s="131"/>
-      <c r="Z52" s="131"/>
-      <c r="AA52" s="93"/>
+      <c r="X52" s="145"/>
+      <c r="Y52" s="139"/>
+      <c r="Z52" s="139"/>
+      <c r="AA52" s="123"/>
     </row>
-    <row r="54" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="58" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="60" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="62" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="64" spans="1:27" ht="14.45" customHeight="1"/>
+    <row r="66" ht="14.45" customHeight="1"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="Z10:Z11"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AA30:AA31"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="E30:G31"/>
@@ -12440,230 +12646,28 @@
     <mergeCell ref="I36:I37"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="X26:X27"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -12739,7 +12743,7 @@
       <formula xml:space="preserve"> AND(OR($H6="Higher the better", $H6="Higher the Better"), L7&gt;= L6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L23:W27 L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15">
+  <conditionalFormatting sqref="L7:W7 L9:W9 L11:W11 L13:W13 L17:W17 L19:W19 L21:W21 L29:W29 L31:W31 L33:W33 N35 Q35 T35:W35 O37 S37:W37 L15:W15 L23:W27">
     <cfRule type="containsBlanks" dxfId="58" priority="245">
       <formula>LEN(TRIM(L7))=0</formula>
     </cfRule>
@@ -13120,8 +13124,9 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13134,46 +13139,24 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A947F7A-4B36-444A-8EB5-D7532A79A0CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CFCB212-7126-4863-80E7-8646D7325D33}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="68108f69-118e-4385-83b3-00743b1bf54c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f5a961e1-edc1-4f62-8655-e8a46ef79e5c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Strategic Execution Dashboard.xlsx
+++ b/data/Strategic Execution Dashboard.xlsx
@@ -1569,248 +1569,248 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9569,10 +9569,10 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="23.45">
-      <c r="A3" s="161" t="s">
+      <c r="A3" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="161"/>
+      <c r="B3" s="110"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -9593,36 +9593,36 @@
       <c r="AA3" s="14"/>
     </row>
     <row r="4" spans="1:27" s="5" customFormat="1">
-      <c r="A4" s="162" t="str">
+      <c r="A4" s="112" t="str">
         <f ca="1">"Current Month-Year " &amp; ":" &amp; TEXT(TODAY(),"YYYY-MM")</f>
         <v>Current Month-Year :2026-10</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="162"/>
-      <c r="G4" s="162"/>
-      <c r="H4" s="162"/>
-      <c r="I4" s="162"/>
-      <c r="J4" s="162"/>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="162"/>
-      <c r="R4" s="162"/>
-      <c r="S4" s="162"/>
-      <c r="T4" s="162"/>
-      <c r="U4" s="162"/>
-      <c r="V4" s="162"/>
-      <c r="W4" s="162"/>
-      <c r="X4" s="162"/>
-      <c r="Y4" s="162"/>
-      <c r="Z4" s="162"/>
-      <c r="AA4" s="162"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
     </row>
     <row r="5" spans="1:27" ht="27" customHeight="1">
       <c r="A5" s="88" t="s">
@@ -9637,11 +9637,11 @@
       <c r="D5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="163" t="s">
+      <c r="E5" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="163"/>
-      <c r="G5" s="163"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
       <c r="H5" s="89" t="s">
         <v>8</v>
       </c>
@@ -9704,30 +9704,30 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="136" t="s">
+      <c r="C6" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="105" t="s">
+      <c r="D6" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="104">
+      <c r="E6" s="108">
         <v>10</v>
       </c>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="103" t="s">
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="104" t="s">
+      <c r="I6" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="106" t="s">
+      <c r="J6" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K6" s="23" t="s">
@@ -9769,24 +9769,24 @@
       <c r="W6" s="28">
         <v>0.05</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="101"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="117" t="s">
+      <c r="X6" s="106"/>
+      <c r="Y6" s="113"/>
+      <c r="Z6" s="113"/>
+      <c r="AA6" s="123" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="92"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="106"/>
+      <c r="A7" s="109"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="107"/>
       <c r="K7" s="23" t="s">
         <v>55</v>
       </c>
@@ -9820,34 +9820,34 @@
       <c r="U7" s="52"/>
       <c r="V7" s="52"/>
       <c r="W7" s="52"/>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="130"/>
-      <c r="Z7" s="130"/>
-      <c r="AA7" s="118"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
+      <c r="AA7" s="124"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="92"/>
-      <c r="B8" s="125" t="s">
+      <c r="A8" s="109"/>
+      <c r="B8" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="136" t="s">
+      <c r="C8" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="105" t="s">
+      <c r="D8" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="104">
+      <c r="E8" s="108">
         <v>90</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="103" t="s">
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="106" t="s">
+      <c r="J8" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
@@ -9879,28 +9879,28 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="28"/>
-      <c r="X8" s="111"/>
-      <c r="Y8" s="129" t="s">
+      <c r="X8" s="94"/>
+      <c r="Y8" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="Z8" s="115">
+      <c r="Z8" s="114">
         <v>46231</v>
       </c>
-      <c r="AA8" s="117" t="s">
+      <c r="AA8" s="123" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="92"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="106"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="107"/>
       <c r="K9" s="23" t="s">
         <v>55</v>
       </c>
@@ -9934,34 +9934,34 @@
       <c r="U9" s="54"/>
       <c r="V9" s="54"/>
       <c r="W9" s="54"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="130"/>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="118"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="96"/>
+      <c r="Z9" s="115"/>
+      <c r="AA9" s="124"/>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="92"/>
-      <c r="B10" s="125" t="s">
+      <c r="A10" s="109"/>
+      <c r="B10" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="136" t="s">
+      <c r="C10" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="105" t="s">
+      <c r="D10" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="108">
         <v>1</v>
       </c>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="103" t="s">
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="104" t="s">
+      <c r="I10" s="108" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="106" t="s">
+      <c r="J10" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -9995,24 +9995,24 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="111"/>
-      <c r="Y10" s="119"/>
-      <c r="Z10" s="164"/>
-      <c r="AA10" s="117" t="s">
+      <c r="X10" s="94"/>
+      <c r="Y10" s="163"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="123" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" thickBot="1">
-      <c r="A11" s="92"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="106"/>
+      <c r="A11" s="109"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="107"/>
       <c r="K11" s="23" t="s">
         <v>55</v>
       </c>
@@ -10046,36 +10046,36 @@
       <c r="U11" s="32"/>
       <c r="V11" s="32"/>
       <c r="W11" s="33"/>
-      <c r="X11" s="111"/>
-      <c r="Y11" s="120"/>
-      <c r="Z11" s="165"/>
-      <c r="AA11" s="118"/>
+      <c r="X11" s="94"/>
+      <c r="Y11" s="164"/>
+      <c r="Z11" s="118"/>
+      <c r="AA11" s="124"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="105" t="s">
+      <c r="D12" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="104">
+      <c r="E12" s="108">
         <v>84</v>
       </c>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="103" t="s">
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="104" t="s">
+      <c r="I12" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="106" t="s">
+      <c r="J12" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -10117,24 +10117,24 @@
       <c r="W12" s="26">
         <v>0.79</v>
       </c>
-      <c r="X12" s="111"/>
-      <c r="Y12" s="129"/>
-      <c r="Z12" s="130"/>
-      <c r="AA12" s="117" t="s">
+      <c r="X12" s="94"/>
+      <c r="Y12" s="95"/>
+      <c r="Z12" s="96"/>
+      <c r="AA12" s="123" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="92"/>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="106"/>
+      <c r="A13" s="109"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="107"/>
       <c r="K13" s="23" t="s">
         <v>55</v>
       </c>
@@ -10166,34 +10166,34 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="29"/>
-      <c r="X13" s="111"/>
-      <c r="Y13" s="130"/>
-      <c r="Z13" s="130"/>
-      <c r="AA13" s="118"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="96"/>
+      <c r="Z13" s="96"/>
+      <c r="AA13" s="124"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="92"/>
-      <c r="B14" s="123" t="s">
+      <c r="A14" s="109"/>
+      <c r="B14" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="C14" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="105" t="s">
+      <c r="D14" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="104">
+      <c r="E14" s="108">
         <v>54.6</v>
       </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="103" t="s">
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="104" t="s">
+      <c r="I14" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="106" t="s">
+      <c r="J14" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -10229,26 +10229,26 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="38"/>
-      <c r="X14" s="111" t="s">
+      <c r="X14" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="Y14" s="100" t="s">
+      <c r="Y14" s="152" t="s">
         <v>72</v>
       </c>
-      <c r="Z14" s="100"/>
-      <c r="AA14" s="127"/>
+      <c r="Z14" s="152"/>
+      <c r="AA14" s="151"/>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1">
-      <c r="A15" s="92"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="106"/>
+      <c r="A15" s="109"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="107"/>
       <c r="K15" s="23" t="s">
         <v>55</v>
       </c>
@@ -10282,36 +10282,36 @@
       <c r="U15" s="32"/>
       <c r="V15" s="32"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="111"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-      <c r="AA15" s="128"/>
+      <c r="X15" s="94"/>
+      <c r="Y15" s="113"/>
+      <c r="Z15" s="113"/>
+      <c r="AA15" s="131"/>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="C16" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="105" t="s">
+      <c r="D16" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="104" t="s">
+      <c r="E16" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="103" t="s">
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="104" t="s">
+      <c r="I16" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -10345,28 +10345,28 @@
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="26"/>
-      <c r="X16" s="111" t="s">
+      <c r="X16" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="Y16" s="129" t="s">
+      <c r="Y16" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="Z16" s="116"/>
-      <c r="AA16" s="117" t="s">
+      <c r="Z16" s="115"/>
+      <c r="AA16" s="123" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="92"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="106"/>
+      <c r="A17" s="109"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="107"/>
       <c r="K17" s="23" t="s">
         <v>55</v>
       </c>
@@ -10398,34 +10398,34 @@
       <c r="U17" s="19"/>
       <c r="V17" s="19"/>
       <c r="W17" s="29"/>
-      <c r="X17" s="111"/>
-      <c r="Y17" s="130"/>
-      <c r="Z17" s="116"/>
-      <c r="AA17" s="118"/>
+      <c r="X17" s="94"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="115"/>
+      <c r="AA17" s="124"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="92"/>
-      <c r="B18" s="123" t="s">
+      <c r="A18" s="109"/>
+      <c r="B18" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="123" t="s">
+      <c r="C18" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="123" t="s">
+      <c r="D18" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="104" t="s">
+      <c r="E18" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="103" t="s">
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="104" t="s">
+      <c r="I18" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="106" t="s">
+      <c r="J18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -10462,26 +10462,26 @@
       <c r="U18" s="48"/>
       <c r="V18" s="48"/>
       <c r="W18" s="48"/>
-      <c r="X18" s="134" t="s">
+      <c r="X18" s="157" t="s">
         <v>83</v>
       </c>
-      <c r="Y18" s="134"/>
-      <c r="Z18" s="131">
+      <c r="Y18" s="157"/>
+      <c r="Z18" s="154">
         <v>46108</v>
       </c>
-      <c r="AA18" s="133"/>
+      <c r="AA18" s="156"/>
     </row>
     <row r="19" spans="1:27" ht="18.600000000000001" customHeight="1">
-      <c r="A19" s="92"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="106"/>
+      <c r="A19" s="109"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="107"/>
       <c r="K19" s="23" t="s">
         <v>55</v>
       </c>
@@ -10515,34 +10515,34 @@
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
       <c r="W19" s="50"/>
-      <c r="X19" s="134"/>
-      <c r="Y19" s="134"/>
-      <c r="Z19" s="132"/>
-      <c r="AA19" s="133"/>
+      <c r="X19" s="157"/>
+      <c r="Y19" s="157"/>
+      <c r="Z19" s="155"/>
+      <c r="AA19" s="156"/>
     </row>
     <row r="20" spans="1:27" ht="24" customHeight="1">
-      <c r="A20" s="92"/>
-      <c r="B20" s="123" t="s">
+      <c r="A20" s="109"/>
+      <c r="B20" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D20" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="104" t="s">
+      <c r="E20" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="103" t="s">
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="104" t="s">
+      <c r="I20" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="106" t="s">
+      <c r="J20" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -10576,28 +10576,28 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="28"/>
-      <c r="X20" s="166" t="s">
+      <c r="X20" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="Y20" s="168" t="s">
+      <c r="Y20" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="152" t="s">
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="125" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A21" s="92"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="106"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="107"/>
       <c r="K21" s="23" t="s">
         <v>55</v>
       </c>
@@ -10629,36 +10629,36 @@
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="31"/>
-      <c r="X21" s="167"/>
-      <c r="Y21" s="169"/>
-      <c r="Z21" s="94"/>
-      <c r="AA21" s="152"/>
+      <c r="X21" s="100"/>
+      <c r="Y21" s="102"/>
+      <c r="Z21" s="119"/>
+      <c r="AA21" s="125"/>
     </row>
     <row r="22" spans="1:27" ht="15.95" customHeight="1">
-      <c r="A22" s="92" t="s">
+      <c r="A22" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="124" t="s">
+      <c r="C22" s="122" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="93" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="104">
+      <c r="E22" s="108">
         <v>90</v>
       </c>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="103" t="s">
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="104" t="s">
+      <c r="I22" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="106" t="s">
+      <c r="J22" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -10700,24 +10700,24 @@
       <c r="W22" s="28">
         <v>0.9</v>
       </c>
-      <c r="X22" s="170"/>
-      <c r="Y22" s="129"/>
-      <c r="Z22" s="115">
+      <c r="X22" s="105"/>
+      <c r="Y22" s="95"/>
+      <c r="Z22" s="114">
         <v>46257</v>
       </c>
-      <c r="AA22" s="113"/>
+      <c r="AA22" s="161"/>
     </row>
     <row r="23" spans="1:27" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A23" s="93"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="106"/>
+      <c r="A23" s="168"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="107"/>
       <c r="K23" s="23" t="s">
         <v>55</v>
       </c>
@@ -10749,40 +10749,40 @@
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="31"/>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="130"/>
-      <c r="Z23" s="116"/>
-      <c r="AA23" s="114"/>
+      <c r="X23" s="106"/>
+      <c r="Y23" s="96"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="162"/>
     </row>
     <row r="24" spans="1:27" ht="17.45" customHeight="1">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="124" t="s">
+      <c r="C24" s="122" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="105" t="s">
+      <c r="D24" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="104" t="s">
+      <c r="E24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="104" t="s">
+      <c r="F24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="104" t="s">
+      <c r="G24" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H24" s="103" t="s">
+      <c r="H24" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="104" t="s">
+      <c r="I24" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="102" t="s">
+      <c r="J24" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -10816,24 +10816,24 @@
         <v>96</v>
       </c>
       <c r="W24" s="39"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="100"/>
-      <c r="Z24" s="94"/>
-      <c r="AA24" s="117" t="s">
+      <c r="X24" s="137"/>
+      <c r="Y24" s="152"/>
+      <c r="Z24" s="119"/>
+      <c r="AA24" s="123" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" thickBot="1">
-      <c r="A25" s="91"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="102"/>
+      <c r="A25" s="167"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="120"/>
       <c r="K25" s="23" t="s">
         <v>55</v>
       </c>
@@ -10869,34 +10869,34 @@
         <v>96</v>
       </c>
       <c r="W25" s="57"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="118"/>
+      <c r="X25" s="106"/>
+      <c r="Y25" s="113"/>
+      <c r="Z25" s="153"/>
+      <c r="AA25" s="124"/>
     </row>
     <row r="26" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A26" s="91"/>
-      <c r="B26" s="125" t="s">
+      <c r="A26" s="167"/>
+      <c r="B26" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="126" t="s">
+      <c r="C26" s="160" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="104">
+      <c r="E26" s="108">
         <v>34</v>
       </c>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="103" t="s">
+      <c r="F26" s="158"/>
+      <c r="G26" s="158"/>
+      <c r="H26" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="104" t="s">
+      <c r="I26" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="106" t="s">
+      <c r="J26" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -10932,24 +10932,24 @@
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="26"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="130"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="117" t="s">
+      <c r="X26" s="94"/>
+      <c r="Y26" s="96"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="123" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A27" s="91"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="106"/>
+      <c r="A27" s="167"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="160"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="158"/>
+      <c r="G27" s="158"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="107"/>
       <c r="K27" s="23" t="s">
         <v>55</v>
       </c>
@@ -10983,34 +10983,34 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="29"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="130"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="118"/>
+      <c r="X27" s="94"/>
+      <c r="Y27" s="96"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="124"/>
     </row>
     <row r="28" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A28" s="91"/>
-      <c r="B28" s="105" t="s">
+      <c r="A28" s="167"/>
+      <c r="B28" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="123" t="s">
+      <c r="C28" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="105" t="s">
+      <c r="D28" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="104" t="s">
+      <c r="E28" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="103" t="s">
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="106" t="s">
+      <c r="J28" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -11044,26 +11044,26 @@
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="158" t="s">
+      <c r="X28" s="103" t="s">
         <v>103</v>
       </c>
-      <c r="Y28" s="96"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="153" t="s">
+      <c r="Y28" s="97"/>
+      <c r="Z28" s="119"/>
+      <c r="AA28" s="128" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="15" thickBot="1">
-      <c r="A29" s="91"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="106"/>
+      <c r="A29" s="167"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="107"/>
       <c r="K29" s="23" t="s">
         <v>55</v>
       </c>
@@ -11095,32 +11095,32 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="29"/>
-      <c r="X29" s="159"/>
-      <c r="Y29" s="97"/>
-      <c r="Z29" s="95"/>
-      <c r="AA29" s="154"/>
+      <c r="X29" s="104"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="153"/>
+      <c r="AA29" s="129"/>
     </row>
     <row r="30" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A30" s="91"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="123" t="s">
+      <c r="A30" s="167"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="105" t="s">
+      <c r="D30" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="104" t="s">
+      <c r="E30" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="103" t="s">
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="104" t="s">
+      <c r="I30" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -11154,22 +11154,22 @@
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="158"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="94"/>
-      <c r="AA30" s="107"/>
+      <c r="X30" s="103"/>
+      <c r="Y30" s="152"/>
+      <c r="Z30" s="119"/>
+      <c r="AA30" s="165"/>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="91"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="106"/>
+      <c r="A31" s="167"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="107"/>
       <c r="K31" s="23" t="s">
         <v>55</v>
       </c>
@@ -11201,34 +11201,34 @@
       <c r="U31" s="45"/>
       <c r="V31" s="45"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="159"/>
-      <c r="Y31" s="101"/>
-      <c r="Z31" s="95"/>
-      <c r="AA31" s="108"/>
+      <c r="X31" s="104"/>
+      <c r="Y31" s="113"/>
+      <c r="Z31" s="153"/>
+      <c r="AA31" s="166"/>
     </row>
     <row r="32" spans="1:27" ht="14.45" customHeight="1">
-      <c r="A32" s="91"/>
-      <c r="B32" s="123" t="s">
+      <c r="A32" s="167"/>
+      <c r="B32" s="93" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="124" t="s">
+      <c r="C32" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="105" t="s">
+      <c r="D32" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="104" t="s">
+      <c r="E32" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="103" t="s">
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="104" t="s">
+      <c r="I32" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J32" s="106" t="s">
+      <c r="J32" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -11262,28 +11262,28 @@
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="34"/>
-      <c r="X32" s="98" t="s">
+      <c r="X32" s="169" t="s">
         <v>108</v>
       </c>
-      <c r="Y32" s="96" t="s">
+      <c r="Y32" s="97" t="s">
         <v>109</v>
       </c>
-      <c r="Z32" s="94"/>
-      <c r="AA32" s="117" t="s">
+      <c r="Z32" s="119"/>
+      <c r="AA32" s="123" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A33" s="91"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="106"/>
+      <c r="A33" s="167"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="107"/>
       <c r="K33" s="23" t="s">
         <v>55</v>
       </c>
@@ -11315,36 +11315,36 @@
       <c r="U33" s="32"/>
       <c r="V33" s="32"/>
       <c r="W33" s="33"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="97"/>
-      <c r="Z33" s="95"/>
-      <c r="AA33" s="118"/>
+      <c r="X33" s="170"/>
+      <c r="Y33" s="98"/>
+      <c r="Z33" s="153"/>
+      <c r="AA33" s="124"/>
     </row>
     <row r="34" spans="1:29">
-      <c r="A34" s="92" t="s">
+      <c r="A34" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="143" t="s">
+      <c r="B34" s="148" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="123" t="s">
+      <c r="C34" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="105" t="s">
+      <c r="D34" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="104">
+      <c r="E34" s="108">
         <v>90</v>
       </c>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="103" t="s">
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="104" t="s">
+      <c r="I34" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="102" t="s">
+      <c r="J34" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -11370,24 +11370,24 @@
       <c r="W34" s="26">
         <v>0.9</v>
       </c>
-      <c r="X34" s="111"/>
-      <c r="Y34" s="130"/>
-      <c r="Z34" s="116"/>
-      <c r="AA34" s="117" t="s">
+      <c r="X34" s="94"/>
+      <c r="Y34" s="96"/>
+      <c r="Z34" s="115"/>
+      <c r="AA34" s="123" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:29">
-      <c r="A35" s="92"/>
-      <c r="B35" s="143"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="102"/>
+      <c r="A35" s="109"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="120"/>
       <c r="K35" s="23" t="s">
         <v>55</v>
       </c>
@@ -11419,34 +11419,34 @@
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="29"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="130"/>
-      <c r="Z35" s="116"/>
-      <c r="AA35" s="118"/>
+      <c r="X35" s="94"/>
+      <c r="Y35" s="96"/>
+      <c r="Z35" s="115"/>
+      <c r="AA35" s="124"/>
     </row>
     <row r="36" spans="1:29">
-      <c r="A36" s="92"/>
-      <c r="B36" s="143" t="s">
+      <c r="A36" s="109"/>
+      <c r="B36" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="123" t="s">
+      <c r="C36" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="105" t="s">
+      <c r="D36" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="104">
+      <c r="E36" s="108">
         <v>83</v>
       </c>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="103" t="s">
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="104" t="s">
+      <c r="I36" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="160" t="s">
+      <c r="J36" s="121" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -11468,28 +11468,28 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="28"/>
-      <c r="X36" s="111" t="s">
+      <c r="X36" s="94" t="s">
         <v>113</v>
       </c>
-      <c r="Y36" s="129" t="s">
+      <c r="Y36" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="117" t="s">
+      <c r="Z36" s="115"/>
+      <c r="AA36" s="123" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:29">
-      <c r="A37" s="92"/>
-      <c r="B37" s="143"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="160"/>
+      <c r="A37" s="109"/>
+      <c r="B37" s="148"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="121"/>
       <c r="K37" s="23" t="s">
         <v>55</v>
       </c>
@@ -11519,45 +11519,45 @@
       <c r="U37" s="58"/>
       <c r="V37" s="58"/>
       <c r="W37" s="59"/>
-      <c r="X37" s="109"/>
-      <c r="Y37" s="96"/>
-      <c r="Z37" s="94"/>
-      <c r="AA37" s="152"/>
+      <c r="X37" s="137"/>
+      <c r="Y37" s="97"/>
+      <c r="Z37" s="119"/>
+      <c r="AA37" s="125"/>
     </row>
     <row r="38" spans="1:29" s="5" customFormat="1">
-      <c r="A38" s="146"/>
-      <c r="B38" s="146"/>
-      <c r="C38" s="146"/>
-      <c r="D38" s="146"/>
-      <c r="E38" s="146"/>
-      <c r="F38" s="146"/>
-      <c r="G38" s="146"/>
-      <c r="H38" s="146"/>
-      <c r="I38" s="146"/>
-      <c r="J38" s="146"/>
-      <c r="K38" s="146"/>
-      <c r="L38" s="146"/>
-      <c r="M38" s="146"/>
-      <c r="N38" s="146"/>
-      <c r="O38" s="146"/>
-      <c r="P38" s="147"/>
-      <c r="Q38" s="147"/>
-      <c r="R38" s="147"/>
-      <c r="S38" s="147"/>
-      <c r="T38" s="147"/>
-      <c r="U38" s="147"/>
-      <c r="V38" s="147"/>
-      <c r="W38" s="147"/>
-      <c r="X38" s="147"/>
-      <c r="Y38" s="147"/>
-      <c r="Z38" s="147"/>
-      <c r="AA38" s="147"/>
+      <c r="A38" s="138"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="138"/>
+      <c r="K38" s="138"/>
+      <c r="L38" s="138"/>
+      <c r="M38" s="138"/>
+      <c r="N38" s="138"/>
+      <c r="O38" s="138"/>
+      <c r="P38" s="139"/>
+      <c r="Q38" s="139"/>
+      <c r="R38" s="139"/>
+      <c r="S38" s="139"/>
+      <c r="T38" s="139"/>
+      <c r="U38" s="139"/>
+      <c r="V38" s="139"/>
+      <c r="W38" s="139"/>
+      <c r="X38" s="139"/>
+      <c r="Y38" s="139"/>
+      <c r="Z38" s="139"/>
+      <c r="AA38" s="139"/>
     </row>
     <row r="39" spans="1:29" s="5" customFormat="1" ht="23.45">
-      <c r="A39" s="148" t="s">
+      <c r="A39" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="148"/>
+      <c r="B39" s="141"/>
       <c r="C39" s="60"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -11668,34 +11668,34 @@
       </c>
     </row>
     <row r="41" spans="1:29">
-      <c r="A41" s="149" t="s">
+      <c r="A41" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="150" t="s">
+      <c r="B41" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="151" t="s">
+      <c r="C41" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="142" t="s">
+      <c r="D41" s="147" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="121" t="s">
+      <c r="E41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="F41" s="121" t="s">
+      <c r="F41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="G41" s="121" t="s">
+      <c r="G41" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="122" t="s">
+      <c r="H41" s="159" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="121" t="s">
+      <c r="I41" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="J41" s="137" t="s">
+      <c r="J41" s="149" t="s">
         <v>52</v>
       </c>
       <c r="K41" s="63" t="s">
@@ -11737,25 +11737,25 @@
       <c r="W41" s="65">
         <v>3.32E-2</v>
       </c>
-      <c r="X41" s="157"/>
-      <c r="Y41" s="128"/>
-      <c r="Z41" s="128"/>
-      <c r="AA41" s="118" t="s">
+      <c r="X41" s="136"/>
+      <c r="Y41" s="131"/>
+      <c r="Z41" s="131"/>
+      <c r="AA41" s="124" t="s">
         <v>124</v>
       </c>
       <c r="AC41" s="12"/>
     </row>
     <row r="42" spans="1:29" ht="23.1" customHeight="1">
-      <c r="A42" s="90"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="136"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="138"/>
+      <c r="A42" s="143"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="92"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="108"/>
+      <c r="J42" s="127"/>
       <c r="K42" s="23" t="s">
         <v>55</v>
       </c>
@@ -11789,40 +11789,40 @@
       <c r="U42" s="57"/>
       <c r="V42" s="57"/>
       <c r="W42" s="61"/>
-      <c r="X42" s="157"/>
-      <c r="Y42" s="128"/>
-      <c r="Z42" s="128"/>
-      <c r="AA42" s="144"/>
+      <c r="X42" s="136"/>
+      <c r="Y42" s="131"/>
+      <c r="Z42" s="131"/>
+      <c r="AA42" s="126"/>
     </row>
     <row r="43" spans="1:29">
-      <c r="A43" s="135" t="s">
+      <c r="A43" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="125" t="s">
+      <c r="B43" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="136" t="s">
+      <c r="C43" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="105" t="s">
+      <c r="D43" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="E43" s="104" t="s">
+      <c r="E43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="104" t="s">
+      <c r="F43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="104" t="s">
+      <c r="G43" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H43" s="103" t="s">
+      <c r="H43" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="104" t="s">
+      <c r="I43" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="102" t="s">
+      <c r="J43" s="120" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="23" t="s">
@@ -11844,28 +11844,28 @@
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
       <c r="W43" s="39"/>
-      <c r="X43" s="145" t="s">
+      <c r="X43" s="130" t="s">
         <v>128</v>
       </c>
-      <c r="Y43" s="140" t="s">
+      <c r="Y43" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="Z43" s="139"/>
-      <c r="AA43" s="155" t="s">
+      <c r="Z43" s="133"/>
+      <c r="AA43" s="134" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:29">
-      <c r="A44" s="135"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="136"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="112"/>
-      <c r="J44" s="102"/>
+      <c r="A44" s="144"/>
+      <c r="B44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
+      <c r="H44" s="111"/>
+      <c r="I44" s="158"/>
+      <c r="J44" s="120"/>
       <c r="K44" s="23" t="s">
         <v>55</v>
       </c>
@@ -11901,38 +11901,38 @@
         <v>96</v>
       </c>
       <c r="W44" s="57"/>
-      <c r="X44" s="145"/>
-      <c r="Y44" s="140"/>
-      <c r="Z44" s="139"/>
-      <c r="AA44" s="155"/>
+      <c r="X44" s="130"/>
+      <c r="Y44" s="132"/>
+      <c r="Z44" s="133"/>
+      <c r="AA44" s="134"/>
     </row>
     <row r="45" spans="1:29">
-      <c r="A45" s="135"/>
-      <c r="B45" s="125" t="s">
+      <c r="A45" s="144"/>
+      <c r="B45" s="91" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="136" t="s">
+      <c r="C45" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="105" t="s">
+      <c r="D45" s="90" t="s">
         <v>132</v>
       </c>
-      <c r="E45" s="104" t="s">
+      <c r="E45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F45" s="104" t="s">
+      <c r="F45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="104" t="s">
+      <c r="G45" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="103" t="s">
+      <c r="H45" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="104" t="s">
+      <c r="I45" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J45" s="138" t="s">
+      <c r="J45" s="127" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -11964,28 +11964,28 @@
       <c r="U45" s="36"/>
       <c r="V45" s="36"/>
       <c r="W45" s="39"/>
-      <c r="X45" s="145"/>
-      <c r="Y45" s="140" t="s">
+      <c r="X45" s="130"/>
+      <c r="Y45" s="132" t="s">
         <v>133</v>
       </c>
-      <c r="Z45" s="156">
+      <c r="Z45" s="135">
         <v>46188</v>
       </c>
-      <c r="AA45" s="144" t="s">
+      <c r="AA45" s="126" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="16.5" customHeight="1">
-      <c r="A46" s="135"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="136"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="138"/>
+      <c r="A46" s="144"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="127"/>
       <c r="K46" s="23" t="s">
         <v>55</v>
       </c>
@@ -12019,38 +12019,38 @@
       <c r="U46" s="19"/>
       <c r="V46" s="19"/>
       <c r="W46" s="29"/>
-      <c r="X46" s="145"/>
-      <c r="Y46" s="139"/>
-      <c r="Z46" s="139"/>
-      <c r="AA46" s="144"/>
+      <c r="X46" s="130"/>
+      <c r="Y46" s="133"/>
+      <c r="Z46" s="133"/>
+      <c r="AA46" s="126"/>
     </row>
     <row r="47" spans="1:29">
-      <c r="A47" s="135"/>
-      <c r="B47" s="125" t="s">
+      <c r="A47" s="144"/>
+      <c r="B47" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="136" t="s">
+      <c r="C47" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="105" t="s">
+      <c r="D47" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="104" t="s">
+      <c r="E47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F47" s="104" t="s">
+      <c r="F47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G47" s="104" t="s">
+      <c r="G47" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H47" s="103" t="s">
+      <c r="H47" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="104" t="s">
+      <c r="I47" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="J47" s="138" t="s">
+      <c r="J47" s="127" t="s">
         <v>52</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -12092,24 +12092,24 @@
       <c r="W47" s="40">
         <v>67</v>
       </c>
-      <c r="X47" s="145"/>
-      <c r="Y47" s="139"/>
-      <c r="Z47" s="139"/>
-      <c r="AA47" s="105" t="s">
+      <c r="X47" s="130"/>
+      <c r="Y47" s="133"/>
+      <c r="Z47" s="133"/>
+      <c r="AA47" s="90" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="20.45" customHeight="1">
-      <c r="A48" s="135"/>
-      <c r="B48" s="125"/>
-      <c r="C48" s="136"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="138"/>
+      <c r="A48" s="144"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108"/>
+      <c r="H48" s="111"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="127"/>
       <c r="K48" s="23" t="s">
         <v>55</v>
       </c>
@@ -12142,40 +12142,40 @@
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
       <c r="W48" s="27"/>
-      <c r="X48" s="145"/>
-      <c r="Y48" s="139"/>
-      <c r="Z48" s="139"/>
-      <c r="AA48" s="105"/>
+      <c r="X48" s="130"/>
+      <c r="Y48" s="133"/>
+      <c r="Z48" s="133"/>
+      <c r="AA48" s="90"/>
     </row>
     <row r="49" spans="1:27">
-      <c r="A49" s="90" t="s">
+      <c r="A49" s="143" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="141" t="s">
+      <c r="B49" s="150" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="136" t="s">
+      <c r="C49" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="105" t="s">
+      <c r="D49" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="E49" s="104">
+      <c r="E49" s="108">
         <v>74</v>
       </c>
-      <c r="F49" s="104" t="s">
+      <c r="F49" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G49" s="104" t="s">
+      <c r="G49" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H49" s="103" t="s">
+      <c r="H49" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="104" t="s">
+      <c r="I49" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="106" t="s">
+      <c r="J49" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K49" s="23" t="s">
@@ -12217,24 +12217,24 @@
       <c r="W49" s="41">
         <v>0.73999999999999966</v>
       </c>
-      <c r="X49" s="145"/>
-      <c r="Y49" s="140"/>
-      <c r="Z49" s="139"/>
-      <c r="AA49" s="144" t="s">
+      <c r="X49" s="130"/>
+      <c r="Y49" s="132"/>
+      <c r="Z49" s="133"/>
+      <c r="AA49" s="126" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:27">
-      <c r="A50" s="90"/>
-      <c r="B50" s="141"/>
-      <c r="C50" s="136"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="106"/>
+      <c r="A50" s="143"/>
+      <c r="B50" s="150"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="111"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="107"/>
       <c r="K50" s="23" t="s">
         <v>55</v>
       </c>
@@ -12268,40 +12268,40 @@
       <c r="U50" s="17"/>
       <c r="V50" s="17"/>
       <c r="W50" s="76"/>
-      <c r="X50" s="145"/>
-      <c r="Y50" s="140"/>
-      <c r="Z50" s="139"/>
-      <c r="AA50" s="144"/>
+      <c r="X50" s="130"/>
+      <c r="Y50" s="132"/>
+      <c r="Z50" s="133"/>
+      <c r="AA50" s="126"/>
     </row>
     <row r="51" spans="1:27">
-      <c r="A51" s="135" t="s">
+      <c r="A51" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="125" t="s">
+      <c r="B51" s="91" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="136" t="s">
+      <c r="C51" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="105" t="s">
+      <c r="D51" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="E51" s="104">
+      <c r="E51" s="108">
         <v>33.1</v>
       </c>
-      <c r="F51" s="104" t="s">
+      <c r="F51" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="104" t="s">
+      <c r="G51" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="H51" s="103" t="s">
+      <c r="H51" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="104" t="s">
+      <c r="I51" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="106" t="s">
+      <c r="J51" s="107" t="s">
         <v>52</v>
       </c>
       <c r="K51" s="23" t="s">
@@ -12335,24 +12335,24 @@
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="39"/>
-      <c r="X51" s="145"/>
-      <c r="Y51" s="139"/>
-      <c r="Z51" s="139"/>
-      <c r="AA51" s="123" t="s">
+      <c r="X51" s="130"/>
+      <c r="Y51" s="133"/>
+      <c r="Z51" s="133"/>
+      <c r="AA51" s="93" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="15" thickBot="1">
-      <c r="A52" s="135"/>
-      <c r="B52" s="125"/>
-      <c r="C52" s="136"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="106"/>
+      <c r="A52" s="144"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="108"/>
+      <c r="J52" s="107"/>
       <c r="K52" s="23" t="s">
         <v>55</v>
       </c>
@@ -12384,10 +12384,10 @@
       <c r="U52" s="30"/>
       <c r="V52" s="30"/>
       <c r="W52" s="31"/>
-      <c r="X52" s="145"/>
-      <c r="Y52" s="139"/>
-      <c r="Z52" s="139"/>
-      <c r="AA52" s="123"/>
+      <c r="X52" s="130"/>
+      <c r="Y52" s="133"/>
+      <c r="Z52" s="133"/>
+      <c r="AA52" s="93"/>
     </row>
     <row r="54" spans="1:27" ht="14.45" customHeight="1"/>
     <row r="56" spans="1:27" ht="14.45" customHeight="1"/>
@@ -12398,27 +12398,231 @@
     <row r="66" ht="14.45" customHeight="1"/>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Y28:Y29"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y26:Y27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="Z32:Z33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z28:Z29"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="E32:G33"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="E36:G37"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="X26:X27"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="Z26:Z27"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="E18:G19"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA41:AA42"/>
+    <mergeCell ref="AA45:AA46"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="AA43:AA44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Y35"/>
+    <mergeCell ref="Z34:Z35"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A3:B3"/>
@@ -12443,231 +12647,27 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="J8:J9"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA41:AA42"/>
-    <mergeCell ref="AA45:AA46"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="Y41:Y42"/>
-    <mergeCell ref="Z41:Z42"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="AA43:AA44"/>
-    <mergeCell ref="Z43:Z44"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Z47:Z48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="Y43:Y44"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="Y49:Y50"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="E22:G23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E16:G17"/>
-    <mergeCell ref="E18:G19"/>
-    <mergeCell ref="E20:G21"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="AA30:AA31"/>
-    <mergeCell ref="X24:X25"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="E36:G37"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="X26:X27"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="Z32:Z33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="Y30:Y31"/>
-    <mergeCell ref="Z28:Z29"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Y28:Y29"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y26:Y27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B6 H6:J6 C6:C12 B8 H8:J8 B10 H10:J10 B12 H12:J12 H14:J14 H16:J16 H20:J20 C22 H22:J22 H24:J24 D26:E26 H26:J26 C26:C27 H28:J28 H30:J30 H32:J32 H34:J34 H36:J36 D41:J41 C41:C43 D45:J45 C45:C52 D47:J47 D49:J49 D51:J51">
@@ -12986,6 +12986,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -13123,40 +13143,20 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CFCB212-7126-4863-80E7-8646D7325D33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7094BB51-7951-4F88-97F3-C0EC6D9471D8}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4496F7DA-3E04-4F13-B9D0-FE26D9FB8ABD}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B59988E5-FE96-444B-A770-A47DB401478A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CFCB212-7126-4863-80E7-8646D7325D33}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
